--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_oil_gas_distribution.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.21</v>
+        <v>0.106</v>
       </c>
       <c r="G2">
-        <v>0.04111164350742693</v>
+        <v>-0.03187347931873479</v>
       </c>
       <c r="H2">
-        <v>0.04111164350742693</v>
+        <v>-0.03187347931873479</v>
       </c>
       <c r="I2">
-        <v>-0.04307618591279349</v>
+        <v>-0.0218978102189781</v>
       </c>
       <c r="J2">
-        <v>-0.04307618591279349</v>
+        <v>-0.0218978102189781</v>
       </c>
       <c r="K2">
-        <v>-13.8</v>
+        <v>-13</v>
       </c>
       <c r="L2">
-        <v>-0.06612362242453283</v>
+        <v>-0.1581508515815085</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4.04</v>
+        <v>2.64</v>
       </c>
       <c r="V2">
-        <v>0.09099099099099099</v>
+        <v>0.1681528662420382</v>
       </c>
       <c r="W2">
-        <v>-8.165680473372781</v>
+        <v>1.43646408839779</v>
       </c>
       <c r="X2">
-        <v>0.3907670634068445</v>
+        <v>1.279078026589057</v>
       </c>
       <c r="Y2">
-        <v>-8.556447536779626</v>
+        <v>0.1573860618087333</v>
       </c>
       <c r="Z2">
-        <v>1.225052829302653</v>
+        <v>0.5248706979120108</v>
       </c>
       <c r="AA2">
-        <v>-0.05277060342803475</v>
+        <v>-0.0114935189323798</v>
       </c>
       <c r="AB2">
-        <v>0.1440303046145887</v>
+        <v>0.275949920307031</v>
       </c>
       <c r="AC2">
-        <v>-0.1968009080426235</v>
+        <v>-0.2874434392394108</v>
       </c>
       <c r="AD2">
-        <v>169.7</v>
+        <v>128.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>169.7</v>
+        <v>128.5</v>
       </c>
       <c r="AG2">
-        <v>165.66</v>
+        <v>125.86</v>
       </c>
       <c r="AH2">
-        <v>0.7926202709014479</v>
+        <v>0.891123439667129</v>
       </c>
       <c r="AI2">
-        <v>1.040657386398479</v>
+        <v>0.929273936939543</v>
       </c>
       <c r="AJ2">
-        <v>0.7886318194801485</v>
+        <v>0.8890929641141565</v>
       </c>
       <c r="AK2">
-        <v>1.041690247123184</v>
+        <v>0.9278973754054852</v>
       </c>
       <c r="AL2">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="AM2">
-        <v>10.2</v>
+        <v>11.055</v>
       </c>
       <c r="AN2">
-        <v>-48.62464183381088</v>
+        <v>35.59556786703601</v>
       </c>
       <c r="AO2">
-        <v>-0.8813725490196079</v>
+        <v>-0.1621621621621622</v>
       </c>
       <c r="AP2">
-        <v>-47.46704871060172</v>
+        <v>34.86426592797784</v>
       </c>
       <c r="AQ2">
-        <v>-0.8813725490196079</v>
+        <v>-0.1628222523744912</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.21</v>
+        <v>0.106</v>
       </c>
       <c r="G3">
-        <v>0.04111164350742693</v>
+        <v>-0.03187347931873479</v>
       </c>
       <c r="H3">
-        <v>0.04111164350742693</v>
+        <v>-0.03187347931873479</v>
       </c>
       <c r="I3">
-        <v>-0.04307618591279349</v>
+        <v>-0.0218978102189781</v>
       </c>
       <c r="J3">
-        <v>-0.04307618591279349</v>
+        <v>-0.0218978102189781</v>
       </c>
       <c r="K3">
-        <v>-13.8</v>
+        <v>-13</v>
       </c>
       <c r="L3">
-        <v>-0.06612362242453283</v>
+        <v>-0.1581508515815085</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4.04</v>
+        <v>2.64</v>
       </c>
       <c r="V3">
-        <v>0.09099099099099099</v>
+        <v>0.1681528662420382</v>
       </c>
       <c r="W3">
-        <v>-8.165680473372781</v>
+        <v>1.43646408839779</v>
       </c>
       <c r="X3">
-        <v>0.3907670634068445</v>
+        <v>1.279078026589057</v>
       </c>
       <c r="Y3">
-        <v>-8.556447536779626</v>
+        <v>0.1573860618087333</v>
       </c>
       <c r="Z3">
-        <v>1.225052829302653</v>
+        <v>0.5248706979120108</v>
       </c>
       <c r="AA3">
-        <v>-0.05277060342803475</v>
+        <v>-0.0114935189323798</v>
       </c>
       <c r="AB3">
-        <v>0.1440303046145887</v>
+        <v>0.275949920307031</v>
       </c>
       <c r="AC3">
-        <v>-0.1968009080426235</v>
+        <v>-0.2874434392394108</v>
       </c>
       <c r="AD3">
-        <v>169.7</v>
+        <v>128.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>169.7</v>
+        <v>128.5</v>
       </c>
       <c r="AG3">
-        <v>165.66</v>
+        <v>125.86</v>
       </c>
       <c r="AH3">
-        <v>0.7926202709014479</v>
+        <v>0.891123439667129</v>
       </c>
       <c r="AI3">
-        <v>1.040657386398479</v>
+        <v>0.929273936939543</v>
       </c>
       <c r="AJ3">
-        <v>0.7886318194801485</v>
+        <v>0.8890929641141565</v>
       </c>
       <c r="AK3">
-        <v>1.041690247123184</v>
+        <v>0.9278973754054852</v>
       </c>
       <c r="AL3">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="AM3">
-        <v>10.2</v>
+        <v>11.055</v>
       </c>
       <c r="AN3">
-        <v>-48.62464183381088</v>
+        <v>35.59556786703601</v>
       </c>
       <c r="AO3">
-        <v>-0.8813725490196079</v>
+        <v>-0.1621621621621622</v>
       </c>
       <c r="AP3">
-        <v>-47.46704871060172</v>
+        <v>34.86426592797784</v>
       </c>
       <c r="AQ3">
-        <v>-0.8813725490196079</v>
+        <v>-0.1628222523744912</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_oil_gas_distribution.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cose_lgl_x0000" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.106</v>
+        <v>0.036</v>
       </c>
       <c r="G2">
-        <v>-0.03187347931873479</v>
+        <v>0.2578763127187865</v>
       </c>
       <c r="H2">
-        <v>-0.03187347931873479</v>
+        <v>0.2578763127187865</v>
       </c>
       <c r="I2">
-        <v>-0.0218978102189781</v>
+        <v>0.2042007001166861</v>
       </c>
       <c r="J2">
-        <v>-0.0218978102189781</v>
+        <v>0.1271990041299644</v>
       </c>
       <c r="K2">
-        <v>-13</v>
+        <v>15.5</v>
       </c>
       <c r="L2">
-        <v>-0.1581508515815085</v>
+        <v>0.1808634772462077</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="V2">
-        <v>0.1681528662420382</v>
+        <v>0.03056234718826406</v>
       </c>
       <c r="W2">
-        <v>1.43646408839779</v>
+        <v>1.890243902439025</v>
       </c>
       <c r="X2">
-        <v>1.279078026589057</v>
+        <v>0.3934745040029612</v>
       </c>
       <c r="Y2">
-        <v>0.1573860618087333</v>
+        <v>1.496769398436063</v>
       </c>
       <c r="Z2">
-        <v>0.5248706979120108</v>
+        <v>0.6392660002983739</v>
       </c>
       <c r="AA2">
-        <v>-0.0114935189323798</v>
+        <v>0.08131399861209866</v>
       </c>
       <c r="AB2">
-        <v>0.275949920307031</v>
+        <v>0.2130152901461316</v>
       </c>
       <c r="AC2">
-        <v>-0.2874434392394108</v>
+        <v>-0.1317012915340329</v>
       </c>
       <c r="AD2">
-        <v>128.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>128.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG2">
-        <v>125.86</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.891123439667129</v>
+        <v>0.706389088298636</v>
       </c>
       <c r="AI2">
-        <v>0.929273936939543</v>
+        <v>0.8692579505300354</v>
       </c>
       <c r="AJ2">
-        <v>0.8890929641141565</v>
+        <v>0.7037305324157913</v>
       </c>
       <c r="AK2">
-        <v>0.9278973754054852</v>
+        <v>0.8677981241625726</v>
       </c>
       <c r="AL2">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="AM2">
-        <v>11.055</v>
+        <v>14.657</v>
       </c>
       <c r="AN2">
-        <v>35.59556786703601</v>
+        <v>4.223175965665236</v>
       </c>
       <c r="AO2">
-        <v>-0.1621621621621622</v>
+        <v>1.182432432432432</v>
       </c>
       <c r="AP2">
-        <v>34.86426592797784</v>
+        <v>4.169527896995708</v>
       </c>
       <c r="AQ2">
-        <v>-0.1628222523744912</v>
+        <v>1.193968752132087</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +718,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.106</v>
+        <v>0.036</v>
       </c>
       <c r="G3">
-        <v>-0.03187347931873479</v>
+        <v>0.2578763127187865</v>
       </c>
       <c r="H3">
-        <v>-0.03187347931873479</v>
+        <v>0.2578763127187865</v>
       </c>
       <c r="I3">
-        <v>-0.0218978102189781</v>
+        <v>0.2042007001166861</v>
       </c>
       <c r="J3">
-        <v>-0.0218978102189781</v>
+        <v>0.1271990041299644</v>
       </c>
       <c r="K3">
-        <v>-13</v>
+        <v>15.5</v>
       </c>
       <c r="L3">
-        <v>-0.1581508515815085</v>
+        <v>0.1808634772462077</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +745,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +754,8851 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="V3">
-        <v>0.1681528662420382</v>
+        <v>0.03056234718826406</v>
       </c>
       <c r="W3">
-        <v>1.43646408839779</v>
+        <v>1.890243902439025</v>
       </c>
       <c r="X3">
-        <v>1.279078026589057</v>
+        <v>0.3934745040029612</v>
       </c>
       <c r="Y3">
-        <v>0.1573860618087333</v>
+        <v>1.496769398436063</v>
       </c>
       <c r="Z3">
-        <v>0.5248706979120108</v>
+        <v>0.6392660002983739</v>
       </c>
       <c r="AA3">
-        <v>-0.0114935189323798</v>
+        <v>0.08131399861209866</v>
       </c>
       <c r="AB3">
-        <v>0.275949920307031</v>
+        <v>0.2130152901461316</v>
       </c>
       <c r="AC3">
-        <v>-0.2874434392394108</v>
+        <v>-0.1317012915340329</v>
       </c>
       <c r="AD3">
-        <v>128.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>128.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AG3">
-        <v>125.86</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.891123439667129</v>
+        <v>0.706389088298636</v>
       </c>
       <c r="AI3">
-        <v>0.929273936939543</v>
+        <v>0.8692579505300354</v>
       </c>
       <c r="AJ3">
-        <v>0.8890929641141565</v>
+        <v>0.7037305324157913</v>
       </c>
       <c r="AK3">
-        <v>0.9278973754054852</v>
+        <v>0.8677981241625726</v>
       </c>
       <c r="AL3">
-        <v>11.1</v>
+        <v>14.8</v>
       </c>
       <c r="AM3">
-        <v>11.055</v>
+        <v>14.657</v>
       </c>
       <c r="AN3">
-        <v>35.59556786703601</v>
+        <v>4.223175965665236</v>
       </c>
       <c r="AO3">
-        <v>-0.1621621621621622</v>
+        <v>1.182432432432432</v>
       </c>
       <c r="AP3">
-        <v>34.86426592797784</v>
+        <v>4.169527896995708</v>
       </c>
       <c r="AQ3">
-        <v>-0.1628222523744912</v>
+        <v>1.193968752132087</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Laugfs Gas PLC (COSE:LGL.X0000)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>COSE:LGL.X0000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oil/Gas Distribution</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.18243243243243</v>
+      </c>
+      <c r="F2">
+        <v>4.70596081262379</v>
+      </c>
+      <c r="G2">
+        <v>4.22317596566524</v>
+      </c>
+      <c r="H2">
+        <v>5.91875536480687</v>
+      </c>
+      <c r="I2">
+        <v>0.706389088298636</v>
+      </c>
+      <c r="J2">
+        <v>0.99</v>
+      </c>
+      <c r="K2">
+        <v>40.9</v>
+      </c>
+      <c r="L2">
+        <v>115.21611701473</v>
+      </c>
+      <c r="M2">
+        <v>138.05</v>
+      </c>
+      <c r="N2">
+        <v>251.87311701473</v>
+      </c>
+      <c r="O2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P2">
+        <v>137.907</v>
+      </c>
+      <c r="Q2">
+        <v>0.213015290146132</v>
+      </c>
+      <c r="R2">
+        <v>0.1342862554993</v>
+      </c>
+      <c r="S2">
+        <v>0.138007344549136</v>
+      </c>
+      <c r="T2">
+        <v>0.038684</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.393474504002961</v>
+      </c>
+      <c r="X2">
+        <v>9.59890954992996</v>
+      </c>
+      <c r="Y2">
+        <v>1.60122501786397</v>
+      </c>
+      <c r="Z2">
+        <v>43.1603806084135</v>
+      </c>
+      <c r="AA2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AB2">
+        <v>0.1815886112488636</v>
+      </c>
+      <c r="AC2">
+        <v>1.182432432432432</v>
+      </c>
+      <c r="AD2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>14.8</v>
+      </c>
+      <c r="AF2">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>23.3</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>40.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.2215019750791156</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.24</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>5.887</v>
+      </c>
+      <c r="AR2">
+        <v>14.8</v>
+      </c>
+      <c r="AS2">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="AT2">
+        <v>1.25</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1641949311375913</v>
+      </c>
+      <c r="C2">
+        <v>193.0473923386409</v>
+      </c>
+      <c r="D2">
+        <v>191.7973923386409</v>
+      </c>
+      <c r="E2">
+        <v>-98.40000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.25</v>
+      </c>
+      <c r="H2">
+        <v>40.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K2">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L2">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="O2">
+        <v>7.927999999999999</v>
+      </c>
+      <c r="P2">
+        <v>25.10533333333333</v>
+      </c>
+      <c r="Q2">
+        <v>30.90533333333333</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1641949311375913</v>
+      </c>
+      <c r="T2">
+        <v>0.5661120226706919</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.033972</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1638457033028611</v>
+      </c>
+      <c r="C3">
+        <v>192.1900443943624</v>
+      </c>
+      <c r="D3">
+        <v>192.3330443943624</v>
+      </c>
+      <c r="E3">
+        <v>-97.00700000000001</v>
+      </c>
+      <c r="F3">
+        <v>1.393</v>
+      </c>
+      <c r="G3">
+        <v>1.25</v>
+      </c>
+      <c r="H3">
+        <v>40.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K3">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L3">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M3">
+        <v>0.06226710000000001</v>
+      </c>
+      <c r="N3">
+        <v>32.97106623333333</v>
+      </c>
+      <c r="O3">
+        <v>7.913055895999999</v>
+      </c>
+      <c r="P3">
+        <v>25.05801033733333</v>
+      </c>
+      <c r="Q3">
+        <v>30.85801033733333</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1651575588917789</v>
+      </c>
+      <c r="T3">
+        <v>0.5704579331477599</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.033972</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>530.5102266418916</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1634964754681309</v>
+      </c>
+      <c r="C4">
+        <v>191.335696769169</v>
+      </c>
+      <c r="D4">
+        <v>192.871696769169</v>
+      </c>
+      <c r="E4">
+        <v>-95.614</v>
+      </c>
+      <c r="F4">
+        <v>2.786</v>
+      </c>
+      <c r="G4">
+        <v>1.25</v>
+      </c>
+      <c r="H4">
+        <v>40.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K4">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L4">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M4">
+        <v>0.1245342</v>
+      </c>
+      <c r="N4">
+        <v>32.90879913333333</v>
+      </c>
+      <c r="O4">
+        <v>7.898111791999999</v>
+      </c>
+      <c r="P4">
+        <v>25.01068734133333</v>
+      </c>
+      <c r="Q4">
+        <v>30.81068734133333</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1661398321103377</v>
+      </c>
+      <c r="T4">
+        <v>0.5748925356753802</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.033972</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>265.2551133209458</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1631472476334007</v>
+      </c>
+      <c r="C5">
+        <v>190.4843747421469</v>
+      </c>
+      <c r="D5">
+        <v>193.4133747421469</v>
+      </c>
+      <c r="E5">
+        <v>-94.221</v>
+      </c>
+      <c r="F5">
+        <v>4.179</v>
+      </c>
+      <c r="G5">
+        <v>1.25</v>
+      </c>
+      <c r="H5">
+        <v>40.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K5">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L5">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M5">
+        <v>0.1868013</v>
+      </c>
+      <c r="N5">
+        <v>32.84653203333333</v>
+      </c>
+      <c r="O5">
+        <v>7.883167687999999</v>
+      </c>
+      <c r="P5">
+        <v>24.96336434533333</v>
+      </c>
+      <c r="Q5">
+        <v>30.76336434533333</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1671423583849492</v>
+      </c>
+      <c r="T5">
+        <v>0.5794185733066629</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.033972</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>176.8367422139638</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1627980197986705</v>
+      </c>
+      <c r="C6">
+        <v>189.6361038771664</v>
+      </c>
+      <c r="D6">
+        <v>193.9581038771664</v>
+      </c>
+      <c r="E6">
+        <v>-92.828</v>
+      </c>
+      <c r="F6">
+        <v>5.572000000000001</v>
+      </c>
+      <c r="G6">
+        <v>1.25</v>
+      </c>
+      <c r="H6">
+        <v>40.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K6">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L6">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M6">
+        <v>0.2490684000000001</v>
+      </c>
+      <c r="N6">
+        <v>32.78426493333333</v>
+      </c>
+      <c r="O6">
+        <v>7.868223584</v>
+      </c>
+      <c r="P6">
+        <v>24.91604134933333</v>
+      </c>
+      <c r="Q6">
+        <v>30.71604134933333</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1681657706236151</v>
+      </c>
+      <c r="T6">
+        <v>0.5840389033885972</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.033972</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>132.6275566604729</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1624487919639402</v>
+      </c>
+      <c r="C7">
+        <v>188.7909100269035</v>
+      </c>
+      <c r="D7">
+        <v>194.5059100269035</v>
+      </c>
+      <c r="E7">
+        <v>-91.435</v>
+      </c>
+      <c r="F7">
+        <v>6.965000000000001</v>
+      </c>
+      <c r="G7">
+        <v>1.25</v>
+      </c>
+      <c r="H7">
+        <v>40.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K7">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L7">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M7">
+        <v>0.3113355</v>
+      </c>
+      <c r="N7">
+        <v>32.72199783333333</v>
+      </c>
+      <c r="O7">
+        <v>7.853279479999999</v>
+      </c>
+      <c r="P7">
+        <v>24.86871835333334</v>
+      </c>
+      <c r="Q7">
+        <v>30.66871835333334</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.169210728383095</v>
+      </c>
+      <c r="T7">
+        <v>0.5887565035775196</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.033972</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>106.1020453283783</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.16209956412921</v>
+      </c>
+      <c r="C8">
+        <v>187.9488193369294</v>
+      </c>
+      <c r="D8">
+        <v>195.0568193369294</v>
+      </c>
+      <c r="E8">
+        <v>-90.042</v>
+      </c>
+      <c r="F8">
+        <v>8.358000000000001</v>
+      </c>
+      <c r="G8">
+        <v>1.25</v>
+      </c>
+      <c r="H8">
+        <v>40.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K8">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L8">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M8">
+        <v>0.3736026000000001</v>
+      </c>
+      <c r="N8">
+        <v>32.65973073333333</v>
+      </c>
+      <c r="O8">
+        <v>7.838335376</v>
+      </c>
+      <c r="P8">
+        <v>24.82139535733333</v>
+      </c>
+      <c r="Q8">
+        <v>30.62139535733333</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1702779192863937</v>
+      </c>
+      <c r="T8">
+        <v>0.5935744782385468</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.033972</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>88.41837110698194</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1617503362944798</v>
+      </c>
+      <c r="C9">
+        <v>187.1098582498711</v>
+      </c>
+      <c r="D9">
+        <v>195.6108582498711</v>
+      </c>
+      <c r="E9">
+        <v>-88.649</v>
+      </c>
+      <c r="F9">
+        <v>9.751000000000001</v>
+      </c>
+      <c r="G9">
+        <v>1.25</v>
+      </c>
+      <c r="H9">
+        <v>40.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K9">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L9">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M9">
+        <v>0.4358697000000001</v>
+      </c>
+      <c r="N9">
+        <v>32.59746363333333</v>
+      </c>
+      <c r="O9">
+        <v>7.823391271999999</v>
+      </c>
+      <c r="P9">
+        <v>24.77407236133334</v>
+      </c>
+      <c r="Q9">
+        <v>30.57407236133334</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1713680605316987</v>
+      </c>
+      <c r="T9">
+        <v>0.5984960652578756</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.033972</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>75.78717523455595</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1614011084597496</v>
+      </c>
+      <c r="C10">
+        <v>186.274053509641</v>
+      </c>
+      <c r="D10">
+        <v>196.168053509641</v>
+      </c>
+      <c r="E10">
+        <v>-87.256</v>
+      </c>
+      <c r="F10">
+        <v>11.144</v>
+      </c>
+      <c r="G10">
+        <v>1.25</v>
+      </c>
+      <c r="H10">
+        <v>40.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K10">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L10">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M10">
+        <v>0.4981368000000001</v>
+      </c>
+      <c r="N10">
+        <v>32.53519653333333</v>
+      </c>
+      <c r="O10">
+        <v>7.808447168</v>
+      </c>
+      <c r="P10">
+        <v>24.72674936533333</v>
+      </c>
+      <c r="Q10">
+        <v>30.52674936533333</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1724819004997278</v>
+      </c>
+      <c r="T10">
+        <v>0.6035246432993637</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.033972</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>66.31377833023645</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1610518806250194</v>
+      </c>
+      <c r="C11">
+        <v>185.4414321657416</v>
+      </c>
+      <c r="D11">
+        <v>196.7284321657416</v>
+      </c>
+      <c r="E11">
+        <v>-85.863</v>
+      </c>
+      <c r="F11">
+        <v>12.537</v>
+      </c>
+      <c r="G11">
+        <v>1.25</v>
+      </c>
+      <c r="H11">
+        <v>40.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K11">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L11">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M11">
+        <v>0.5604039000000001</v>
+      </c>
+      <c r="N11">
+        <v>32.47292943333333</v>
+      </c>
+      <c r="O11">
+        <v>7.793503064</v>
+      </c>
+      <c r="P11">
+        <v>24.67942636933333</v>
+      </c>
+      <c r="Q11">
+        <v>30.47942636933334</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1736202204670542</v>
+      </c>
+      <c r="T11">
+        <v>0.6086637395395659</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.033972</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>58.94558073798796</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1607026527902892</v>
+      </c>
+      <c r="C12">
+        <v>184.6120215776415</v>
+      </c>
+      <c r="D12">
+        <v>197.2920215776415</v>
+      </c>
+      <c r="E12">
+        <v>-84.47</v>
+      </c>
+      <c r="F12">
+        <v>13.93</v>
+      </c>
+      <c r="G12">
+        <v>1.25</v>
+      </c>
+      <c r="H12">
+        <v>40.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K12">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L12">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M12">
+        <v>0.6226710000000001</v>
+      </c>
+      <c r="N12">
+        <v>32.41066233333333</v>
+      </c>
+      <c r="O12">
+        <v>7.77855896</v>
+      </c>
+      <c r="P12">
+        <v>24.63210337333334</v>
+      </c>
+      <c r="Q12">
+        <v>30.43210337333334</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1747838364336546</v>
+      </c>
+      <c r="T12">
+        <v>0.6139170379184393</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.033972</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>53.05102266418916</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1603534249555589</v>
+      </c>
+      <c r="C13">
+        <v>183.7858494192288</v>
+      </c>
+      <c r="D13">
+        <v>197.8588494192288</v>
+      </c>
+      <c r="E13">
+        <v>-83.077</v>
+      </c>
+      <c r="F13">
+        <v>15.323</v>
+      </c>
+      <c r="G13">
+        <v>1.25</v>
+      </c>
+      <c r="H13">
+        <v>40.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K13">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L13">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M13">
+        <v>0.6849381000000001</v>
+      </c>
+      <c r="N13">
+        <v>32.34839523333333</v>
+      </c>
+      <c r="O13">
+        <v>7.763614856</v>
+      </c>
+      <c r="P13">
+        <v>24.58478037733333</v>
+      </c>
+      <c r="Q13">
+        <v>30.38478037733334</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1759736010736617</v>
+      </c>
+      <c r="T13">
+        <v>0.6192883879462761</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.033972</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>48.22820242199015</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1600041971208287</v>
+      </c>
+      <c r="C14">
+        <v>182.9629436833409</v>
+      </c>
+      <c r="D14">
+        <v>198.4289436833409</v>
+      </c>
+      <c r="E14">
+        <v>-81.684</v>
+      </c>
+      <c r="F14">
+        <v>16.716</v>
+      </c>
+      <c r="G14">
+        <v>1.25</v>
+      </c>
+      <c r="H14">
+        <v>40.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K14">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L14">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M14">
+        <v>0.7472052000000001</v>
+      </c>
+      <c r="N14">
+        <v>32.28612813333333</v>
+      </c>
+      <c r="O14">
+        <v>7.748670751999999</v>
+      </c>
+      <c r="P14">
+        <v>24.53745738133333</v>
+      </c>
+      <c r="Q14">
+        <v>30.33745738133333</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1771904058191235</v>
+      </c>
+      <c r="T14">
+        <v>0.624781814111109</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.033972</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>44.20918555349096</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1596549692860985</v>
+      </c>
+      <c r="C15">
+        <v>182.1433326863722</v>
+      </c>
+      <c r="D15">
+        <v>199.0023326863722</v>
+      </c>
+      <c r="E15">
+        <v>-80.291</v>
+      </c>
+      <c r="F15">
+        <v>18.109</v>
+      </c>
+      <c r="G15">
+        <v>1.25</v>
+      </c>
+      <c r="H15">
+        <v>40.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K15">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L15">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M15">
+        <v>0.8094723000000001</v>
+      </c>
+      <c r="N15">
+        <v>32.22386103333333</v>
+      </c>
+      <c r="O15">
+        <v>7.733726647999998</v>
+      </c>
+      <c r="P15">
+        <v>24.49013438533333</v>
+      </c>
+      <c r="Q15">
+        <v>30.29013438533333</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1784351830874695</v>
+      </c>
+      <c r="T15">
+        <v>0.6304015259349038</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.033972</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>40.80847897245319</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1593057414513683</v>
+      </c>
+      <c r="C16">
+        <v>181.3270450729631</v>
+      </c>
+      <c r="D16">
+        <v>199.5790450729631</v>
+      </c>
+      <c r="E16">
+        <v>-78.898</v>
+      </c>
+      <c r="F16">
+        <v>19.502</v>
+      </c>
+      <c r="G16">
+        <v>1.25</v>
+      </c>
+      <c r="H16">
+        <v>40.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K16">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L16">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M16">
+        <v>0.8717394000000002</v>
+      </c>
+      <c r="N16">
+        <v>32.16159393333333</v>
+      </c>
+      <c r="O16">
+        <v>7.718782543999999</v>
+      </c>
+      <c r="P16">
+        <v>24.44281138933333</v>
+      </c>
+      <c r="Q16">
+        <v>30.24281138933333</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1797089086643817</v>
+      </c>
+      <c r="T16">
+        <v>0.636151928731345</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.033972</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>37.89358761727797</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.158956513616638</v>
+      </c>
+      <c r="C17">
+        <v>180.5141098207697</v>
+      </c>
+      <c r="D17">
+        <v>200.1591098207697</v>
+      </c>
+      <c r="E17">
+        <v>-77.50500000000001</v>
+      </c>
+      <c r="F17">
+        <v>20.895</v>
+      </c>
+      <c r="G17">
+        <v>1.25</v>
+      </c>
+      <c r="H17">
+        <v>40.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K17">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L17">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M17">
+        <v>0.9340065000000001</v>
+      </c>
+      <c r="N17">
+        <v>32.09932683333333</v>
+      </c>
+      <c r="O17">
+        <v>7.703838439999998</v>
+      </c>
+      <c r="P17">
+        <v>24.39548839333333</v>
+      </c>
+      <c r="Q17">
+        <v>30.19548839333333</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1810126042548683</v>
+      </c>
+      <c r="T17">
+        <v>0.6420376351229965</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.24</v>
+      </c>
+      <c r="W17">
+        <v>0.033972</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>35.36734844279277</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1586072857819078</v>
+      </c>
+      <c r="C18">
+        <v>179.7045562453175</v>
+      </c>
+      <c r="D18">
+        <v>200.7425562453176</v>
+      </c>
+      <c r="E18">
+        <v>-76.11199999999999</v>
+      </c>
+      <c r="F18">
+        <v>22.288</v>
+      </c>
+      <c r="G18">
+        <v>1.25</v>
+      </c>
+      <c r="H18">
+        <v>40.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K18">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L18">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M18">
+        <v>0.9962736000000002</v>
+      </c>
+      <c r="N18">
+        <v>32.03705973333333</v>
+      </c>
+      <c r="O18">
+        <v>7.688894335999999</v>
+      </c>
+      <c r="P18">
+        <v>24.34816539733333</v>
+      </c>
+      <c r="Q18">
+        <v>30.14816539733333</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.182347340216557</v>
+      </c>
+      <c r="T18">
+        <v>0.648063477381116</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.24</v>
+      </c>
+      <c r="W18">
+        <v>0.033972</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>33.15688916511822</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1582580579471776</v>
+      </c>
+      <c r="C19">
+        <v>178.8984140049402</v>
+      </c>
+      <c r="D19">
+        <v>201.3294140049402</v>
+      </c>
+      <c r="E19">
+        <v>-74.71899999999999</v>
+      </c>
+      <c r="F19">
+        <v>23.681</v>
+      </c>
+      <c r="G19">
+        <v>1.25</v>
+      </c>
+      <c r="H19">
+        <v>40.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K19">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L19">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M19">
+        <v>1.0585407</v>
+      </c>
+      <c r="N19">
+        <v>31.97479263333333</v>
+      </c>
+      <c r="O19">
+        <v>7.673950231999999</v>
+      </c>
+      <c r="P19">
+        <v>24.30084240133333</v>
+      </c>
+      <c r="Q19">
+        <v>30.10084240133333</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1837142384905754</v>
+      </c>
+      <c r="T19">
+        <v>0.6542345206575033</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.24</v>
+      </c>
+      <c r="W19">
+        <v>0.033972</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>31.20648392011126</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1579088301124474</v>
+      </c>
+      <c r="C20">
+        <v>178.0957131058052</v>
+      </c>
+      <c r="D20">
+        <v>201.9197131058052</v>
+      </c>
+      <c r="E20">
+        <v>-73.32600000000001</v>
+      </c>
+      <c r="F20">
+        <v>25.074</v>
+      </c>
+      <c r="G20">
+        <v>1.25</v>
+      </c>
+      <c r="H20">
+        <v>40.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K20">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L20">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M20">
+        <v>1.1208078</v>
+      </c>
+      <c r="N20">
+        <v>31.91252553333333</v>
+      </c>
+      <c r="O20">
+        <v>7.659006127999999</v>
+      </c>
+      <c r="P20">
+        <v>24.25351940533333</v>
+      </c>
+      <c r="Q20">
+        <v>30.05351940533333</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1851144757468871</v>
+      </c>
+      <c r="T20">
+        <v>0.6605560771845341</v>
+      </c>
+      <c r="U20">
+        <v>0.0447</v>
+      </c>
+      <c r="V20">
+        <v>0.24</v>
+      </c>
+      <c r="W20">
+        <v>0.033972</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>29.47279036899398</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1575596022777172</v>
+      </c>
+      <c r="C21">
+        <v>177.2964839070275</v>
+      </c>
+      <c r="D21">
+        <v>202.5134839070275</v>
+      </c>
+      <c r="E21">
+        <v>-71.93300000000001</v>
+      </c>
+      <c r="F21">
+        <v>26.467</v>
+      </c>
+      <c r="G21">
+        <v>1.25</v>
+      </c>
+      <c r="H21">
+        <v>40.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K21">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L21">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M21">
+        <v>1.1830749</v>
+      </c>
+      <c r="N21">
+        <v>31.85025843333333</v>
+      </c>
+      <c r="O21">
+        <v>7.644062023999999</v>
+      </c>
+      <c r="P21">
+        <v>24.20619640933333</v>
+      </c>
+      <c r="Q21">
+        <v>30.00619640933333</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1865492867626138</v>
+      </c>
+      <c r="T21">
+        <v>0.6670337215270473</v>
+      </c>
+      <c r="U21">
+        <v>0.0447</v>
+      </c>
+      <c r="V21">
+        <v>0.24</v>
+      </c>
+      <c r="W21">
+        <v>0.033972</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>27.92159087588903</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.157210374442987</v>
+      </c>
+      <c r="C22">
+        <v>176.5007571258752</v>
+      </c>
+      <c r="D22">
+        <v>203.1107571258752</v>
+      </c>
+      <c r="E22">
+        <v>-70.54000000000001</v>
+      </c>
+      <c r="F22">
+        <v>27.86</v>
+      </c>
+      <c r="G22">
+        <v>1.25</v>
+      </c>
+      <c r="H22">
+        <v>40.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K22">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L22">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M22">
+        <v>1.245342</v>
+      </c>
+      <c r="N22">
+        <v>31.78799133333333</v>
+      </c>
+      <c r="O22">
+        <v>7.629117919999999</v>
+      </c>
+      <c r="P22">
+        <v>24.15887341333333</v>
+      </c>
+      <c r="Q22">
+        <v>29.95887341333333</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1880199680537337</v>
+      </c>
+      <c r="T22">
+        <v>0.6736733069781233</v>
+      </c>
+      <c r="U22">
+        <v>0.0447</v>
+      </c>
+      <c r="V22">
+        <v>0.24</v>
+      </c>
+      <c r="W22">
+        <v>0.033972</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>26.52551133209458</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1568611466082567</v>
+      </c>
+      <c r="C23">
+        <v>175.708563843066</v>
+      </c>
+      <c r="D23">
+        <v>203.711563843066</v>
+      </c>
+      <c r="E23">
+        <v>-69.14700000000001</v>
+      </c>
+      <c r="F23">
+        <v>29.253</v>
+      </c>
+      <c r="G23">
+        <v>1.25</v>
+      </c>
+      <c r="H23">
+        <v>40.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K23">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L23">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M23">
+        <v>1.3076091</v>
+      </c>
+      <c r="N23">
+        <v>31.72572423333333</v>
+      </c>
+      <c r="O23">
+        <v>7.614173815999999</v>
+      </c>
+      <c r="P23">
+        <v>24.11155041733333</v>
+      </c>
+      <c r="Q23">
+        <v>29.91155041733333</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1895278817826035</v>
+      </c>
+      <c r="T23">
+        <v>0.6804809832001127</v>
+      </c>
+      <c r="U23">
+        <v>0.0447</v>
+      </c>
+      <c r="V23">
+        <v>0.24</v>
+      </c>
+      <c r="W23">
+        <v>0.033972</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>25.26239174485198</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1565119187735265</v>
+      </c>
+      <c r="C24">
+        <v>174.9199355081587</v>
+      </c>
+      <c r="D24">
+        <v>204.3159355081587</v>
+      </c>
+      <c r="E24">
+        <v>-67.754</v>
+      </c>
+      <c r="F24">
+        <v>30.646</v>
+      </c>
+      <c r="G24">
+        <v>1.25</v>
+      </c>
+      <c r="H24">
+        <v>40.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K24">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L24">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M24">
+        <v>1.3698762</v>
+      </c>
+      <c r="N24">
+        <v>31.66345713333333</v>
+      </c>
+      <c r="O24">
+        <v>7.599229712</v>
+      </c>
+      <c r="P24">
+        <v>24.06422742133333</v>
+      </c>
+      <c r="Q24">
+        <v>29.86422742133333</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1910744599660597</v>
+      </c>
+      <c r="T24">
+        <v>0.687463215222666</v>
+      </c>
+      <c r="U24">
+        <v>0.0447</v>
+      </c>
+      <c r="V24">
+        <v>0.24</v>
+      </c>
+      <c r="W24">
+        <v>0.033972</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>24.11410121099507</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1561626909387963</v>
+      </c>
+      <c r="C25">
+        <v>174.1349039450413</v>
+      </c>
+      <c r="D25">
+        <v>204.9239039450413</v>
+      </c>
+      <c r="E25">
+        <v>-66.361</v>
+      </c>
+      <c r="F25">
+        <v>32.039</v>
+      </c>
+      <c r="G25">
+        <v>1.25</v>
+      </c>
+      <c r="H25">
+        <v>40.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K25">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L25">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M25">
+        <v>1.4321433</v>
+      </c>
+      <c r="N25">
+        <v>31.60119003333333</v>
+      </c>
+      <c r="O25">
+        <v>7.584285607999999</v>
+      </c>
+      <c r="P25">
+        <v>24.01690442533333</v>
+      </c>
+      <c r="Q25">
+        <v>29.81690442533333</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1926612090114238</v>
+      </c>
+      <c r="T25">
+        <v>0.6946268039211296</v>
+      </c>
+      <c r="U25">
+        <v>0.0447</v>
+      </c>
+      <c r="V25">
+        <v>0.24</v>
+      </c>
+      <c r="W25">
+        <v>0.033972</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>23.06566202790833</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1558134631040661</v>
+      </c>
+      <c r="C26">
+        <v>173.3535013575163</v>
+      </c>
+      <c r="D26">
+        <v>205.5355013575164</v>
+      </c>
+      <c r="E26">
+        <v>-64.968</v>
+      </c>
+      <c r="F26">
+        <v>33.432</v>
+      </c>
+      <c r="G26">
+        <v>1.25</v>
+      </c>
+      <c r="H26">
+        <v>40.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K26">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L26">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M26">
+        <v>1.4944104</v>
+      </c>
+      <c r="N26">
+        <v>31.53892293333333</v>
+      </c>
+      <c r="O26">
+        <v>7.569341504</v>
+      </c>
+      <c r="P26">
+        <v>23.96958142933333</v>
+      </c>
+      <c r="Q26">
+        <v>29.76958142933333</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1942897146106133</v>
+      </c>
+      <c r="T26">
+        <v>0.701978908111658</v>
+      </c>
+      <c r="U26">
+        <v>0.0447</v>
+      </c>
+      <c r="V26">
+        <v>0.24</v>
+      </c>
+      <c r="W26">
+        <v>0.033972</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>22.10459277674548</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1554642352693359</v>
+      </c>
+      <c r="C27">
+        <v>172.5757603349876</v>
+      </c>
+      <c r="D27">
+        <v>206.1507603349876</v>
+      </c>
+      <c r="E27">
+        <v>-63.575</v>
+      </c>
+      <c r="F27">
+        <v>34.825</v>
+      </c>
+      <c r="G27">
+        <v>1.25</v>
+      </c>
+      <c r="H27">
+        <v>40.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K27">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L27">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M27">
+        <v>1.5566775</v>
+      </c>
+      <c r="N27">
+        <v>31.47665583333333</v>
+      </c>
+      <c r="O27">
+        <v>7.554397399999999</v>
+      </c>
+      <c r="P27">
+        <v>23.92225843333333</v>
+      </c>
+      <c r="Q27">
+        <v>29.72225843333333</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1959616470257812</v>
+      </c>
+      <c r="T27">
+        <v>0.709527068413934</v>
+      </c>
+      <c r="U27">
+        <v>0.0447</v>
+      </c>
+      <c r="V27">
+        <v>0.24</v>
+      </c>
+      <c r="W27">
+        <v>0.033972</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>21.22040906567566</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1551150074346056</v>
+      </c>
+      <c r="C28">
+        <v>171.8017138582487</v>
+      </c>
+      <c r="D28">
+        <v>206.7697138582487</v>
+      </c>
+      <c r="E28">
+        <v>-62.182</v>
+      </c>
+      <c r="F28">
+        <v>36.218</v>
+      </c>
+      <c r="G28">
+        <v>1.25</v>
+      </c>
+      <c r="H28">
+        <v>40.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K28">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L28">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M28">
+        <v>1.6189446</v>
+      </c>
+      <c r="N28">
+        <v>31.41438873333333</v>
+      </c>
+      <c r="O28">
+        <v>7.539453296</v>
+      </c>
+      <c r="P28">
+        <v>23.87493543733333</v>
+      </c>
+      <c r="Q28">
+        <v>29.67493543733334</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1976787668035211</v>
+      </c>
+      <c r="T28">
+        <v>0.7172792330487037</v>
+      </c>
+      <c r="U28">
+        <v>0.0447</v>
+      </c>
+      <c r="V28">
+        <v>0.24</v>
+      </c>
+      <c r="W28">
+        <v>0.033972</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>20.4042394862266</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1547657795998754</v>
+      </c>
+      <c r="C29">
+        <v>171.031395305376</v>
+      </c>
+      <c r="D29">
+        <v>207.392395305376</v>
+      </c>
+      <c r="E29">
+        <v>-60.789</v>
+      </c>
+      <c r="F29">
+        <v>37.611</v>
+      </c>
+      <c r="G29">
+        <v>1.25</v>
+      </c>
+      <c r="H29">
+        <v>40.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K29">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L29">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M29">
+        <v>1.6812117</v>
+      </c>
+      <c r="N29">
+        <v>31.35212163333333</v>
+      </c>
+      <c r="O29">
+        <v>7.524509192</v>
+      </c>
+      <c r="P29">
+        <v>23.82761244133333</v>
+      </c>
+      <c r="Q29">
+        <v>29.62761244133333</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1994429309587334</v>
+      </c>
+      <c r="T29">
+        <v>0.725243785755659</v>
+      </c>
+      <c r="U29">
+        <v>0.0447</v>
+      </c>
+      <c r="V29">
+        <v>0.24</v>
+      </c>
+      <c r="W29">
+        <v>0.033972</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>19.64852691266265</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1544165517651452</v>
+      </c>
+      <c r="C30">
+        <v>170.2648384577296</v>
+      </c>
+      <c r="D30">
+        <v>208.0188384577296</v>
+      </c>
+      <c r="E30">
+        <v>-59.396</v>
+      </c>
+      <c r="F30">
+        <v>39.004</v>
+      </c>
+      <c r="G30">
+        <v>1.25</v>
+      </c>
+      <c r="H30">
+        <v>40.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K30">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L30">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M30">
+        <v>1.7434788</v>
+      </c>
+      <c r="N30">
+        <v>31.28985453333333</v>
+      </c>
+      <c r="O30">
+        <v>7.509565087999999</v>
+      </c>
+      <c r="P30">
+        <v>23.78028944533333</v>
+      </c>
+      <c r="Q30">
+        <v>29.58028944533333</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2012560996738128</v>
+      </c>
+      <c r="T30">
+        <v>0.7334295760378076</v>
+      </c>
+      <c r="U30">
+        <v>0.0447</v>
+      </c>
+      <c r="V30">
+        <v>0.24</v>
+      </c>
+      <c r="W30">
+        <v>0.033972</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>18.94679380863898</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.154067323930415</v>
+      </c>
+      <c r="C31">
+        <v>169.5020775060616</v>
+      </c>
+      <c r="D31">
+        <v>208.6490775060616</v>
+      </c>
+      <c r="E31">
+        <v>-58.00300000000001</v>
+      </c>
+      <c r="F31">
+        <v>40.397</v>
+      </c>
+      <c r="G31">
+        <v>1.25</v>
+      </c>
+      <c r="H31">
+        <v>40.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K31">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L31">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M31">
+        <v>1.8057459</v>
+      </c>
+      <c r="N31">
+        <v>31.22758743333333</v>
+      </c>
+      <c r="O31">
+        <v>7.494620983999999</v>
+      </c>
+      <c r="P31">
+        <v>23.73296644933333</v>
+      </c>
+      <c r="Q31">
+        <v>29.53296644933333</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2031203435639648</v>
+      </c>
+      <c r="T31">
+        <v>0.7418459519617068</v>
+      </c>
+      <c r="U31">
+        <v>0.0447</v>
+      </c>
+      <c r="V31">
+        <v>0.24</v>
+      </c>
+      <c r="W31">
+        <v>0.033972</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>18.29345609109971</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1537180960956847</v>
+      </c>
+      <c r="C32">
+        <v>168.7431470567374</v>
+      </c>
+      <c r="D32">
+        <v>209.2831470567374</v>
+      </c>
+      <c r="E32">
+        <v>-56.61000000000001</v>
+      </c>
+      <c r="F32">
+        <v>41.79</v>
+      </c>
+      <c r="G32">
+        <v>1.25</v>
+      </c>
+      <c r="H32">
+        <v>40.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K32">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L32">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M32">
+        <v>1.868013</v>
+      </c>
+      <c r="N32">
+        <v>31.16532033333333</v>
+      </c>
+      <c r="O32">
+        <v>7.479676879999999</v>
+      </c>
+      <c r="P32">
+        <v>23.68564345333333</v>
+      </c>
+      <c r="Q32">
+        <v>29.48564345333333</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2050378515652639</v>
+      </c>
+      <c r="T32">
+        <v>0.7505027957691458</v>
+      </c>
+      <c r="U32">
+        <v>0.0447</v>
+      </c>
+      <c r="V32">
+        <v>0.24</v>
+      </c>
+      <c r="W32">
+        <v>0.033972</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>17.68367422139639</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1533688682609546</v>
+      </c>
+      <c r="C33">
+        <v>167.9880821380692</v>
+      </c>
+      <c r="D33">
+        <v>209.9210821380692</v>
+      </c>
+      <c r="E33">
+        <v>-55.21700000000001</v>
+      </c>
+      <c r="F33">
+        <v>43.183</v>
+      </c>
+      <c r="G33">
+        <v>1.25</v>
+      </c>
+      <c r="H33">
+        <v>40.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K33">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L33">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M33">
+        <v>1.9302801</v>
+      </c>
+      <c r="N33">
+        <v>31.10305323333333</v>
+      </c>
+      <c r="O33">
+        <v>7.464732775999999</v>
+      </c>
+      <c r="P33">
+        <v>23.63832045733333</v>
+      </c>
+      <c r="Q33">
+        <v>29.43832045733333</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2070109395086298</v>
+      </c>
+      <c r="T33">
+        <v>0.7594105625854963</v>
+      </c>
+      <c r="U33">
+        <v>0.0447</v>
+      </c>
+      <c r="V33">
+        <v>0.24</v>
+      </c>
+      <c r="W33">
+        <v>0.033972</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>17.11323311748037</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1530196404262243</v>
+      </c>
+      <c r="C34">
+        <v>167.2369182067675</v>
+      </c>
+      <c r="D34">
+        <v>210.5629182067675</v>
+      </c>
+      <c r="E34">
+        <v>-53.824</v>
+      </c>
+      <c r="F34">
+        <v>44.57600000000001</v>
+      </c>
+      <c r="G34">
+        <v>1.25</v>
+      </c>
+      <c r="H34">
+        <v>40.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K34">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L34">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M34">
+        <v>1.9925472</v>
+      </c>
+      <c r="N34">
+        <v>31.04078613333333</v>
+      </c>
+      <c r="O34">
+        <v>7.449788672</v>
+      </c>
+      <c r="P34">
+        <v>23.59099746133333</v>
+      </c>
+      <c r="Q34">
+        <v>29.39099746133333</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2090420594503299</v>
+      </c>
+      <c r="T34">
+        <v>0.7685803225435042</v>
+      </c>
+      <c r="U34">
+        <v>0.0447</v>
+      </c>
+      <c r="V34">
+        <v>0.24</v>
+      </c>
+      <c r="W34">
+        <v>0.033972</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>16.57844458255911</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1526704125914941</v>
+      </c>
+      <c r="C35">
+        <v>166.4896911545096</v>
+      </c>
+      <c r="D35">
+        <v>211.2086911545096</v>
+      </c>
+      <c r="E35">
+        <v>-52.431</v>
+      </c>
+      <c r="F35">
+        <v>45.96900000000001</v>
+      </c>
+      <c r="G35">
+        <v>1.25</v>
+      </c>
+      <c r="H35">
+        <v>40.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K35">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L35">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M35">
+        <v>2.0548143</v>
+      </c>
+      <c r="N35">
+        <v>30.97851903333333</v>
+      </c>
+      <c r="O35">
+        <v>7.434844567999999</v>
+      </c>
+      <c r="P35">
+        <v>23.54367446533333</v>
+      </c>
+      <c r="Q35">
+        <v>29.34367446533333</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2111338098380509</v>
+      </c>
+      <c r="T35">
+        <v>0.7780238066793629</v>
+      </c>
+      <c r="U35">
+        <v>0.0447</v>
+      </c>
+      <c r="V35">
+        <v>0.24</v>
+      </c>
+      <c r="W35">
+        <v>0.033972</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>16.07606747399672</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1523211847567639</v>
+      </c>
+      <c r="C36">
+        <v>165.7464373146306</v>
+      </c>
+      <c r="D36">
+        <v>211.8584373146306</v>
+      </c>
+      <c r="E36">
+        <v>-51.038</v>
+      </c>
+      <c r="F36">
+        <v>47.36200000000001</v>
+      </c>
+      <c r="G36">
+        <v>1.25</v>
+      </c>
+      <c r="H36">
+        <v>40.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K36">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L36">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M36">
+        <v>2.1170814</v>
+      </c>
+      <c r="N36">
+        <v>30.91625193333333</v>
+      </c>
+      <c r="O36">
+        <v>7.419900463999999</v>
+      </c>
+      <c r="P36">
+        <v>23.49635146933333</v>
+      </c>
+      <c r="Q36">
+        <v>29.29635146933333</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2132889466011574</v>
+      </c>
+      <c r="T36">
+        <v>0.7877534570011568</v>
+      </c>
+      <c r="U36">
+        <v>0.0447</v>
+      </c>
+      <c r="V36">
+        <v>0.24</v>
+      </c>
+      <c r="W36">
+        <v>0.033972</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>15.60324196005563</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1519719569220336</v>
+      </c>
+      <c r="C37">
+        <v>165.0071934689374</v>
+      </c>
+      <c r="D37">
+        <v>212.5121934689375</v>
+      </c>
+      <c r="E37">
+        <v>-49.645</v>
+      </c>
+      <c r="F37">
+        <v>48.75500000000001</v>
+      </c>
+      <c r="G37">
+        <v>1.25</v>
+      </c>
+      <c r="H37">
+        <v>40.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K37">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L37">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M37">
+        <v>2.179348500000001</v>
+      </c>
+      <c r="N37">
+        <v>30.85398483333333</v>
+      </c>
+      <c r="O37">
+        <v>7.404956359999999</v>
+      </c>
+      <c r="P37">
+        <v>23.44902847333333</v>
+      </c>
+      <c r="Q37">
+        <v>29.24902847333333</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2155103952646672</v>
+      </c>
+      <c r="T37">
+        <v>0.7977824811790059</v>
+      </c>
+      <c r="U37">
+        <v>0.0447</v>
+      </c>
+      <c r="V37">
+        <v>0.24</v>
+      </c>
+      <c r="W37">
+        <v>0.033972</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>15.15743504691119</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1516227290873035</v>
+      </c>
+      <c r="C38">
+        <v>164.2719968546497</v>
+      </c>
+      <c r="D38">
+        <v>213.1699968546497</v>
+      </c>
+      <c r="E38">
+        <v>-48.252</v>
+      </c>
+      <c r="F38">
+        <v>50.148</v>
+      </c>
+      <c r="G38">
+        <v>1.25</v>
+      </c>
+      <c r="H38">
+        <v>40.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K38">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L38">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M38">
+        <v>2.2416156</v>
+      </c>
+      <c r="N38">
+        <v>30.79171773333333</v>
+      </c>
+      <c r="O38">
+        <v>7.390012255999999</v>
+      </c>
+      <c r="P38">
+        <v>23.40170547733333</v>
+      </c>
+      <c r="Q38">
+        <v>29.20170547733333</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2178012641989116</v>
+      </c>
+      <c r="T38">
+        <v>0.8081249123624127</v>
+      </c>
+      <c r="U38">
+        <v>0.0447</v>
+      </c>
+      <c r="V38">
+        <v>0.24</v>
+      </c>
+      <c r="W38">
+        <v>0.033972</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>14.73639518449699</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1512735012525732</v>
+      </c>
+      <c r="C39">
+        <v>163.5408851714704</v>
+      </c>
+      <c r="D39">
+        <v>213.8318851714704</v>
+      </c>
+      <c r="E39">
+        <v>-46.859</v>
+      </c>
+      <c r="F39">
+        <v>51.541</v>
+      </c>
+      <c r="G39">
+        <v>1.25</v>
+      </c>
+      <c r="H39">
+        <v>40.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K39">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L39">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M39">
+        <v>2.3038827</v>
+      </c>
+      <c r="N39">
+        <v>30.72945063333333</v>
+      </c>
+      <c r="O39">
+        <v>7.375068152</v>
+      </c>
+      <c r="P39">
+        <v>23.35438248133333</v>
+      </c>
+      <c r="Q39">
+        <v>29.15438248133333</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2201648591310686</v>
+      </c>
+      <c r="T39">
+        <v>0.8187956746944992</v>
+      </c>
+      <c r="U39">
+        <v>0.0447</v>
+      </c>
+      <c r="V39">
+        <v>0.24</v>
+      </c>
+      <c r="W39">
+        <v>0.033972</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>14.33811423356464</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.150924273417843</v>
+      </c>
+      <c r="C40">
+        <v>162.8138965887879</v>
+      </c>
+      <c r="D40">
+        <v>214.4978965887879</v>
+      </c>
+      <c r="E40">
+        <v>-45.466</v>
+      </c>
+      <c r="F40">
+        <v>52.934</v>
+      </c>
+      <c r="G40">
+        <v>1.25</v>
+      </c>
+      <c r="H40">
+        <v>40.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K40">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L40">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M40">
+        <v>2.366149800000001</v>
+      </c>
+      <c r="N40">
+        <v>30.66718353333333</v>
+      </c>
+      <c r="O40">
+        <v>7.360124047999999</v>
+      </c>
+      <c r="P40">
+        <v>23.30705948533333</v>
+      </c>
+      <c r="Q40">
+        <v>29.10705948533333</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2226046990610371</v>
+      </c>
+      <c r="T40">
+        <v>0.8298106551663303</v>
+      </c>
+      <c r="U40">
+        <v>0.0447</v>
+      </c>
+      <c r="V40">
+        <v>0.24</v>
+      </c>
+      <c r="W40">
+        <v>0.033972</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>13.96079543794451</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1505750455831128</v>
+      </c>
+      <c r="C41">
+        <v>162.0910697530134</v>
+      </c>
+      <c r="D41">
+        <v>215.1680697530134</v>
+      </c>
+      <c r="E41">
+        <v>-44.073</v>
+      </c>
+      <c r="F41">
+        <v>54.32700000000001</v>
+      </c>
+      <c r="G41">
+        <v>1.25</v>
+      </c>
+      <c r="H41">
+        <v>40.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K41">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L41">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M41">
+        <v>2.4284169</v>
+      </c>
+      <c r="N41">
+        <v>30.60491643333333</v>
+      </c>
+      <c r="O41">
+        <v>7.345179943999999</v>
+      </c>
+      <c r="P41">
+        <v>23.25973648933333</v>
+      </c>
+      <c r="Q41">
+        <v>29.05973648933333</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2251245337428079</v>
+      </c>
+      <c r="T41">
+        <v>0.8411867825388774</v>
+      </c>
+      <c r="U41">
+        <v>0.0447</v>
+      </c>
+      <c r="V41">
+        <v>0.24</v>
+      </c>
+      <c r="W41">
+        <v>0.033972</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>13.60282632415107</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1502258177483826</v>
+      </c>
+      <c r="C42">
+        <v>161.3724437950564</v>
+      </c>
+      <c r="D42">
+        <v>215.8424437950564</v>
+      </c>
+      <c r="E42">
+        <v>-42.68</v>
+      </c>
+      <c r="F42">
+        <v>55.72000000000001</v>
+      </c>
+      <c r="G42">
+        <v>1.25</v>
+      </c>
+      <c r="H42">
+        <v>40.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K42">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L42">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M42">
+        <v>2.490684</v>
+      </c>
+      <c r="N42">
+        <v>30.54264933333333</v>
+      </c>
+      <c r="O42">
+        <v>7.330235839999999</v>
+      </c>
+      <c r="P42">
+        <v>23.21241349333333</v>
+      </c>
+      <c r="Q42">
+        <v>29.01241349333333</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.227728362913971</v>
+      </c>
+      <c r="T42">
+        <v>0.8529421141571759</v>
+      </c>
+      <c r="U42">
+        <v>0.0447</v>
+      </c>
+      <c r="V42">
+        <v>0.24</v>
+      </c>
+      <c r="W42">
+        <v>0.033972</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>13.26275566604729</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1498765899136524</v>
+      </c>
+      <c r="C43">
+        <v>160.658058337941</v>
+      </c>
+      <c r="D43">
+        <v>216.521058337941</v>
+      </c>
+      <c r="E43">
+        <v>-41.287</v>
+      </c>
+      <c r="F43">
+        <v>57.11300000000001</v>
+      </c>
+      <c r="G43">
+        <v>1.25</v>
+      </c>
+      <c r="H43">
+        <v>40.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K43">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L43">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M43">
+        <v>2.5529511</v>
+      </c>
+      <c r="N43">
+        <v>30.48038223333333</v>
+      </c>
+      <c r="O43">
+        <v>7.315291735999999</v>
+      </c>
+      <c r="P43">
+        <v>23.16509049733333</v>
+      </c>
+      <c r="Q43">
+        <v>28.96509049733333</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2304204574807667</v>
+      </c>
+      <c r="T43">
+        <v>0.8650959315930438</v>
+      </c>
+      <c r="U43">
+        <v>0.0447</v>
+      </c>
+      <c r="V43">
+        <v>0.24</v>
+      </c>
+      <c r="W43">
+        <v>0.033972</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>12.93927382053394</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1498784820789222</v>
+      </c>
+      <c r="C44">
+        <v>159.2613700121816</v>
+      </c>
+      <c r="D44">
+        <v>216.5173700121816</v>
+      </c>
+      <c r="E44">
+        <v>-39.89400000000001</v>
+      </c>
+      <c r="F44">
+        <v>58.506</v>
+      </c>
+      <c r="G44">
+        <v>1.25</v>
+      </c>
+      <c r="H44">
+        <v>40.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K44">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L44">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M44">
+        <v>2.6795748</v>
+      </c>
+      <c r="N44">
+        <v>30.35375853333333</v>
+      </c>
+      <c r="O44">
+        <v>7.284902047999999</v>
+      </c>
+      <c r="P44">
+        <v>23.06885648533333</v>
+      </c>
+      <c r="Q44">
+        <v>28.86885648533333</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2332053828946933</v>
+      </c>
+      <c r="T44">
+        <v>0.8776688461818727</v>
+      </c>
+      <c r="U44">
+        <v>0.0458</v>
+      </c>
+      <c r="V44">
+        <v>0.24</v>
+      </c>
+      <c r="W44">
+        <v>0.034808</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>12.32782653924545</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1495376142441919</v>
+      </c>
+      <c r="C45">
+        <v>158.5348446116324</v>
+      </c>
+      <c r="D45">
+        <v>217.1838446116324</v>
+      </c>
+      <c r="E45">
+        <v>-38.501</v>
+      </c>
+      <c r="F45">
+        <v>59.899</v>
+      </c>
+      <c r="G45">
+        <v>1.25</v>
+      </c>
+      <c r="H45">
+        <v>40.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K45">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L45">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M45">
+        <v>2.7433742</v>
+      </c>
+      <c r="N45">
+        <v>30.28995913333333</v>
+      </c>
+      <c r="O45">
+        <v>7.269590192</v>
+      </c>
+      <c r="P45">
+        <v>23.02036894133333</v>
+      </c>
+      <c r="Q45">
+        <v>28.82036894133334</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2360880249898104</v>
+      </c>
+      <c r="T45">
+        <v>0.8906829156685553</v>
+      </c>
+      <c r="U45">
+        <v>0.0458</v>
+      </c>
+      <c r="V45">
+        <v>0.24</v>
+      </c>
+      <c r="W45">
+        <v>0.034808</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>12.04113289879789</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1491967464094617</v>
+      </c>
+      <c r="C46">
+        <v>157.8124349076232</v>
+      </c>
+      <c r="D46">
+        <v>217.8544349076232</v>
+      </c>
+      <c r="E46">
+        <v>-37.108</v>
+      </c>
+      <c r="F46">
+        <v>61.29200000000001</v>
+      </c>
+      <c r="G46">
+        <v>1.25</v>
+      </c>
+      <c r="H46">
+        <v>40.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K46">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L46">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M46">
+        <v>2.8071736</v>
+      </c>
+      <c r="N46">
+        <v>30.22615973333333</v>
+      </c>
+      <c r="O46">
+        <v>7.254278336</v>
+      </c>
+      <c r="P46">
+        <v>22.97188139733333</v>
+      </c>
+      <c r="Q46">
+        <v>28.77188139733333</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2390736185883244</v>
+      </c>
+      <c r="T46">
+        <v>0.9041617733511907</v>
+      </c>
+      <c r="U46">
+        <v>0.0458</v>
+      </c>
+      <c r="V46">
+        <v>0.24</v>
+      </c>
+      <c r="W46">
+        <v>0.034808</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>11.76747078746157</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1488558785747315</v>
+      </c>
+      <c r="C47">
+        <v>157.0941791418707</v>
+      </c>
+      <c r="D47">
+        <v>218.5291791418707</v>
+      </c>
+      <c r="E47">
+        <v>-35.715</v>
+      </c>
+      <c r="F47">
+        <v>62.68500000000001</v>
+      </c>
+      <c r="G47">
+        <v>1.25</v>
+      </c>
+      <c r="H47">
+        <v>40.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K47">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L47">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M47">
+        <v>2.870973000000001</v>
+      </c>
+      <c r="N47">
+        <v>30.16236033333333</v>
+      </c>
+      <c r="O47">
+        <v>7.238966479999999</v>
+      </c>
+      <c r="P47">
+        <v>22.92339385333333</v>
+      </c>
+      <c r="Q47">
+        <v>28.72339385333333</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2421677792267845</v>
+      </c>
+      <c r="T47">
+        <v>0.918130771313195</v>
+      </c>
+      <c r="U47">
+        <v>0.0458</v>
+      </c>
+      <c r="V47">
+        <v>0.24</v>
+      </c>
+      <c r="W47">
+        <v>0.034808</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>11.50597143662909</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1485150107400013</v>
+      </c>
+      <c r="C48">
+        <v>156.3801160313359</v>
+      </c>
+      <c r="D48">
+        <v>219.2081160313359</v>
+      </c>
+      <c r="E48">
+        <v>-34.322</v>
+      </c>
+      <c r="F48">
+        <v>64.078</v>
+      </c>
+      <c r="G48">
+        <v>1.25</v>
+      </c>
+      <c r="H48">
+        <v>40.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K48">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L48">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M48">
+        <v>2.9347724</v>
+      </c>
+      <c r="N48">
+        <v>30.09856093333333</v>
+      </c>
+      <c r="O48">
+        <v>7.223654623999999</v>
+      </c>
+      <c r="P48">
+        <v>22.87490630933333</v>
+      </c>
+      <c r="Q48">
+        <v>28.67490630933333</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2453765384074097</v>
+      </c>
+      <c r="T48">
+        <v>0.9326171395700881</v>
+      </c>
+      <c r="U48">
+        <v>0.0458</v>
+      </c>
+      <c r="V48">
+        <v>0.24</v>
+      </c>
+      <c r="W48">
+        <v>0.034808</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>11.25584162278933</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.148174142905271</v>
+      </c>
+      <c r="C49">
+        <v>155.6702847756305</v>
+      </c>
+      <c r="D49">
+        <v>219.8912847756305</v>
+      </c>
+      <c r="E49">
+        <v>-32.929</v>
+      </c>
+      <c r="F49">
+        <v>65.471</v>
+      </c>
+      <c r="G49">
+        <v>1.25</v>
+      </c>
+      <c r="H49">
+        <v>40.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K49">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L49">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M49">
+        <v>2.9985718</v>
+      </c>
+      <c r="N49">
+        <v>30.03476153333333</v>
+      </c>
+      <c r="O49">
+        <v>7.208342767999999</v>
+      </c>
+      <c r="P49">
+        <v>22.82641876533333</v>
+      </c>
+      <c r="Q49">
+        <v>28.62641876533333</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.248706382840134</v>
+      </c>
+      <c r="T49">
+        <v>0.9476501632329016</v>
+      </c>
+      <c r="U49">
+        <v>0.0458</v>
+      </c>
+      <c r="V49">
+        <v>0.24</v>
+      </c>
+      <c r="W49">
+        <v>0.034808</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>11.01635563081509</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1478332750705408</v>
+      </c>
+      <c r="C50">
+        <v>154.964725064561</v>
+      </c>
+      <c r="D50">
+        <v>220.578725064561</v>
+      </c>
+      <c r="E50">
+        <v>-31.536</v>
+      </c>
+      <c r="F50">
+        <v>66.864</v>
+      </c>
+      <c r="G50">
+        <v>1.25</v>
+      </c>
+      <c r="H50">
+        <v>40.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K50">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L50">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M50">
+        <v>3.0623712</v>
+      </c>
+      <c r="N50">
+        <v>29.97096213333333</v>
+      </c>
+      <c r="O50">
+        <v>7.193030911999999</v>
+      </c>
+      <c r="P50">
+        <v>22.77793122133333</v>
+      </c>
+      <c r="Q50">
+        <v>28.57793122133333</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2521642982125785</v>
+      </c>
+      <c r="T50">
+        <v>0.9632613801135158</v>
+      </c>
+      <c r="U50">
+        <v>0.0458</v>
+      </c>
+      <c r="V50">
+        <v>0.24</v>
+      </c>
+      <c r="W50">
+        <v>0.034808</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>10.78684822183977</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1474924072358106</v>
+      </c>
+      <c r="C51">
+        <v>154.2634770858146</v>
+      </c>
+      <c r="D51">
+        <v>221.2704770858146</v>
+      </c>
+      <c r="E51">
+        <v>-30.143</v>
+      </c>
+      <c r="F51">
+        <v>68.25700000000001</v>
+      </c>
+      <c r="G51">
+        <v>1.25</v>
+      </c>
+      <c r="H51">
+        <v>40.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K51">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L51">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M51">
+        <v>3.1261706</v>
+      </c>
+      <c r="N51">
+        <v>29.90716273333333</v>
+      </c>
+      <c r="O51">
+        <v>7.177719055999999</v>
+      </c>
+      <c r="P51">
+        <v>22.72944367733333</v>
+      </c>
+      <c r="Q51">
+        <v>28.52944367733333</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2557578181094325</v>
+      </c>
+      <c r="T51">
+        <v>0.9794848015776834</v>
+      </c>
+      <c r="U51">
+        <v>0.0458</v>
+      </c>
+      <c r="V51">
+        <v>0.24</v>
+      </c>
+      <c r="W51">
+        <v>0.034808</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>10.56670846221039</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1471515394010804</v>
+      </c>
+      <c r="C52">
+        <v>153.5665815327923</v>
+      </c>
+      <c r="D52">
+        <v>221.9665815327923</v>
+      </c>
+      <c r="E52">
+        <v>-28.75</v>
+      </c>
+      <c r="F52">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="G52">
+        <v>1.25</v>
+      </c>
+      <c r="H52">
+        <v>40.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K52">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L52">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M52">
+        <v>3.18997</v>
+      </c>
+      <c r="N52">
+        <v>29.84336333333333</v>
+      </c>
+      <c r="O52">
+        <v>7.1624072</v>
+      </c>
+      <c r="P52">
+        <v>22.68095613333333</v>
+      </c>
+      <c r="Q52">
+        <v>28.48095613333333</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2594950788021608</v>
+      </c>
+      <c r="T52">
+        <v>0.9963571599004178</v>
+      </c>
+      <c r="U52">
+        <v>0.0458</v>
+      </c>
+      <c r="V52">
+        <v>0.24</v>
+      </c>
+      <c r="W52">
+        <v>0.034808</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>10.35537429296618</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1468106715663502</v>
+      </c>
+      <c r="C53">
+        <v>152.8740796125868</v>
+      </c>
+      <c r="D53">
+        <v>222.6670796125868</v>
+      </c>
+      <c r="E53">
+        <v>-27.357</v>
+      </c>
+      <c r="F53">
+        <v>71.04300000000001</v>
+      </c>
+      <c r="G53">
+        <v>1.25</v>
+      </c>
+      <c r="H53">
+        <v>40.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K53">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L53">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M53">
+        <v>3.2537694</v>
+      </c>
+      <c r="N53">
+        <v>29.77956393333333</v>
+      </c>
+      <c r="O53">
+        <v>7.147095343999999</v>
+      </c>
+      <c r="P53">
+        <v>22.63246858933333</v>
+      </c>
+      <c r="Q53">
+        <v>28.43246858933333</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2633848807476534</v>
+      </c>
+      <c r="T53">
+        <v>1.013918185909795</v>
+      </c>
+      <c r="U53">
+        <v>0.0458</v>
+      </c>
+      <c r="V53">
+        <v>0.24</v>
+      </c>
+      <c r="W53">
+        <v>0.034808</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>10.15232773820214</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1464698037316199</v>
+      </c>
+      <c r="C54">
+        <v>152.1860130541155</v>
+      </c>
+      <c r="D54">
+        <v>223.3720130541155</v>
+      </c>
+      <c r="E54">
+        <v>-25.964</v>
+      </c>
+      <c r="F54">
+        <v>72.43600000000001</v>
+      </c>
+      <c r="G54">
+        <v>1.25</v>
+      </c>
+      <c r="H54">
+        <v>40.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K54">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L54">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M54">
+        <v>3.317568800000001</v>
+      </c>
+      <c r="N54">
+        <v>29.71576453333333</v>
+      </c>
+      <c r="O54">
+        <v>7.131783487999999</v>
+      </c>
+      <c r="P54">
+        <v>22.58398104533333</v>
+      </c>
+      <c r="Q54">
+        <v>28.38398104533333</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2674367577742082</v>
+      </c>
+      <c r="T54">
+        <v>1.032210921336228</v>
+      </c>
+      <c r="U54">
+        <v>0.0458</v>
+      </c>
+      <c r="V54">
+        <v>0.24</v>
+      </c>
+      <c r="W54">
+        <v>0.034808</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>9.957090666313634</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1470150958968897</v>
+      </c>
+      <c r="C55">
+        <v>149.6674491237836</v>
+      </c>
+      <c r="D55">
+        <v>222.2464491237836</v>
+      </c>
+      <c r="E55">
+        <v>-24.571</v>
+      </c>
+      <c r="F55">
+        <v>73.82900000000001</v>
+      </c>
+      <c r="G55">
+        <v>1.25</v>
+      </c>
+      <c r="H55">
+        <v>40.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K55">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L55">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M55">
+        <v>3.543792</v>
+      </c>
+      <c r="N55">
+        <v>29.48954133333333</v>
+      </c>
+      <c r="O55">
+        <v>7.07748992</v>
+      </c>
+      <c r="P55">
+        <v>22.41205141333333</v>
+      </c>
+      <c r="Q55">
+        <v>28.21205141333333</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2716610550997653</v>
+      </c>
+      <c r="T55">
+        <v>1.051282071036127</v>
+      </c>
+      <c r="U55">
+        <v>0.048</v>
+      </c>
+      <c r="V55">
+        <v>0.24</v>
+      </c>
+      <c r="W55">
+        <v>0.03648</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>9.321465067174746</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1466909480621595</v>
+      </c>
+      <c r="C56">
+        <v>148.9421669124756</v>
+      </c>
+      <c r="D56">
+        <v>222.9141669124757</v>
+      </c>
+      <c r="E56">
+        <v>-23.178</v>
+      </c>
+      <c r="F56">
+        <v>75.22200000000001</v>
+      </c>
+      <c r="G56">
+        <v>1.25</v>
+      </c>
+      <c r="H56">
+        <v>40.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K56">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L56">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M56">
+        <v>3.610656000000001</v>
+      </c>
+      <c r="N56">
+        <v>29.42267733333333</v>
+      </c>
+      <c r="O56">
+        <v>7.06144256</v>
+      </c>
+      <c r="P56">
+        <v>22.36123477333333</v>
+      </c>
+      <c r="Q56">
+        <v>28.16123477333333</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2760690175264338</v>
+      </c>
+      <c r="T56">
+        <v>1.071182401157762</v>
+      </c>
+      <c r="U56">
+        <v>0.048</v>
+      </c>
+      <c r="V56">
+        <v>0.24</v>
+      </c>
+      <c r="W56">
+        <v>0.03648</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>9.148845343708548</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1463668002274293</v>
+      </c>
+      <c r="C57">
+        <v>148.2209089777095</v>
+      </c>
+      <c r="D57">
+        <v>223.5859089777096</v>
+      </c>
+      <c r="E57">
+        <v>-21.785</v>
+      </c>
+      <c r="F57">
+        <v>76.61500000000001</v>
+      </c>
+      <c r="G57">
+        <v>1.25</v>
+      </c>
+      <c r="H57">
+        <v>40.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K57">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L57">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M57">
+        <v>3.67752</v>
+      </c>
+      <c r="N57">
+        <v>29.35581333333333</v>
+      </c>
+      <c r="O57">
+        <v>7.045395199999999</v>
+      </c>
+      <c r="P57">
+        <v>22.31041813333333</v>
+      </c>
+      <c r="Q57">
+        <v>28.11041813333333</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2806728893942873</v>
+      </c>
+      <c r="T57">
+        <v>1.091967190395913</v>
+      </c>
+      <c r="U57">
+        <v>0.048</v>
+      </c>
+      <c r="V57">
+        <v>0.24</v>
+      </c>
+      <c r="W57">
+        <v>0.03648</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>8.982502701095665</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1460426523926991</v>
+      </c>
+      <c r="C58">
+        <v>147.5037118103915</v>
+      </c>
+      <c r="D58">
+        <v>224.2617118103915</v>
+      </c>
+      <c r="E58">
+        <v>-20.392</v>
+      </c>
+      <c r="F58">
+        <v>78.00800000000001</v>
+      </c>
+      <c r="G58">
+        <v>1.25</v>
+      </c>
+      <c r="H58">
+        <v>40.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K58">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L58">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M58">
+        <v>3.744384000000001</v>
+      </c>
+      <c r="N58">
+        <v>29.28894933333333</v>
+      </c>
+      <c r="O58">
+        <v>7.029347839999999</v>
+      </c>
+      <c r="P58">
+        <v>22.25960149333333</v>
+      </c>
+      <c r="Q58">
+        <v>28.05960149333333</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2854860281652252</v>
+      </c>
+      <c r="T58">
+        <v>1.113696742781252</v>
+      </c>
+      <c r="U58">
+        <v>0.048</v>
+      </c>
+      <c r="V58">
+        <v>0.24</v>
+      </c>
+      <c r="W58">
+        <v>0.03648</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>8.822100867147526</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1457185045579688</v>
+      </c>
+      <c r="C59">
+        <v>146.7906123439499</v>
+      </c>
+      <c r="D59">
+        <v>224.9416123439499</v>
+      </c>
+      <c r="E59">
+        <v>-18.999</v>
+      </c>
+      <c r="F59">
+        <v>79.40100000000001</v>
+      </c>
+      <c r="G59">
+        <v>1.25</v>
+      </c>
+      <c r="H59">
+        <v>40.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K59">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L59">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M59">
+        <v>3.811248</v>
+      </c>
+      <c r="N59">
+        <v>29.22208533333333</v>
+      </c>
+      <c r="O59">
+        <v>7.01330048</v>
+      </c>
+      <c r="P59">
+        <v>22.20878485333333</v>
+      </c>
+      <c r="Q59">
+        <v>28.00878485333334</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2905230338557415</v>
+      </c>
+      <c r="T59">
+        <v>1.136436972021724</v>
+      </c>
+      <c r="U59">
+        <v>0.048</v>
+      </c>
+      <c r="V59">
+        <v>0.24</v>
+      </c>
+      <c r="W59">
+        <v>0.03648</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>8.667327167723887</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1453943567232386</v>
+      </c>
+      <c r="C60">
+        <v>146.0816479610635</v>
+      </c>
+      <c r="D60">
+        <v>225.6256479610635</v>
+      </c>
+      <c r="E60">
+        <v>-17.60600000000001</v>
+      </c>
+      <c r="F60">
+        <v>80.794</v>
+      </c>
+      <c r="G60">
+        <v>1.25</v>
+      </c>
+      <c r="H60">
+        <v>40.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K60">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L60">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M60">
+        <v>3.878112</v>
+      </c>
+      <c r="N60">
+        <v>29.15522133333333</v>
+      </c>
+      <c r="O60">
+        <v>6.997253119999999</v>
+      </c>
+      <c r="P60">
+        <v>22.15796821333333</v>
+      </c>
+      <c r="Q60">
+        <v>27.95796821333333</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.295799896960092</v>
+      </c>
+      <c r="T60">
+        <v>1.160260069321266</v>
+      </c>
+      <c r="U60">
+        <v>0.048</v>
+      </c>
+      <c r="V60">
+        <v>0.24</v>
+      </c>
+      <c r="W60">
+        <v>0.03648</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>8.517890492418303</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1450702088885084</v>
+      </c>
+      <c r="C61">
+        <v>145.3768565005133</v>
+      </c>
+      <c r="D61">
+        <v>226.3138565005133</v>
+      </c>
+      <c r="E61">
+        <v>-16.21300000000001</v>
+      </c>
+      <c r="F61">
+        <v>82.187</v>
+      </c>
+      <c r="G61">
+        <v>1.25</v>
+      </c>
+      <c r="H61">
+        <v>40.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K61">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L61">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M61">
+        <v>3.944976</v>
+      </c>
+      <c r="N61">
+        <v>29.08835733333333</v>
+      </c>
+      <c r="O61">
+        <v>6.981205759999999</v>
+      </c>
+      <c r="P61">
+        <v>22.10715157333333</v>
+      </c>
+      <c r="Q61">
+        <v>27.90715157333333</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3013341680207522</v>
+      </c>
+      <c r="T61">
+        <v>1.185245268928102</v>
+      </c>
+      <c r="U61">
+        <v>0.048</v>
+      </c>
+      <c r="V61">
+        <v>0.24</v>
+      </c>
+      <c r="W61">
+        <v>0.03648</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>8.373519467123078</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1447460610537782</v>
+      </c>
+      <c r="C62">
+        <v>144.6762762641594</v>
+      </c>
+      <c r="D62">
+        <v>227.0062762641594</v>
+      </c>
+      <c r="E62">
+        <v>-14.82000000000001</v>
+      </c>
+      <c r="F62">
+        <v>83.58</v>
+      </c>
+      <c r="G62">
+        <v>1.25</v>
+      </c>
+      <c r="H62">
+        <v>40.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K62">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L62">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M62">
+        <v>4.01184</v>
+      </c>
+      <c r="N62">
+        <v>29.02149333333333</v>
+      </c>
+      <c r="O62">
+        <v>6.965158399999999</v>
+      </c>
+      <c r="P62">
+        <v>22.05633493333333</v>
+      </c>
+      <c r="Q62">
+        <v>27.85633493333333</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3071451526344454</v>
+      </c>
+      <c r="T62">
+        <v>1.211479728515281</v>
+      </c>
+      <c r="U62">
+        <v>0.048</v>
+      </c>
+      <c r="V62">
+        <v>0.24</v>
+      </c>
+      <c r="W62">
+        <v>0.03648</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>8.233960809337692</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.144421913219048</v>
+      </c>
+      <c r="C63">
+        <v>143.979946024047</v>
+      </c>
+      <c r="D63">
+        <v>227.702946024047</v>
+      </c>
+      <c r="E63">
+        <v>-13.42700000000001</v>
+      </c>
+      <c r="F63">
+        <v>84.973</v>
+      </c>
+      <c r="G63">
+        <v>1.25</v>
+      </c>
+      <c r="H63">
+        <v>40.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K63">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L63">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M63">
+        <v>4.078704</v>
+      </c>
+      <c r="N63">
+        <v>28.95462933333333</v>
+      </c>
+      <c r="O63">
+        <v>6.949111039999999</v>
+      </c>
+      <c r="P63">
+        <v>22.00551829333333</v>
+      </c>
+      <c r="Q63">
+        <v>27.80551829333333</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3132541364590974</v>
+      </c>
+      <c r="T63">
+        <v>1.239059545004366</v>
+      </c>
+      <c r="U63">
+        <v>0.048</v>
+      </c>
+      <c r="V63">
+        <v>0.24</v>
+      </c>
+      <c r="W63">
+        <v>0.03648</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>8.098977845250189</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1440977653843178</v>
+      </c>
+      <c r="C64">
+        <v>143.2879050296442</v>
+      </c>
+      <c r="D64">
+        <v>228.4039050296441</v>
+      </c>
+      <c r="E64">
+        <v>-12.03400000000001</v>
+      </c>
+      <c r="F64">
+        <v>86.366</v>
+      </c>
+      <c r="G64">
+        <v>1.25</v>
+      </c>
+      <c r="H64">
+        <v>40.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K64">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L64">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M64">
+        <v>4.145568</v>
+      </c>
+      <c r="N64">
+        <v>28.88776533333333</v>
+      </c>
+      <c r="O64">
+        <v>6.933063679999999</v>
+      </c>
+      <c r="P64">
+        <v>21.95470165333333</v>
+      </c>
+      <c r="Q64">
+        <v>27.75470165333333</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3196846457482047</v>
+      </c>
+      <c r="T64">
+        <v>1.26809093078235</v>
+      </c>
+      <c r="U64">
+        <v>0.048</v>
+      </c>
+      <c r="V64">
+        <v>0.24</v>
+      </c>
+      <c r="W64">
+        <v>0.03648</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>7.9683491703268</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1437736175495875</v>
+      </c>
+      <c r="C65">
+        <v>142.6001930152117</v>
+      </c>
+      <c r="D65">
+        <v>229.1091930152118</v>
+      </c>
+      <c r="E65">
+        <v>-10.64099999999999</v>
+      </c>
+      <c r="F65">
+        <v>87.75900000000001</v>
+      </c>
+      <c r="G65">
+        <v>1.25</v>
+      </c>
+      <c r="H65">
+        <v>40.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K65">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L65">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M65">
+        <v>4.212432000000001</v>
+      </c>
+      <c r="N65">
+        <v>28.82090133333333</v>
+      </c>
+      <c r="O65">
+        <v>6.917016319999999</v>
+      </c>
+      <c r="P65">
+        <v>21.90388501333333</v>
+      </c>
+      <c r="Q65">
+        <v>27.70388501333333</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3264627501340203</v>
+      </c>
+      <c r="T65">
+        <v>1.298691580656441</v>
+      </c>
+      <c r="U65">
+        <v>0.048</v>
+      </c>
+      <c r="V65">
+        <v>0.24</v>
+      </c>
+      <c r="W65">
+        <v>0.03648</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>7.841867437464469</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1441790697148573</v>
+      </c>
+      <c r="C66">
+        <v>140.3256819272643</v>
+      </c>
+      <c r="D66">
+        <v>228.2276819272643</v>
+      </c>
+      <c r="E66">
+        <v>-9.24799999999999</v>
+      </c>
+      <c r="F66">
+        <v>89.15200000000002</v>
+      </c>
+      <c r="G66">
+        <v>1.25</v>
+      </c>
+      <c r="H66">
+        <v>40.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K66">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L66">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M66">
+        <v>4.413024000000001</v>
+      </c>
+      <c r="N66">
+        <v>28.62030933333333</v>
+      </c>
+      <c r="O66">
+        <v>6.868874239999999</v>
+      </c>
+      <c r="P66">
+        <v>21.75143509333333</v>
+      </c>
+      <c r="Q66">
+        <v>27.55143509333333</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3336174158746036</v>
+      </c>
+      <c r="T66">
+        <v>1.330992266634649</v>
+      </c>
+      <c r="U66">
+        <v>0.0495</v>
+      </c>
+      <c r="V66">
+        <v>0.24</v>
+      </c>
+      <c r="W66">
+        <v>0.03762</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>7.48541891757972</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1438663218801271</v>
+      </c>
+      <c r="C67">
+        <v>139.6120405654175</v>
+      </c>
+      <c r="D67">
+        <v>228.9070405654175</v>
+      </c>
+      <c r="E67">
+        <v>-7.85499999999999</v>
+      </c>
+      <c r="F67">
+        <v>90.54500000000002</v>
+      </c>
+      <c r="G67">
+        <v>1.25</v>
+      </c>
+      <c r="H67">
+        <v>40.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K67">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L67">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M67">
+        <v>4.481977500000001</v>
+      </c>
+      <c r="N67">
+        <v>28.55135583333333</v>
+      </c>
+      <c r="O67">
+        <v>6.8523254</v>
+      </c>
+      <c r="P67">
+        <v>21.69903043333333</v>
+      </c>
+      <c r="Q67">
+        <v>27.49903043333333</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.341180919657506</v>
+      </c>
+      <c r="T67">
+        <v>1.365138706097326</v>
+      </c>
+      <c r="U67">
+        <v>0.0495</v>
+      </c>
+      <c r="V67">
+        <v>0.24</v>
+      </c>
+      <c r="W67">
+        <v>0.03762</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>7.370258626540032</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1435535740453969</v>
+      </c>
+      <c r="C68">
+        <v>138.902455732334</v>
+      </c>
+      <c r="D68">
+        <v>229.590455732334</v>
+      </c>
+      <c r="E68">
+        <v>-6.461999999999989</v>
+      </c>
+      <c r="F68">
+        <v>91.93800000000002</v>
+      </c>
+      <c r="G68">
+        <v>1.25</v>
+      </c>
+      <c r="H68">
+        <v>40.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K68">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L68">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M68">
+        <v>4.550931000000001</v>
+      </c>
+      <c r="N68">
+        <v>28.48240233333333</v>
+      </c>
+      <c r="O68">
+        <v>6.835776559999998</v>
+      </c>
+      <c r="P68">
+        <v>21.64662577333333</v>
+      </c>
+      <c r="Q68">
+        <v>27.44662577333333</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3491893354276379</v>
+      </c>
+      <c r="T68">
+        <v>1.401293759646042</v>
+      </c>
+      <c r="U68">
+        <v>0.0495</v>
+      </c>
+      <c r="V68">
+        <v>0.24</v>
+      </c>
+      <c r="W68">
+        <v>0.03762</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>7.258588041289425</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1432408262106667</v>
+      </c>
+      <c r="C69">
+        <v>138.1969638698144</v>
+      </c>
+      <c r="D69">
+        <v>230.2779638698144</v>
+      </c>
+      <c r="E69">
+        <v>-5.068999999999988</v>
+      </c>
+      <c r="F69">
+        <v>93.33100000000002</v>
+      </c>
+      <c r="G69">
+        <v>1.25</v>
+      </c>
+      <c r="H69">
+        <v>40.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K69">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L69">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M69">
+        <v>4.619884500000001</v>
+      </c>
+      <c r="N69">
+        <v>28.41344883333333</v>
+      </c>
+      <c r="O69">
+        <v>6.819227719999999</v>
+      </c>
+      <c r="P69">
+        <v>21.59422111333333</v>
+      </c>
+      <c r="Q69">
+        <v>27.39422111333333</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.357683109729293</v>
+      </c>
+      <c r="T69">
+        <v>1.439640028561348</v>
+      </c>
+      <c r="U69">
+        <v>0.0495</v>
+      </c>
+      <c r="V69">
+        <v>0.24</v>
+      </c>
+      <c r="W69">
+        <v>0.03762</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>7.150250906344806</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1429280783759364</v>
+      </c>
+      <c r="C70">
+        <v>137.49560185747</v>
+      </c>
+      <c r="D70">
+        <v>230.96960185747</v>
+      </c>
+      <c r="E70">
+        <v>-3.675999999999988</v>
+      </c>
+      <c r="F70">
+        <v>94.72400000000002</v>
+      </c>
+      <c r="G70">
+        <v>1.25</v>
+      </c>
+      <c r="H70">
+        <v>40.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K70">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L70">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M70">
+        <v>4.688838000000001</v>
+      </c>
+      <c r="N70">
+        <v>28.34449533333333</v>
+      </c>
+      <c r="O70">
+        <v>6.802678879999999</v>
+      </c>
+      <c r="P70">
+        <v>21.54181645333333</v>
+      </c>
+      <c r="Q70">
+        <v>27.34181645333333</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3667077449248013</v>
+      </c>
+      <c r="T70">
+        <v>1.480382939283859</v>
+      </c>
+      <c r="U70">
+        <v>0.0495</v>
+      </c>
+      <c r="V70">
+        <v>0.24</v>
+      </c>
+      <c r="W70">
+        <v>0.03762</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>7.045100157722088</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1426153305412062</v>
+      </c>
+      <c r="C71">
+        <v>136.7984070193169</v>
+      </c>
+      <c r="D71">
+        <v>231.6654070193169</v>
+      </c>
+      <c r="E71">
+        <v>-2.282999999999987</v>
+      </c>
+      <c r="F71">
+        <v>96.11700000000002</v>
+      </c>
+      <c r="G71">
+        <v>1.25</v>
+      </c>
+      <c r="H71">
+        <v>40.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K71">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L71">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M71">
+        <v>4.757791500000002</v>
+      </c>
+      <c r="N71">
+        <v>28.27554183333333</v>
+      </c>
+      <c r="O71">
+        <v>6.786130039999999</v>
+      </c>
+      <c r="P71">
+        <v>21.48941179333333</v>
+      </c>
+      <c r="Q71">
+        <v>27.28941179333333</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3763146146490524</v>
+      </c>
+      <c r="T71">
+        <v>1.523754424891695</v>
+      </c>
+      <c r="U71">
+        <v>0.0495</v>
+      </c>
+      <c r="V71">
+        <v>0.24</v>
+      </c>
+      <c r="W71">
+        <v>0.03762</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>6.942997256885536</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.142302582706476</v>
+      </c>
+      <c r="C72">
+        <v>136.1054171304912</v>
+      </c>
+      <c r="D72">
+        <v>232.3654171304913</v>
+      </c>
+      <c r="E72">
+        <v>-0.8899999999999864</v>
+      </c>
+      <c r="F72">
+        <v>97.51000000000002</v>
+      </c>
+      <c r="G72">
+        <v>1.25</v>
+      </c>
+      <c r="H72">
+        <v>40.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K72">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L72">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M72">
+        <v>4.826745000000002</v>
+      </c>
+      <c r="N72">
+        <v>28.20658833333333</v>
+      </c>
+      <c r="O72">
+        <v>6.769581199999998</v>
+      </c>
+      <c r="P72">
+        <v>21.43700713333333</v>
+      </c>
+      <c r="Q72">
+        <v>27.23700713333333</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.38656194235492</v>
+      </c>
+      <c r="T72">
+        <v>1.570017342873386</v>
+      </c>
+      <c r="U72">
+        <v>0.0495</v>
+      </c>
+      <c r="V72">
+        <v>0.24</v>
+      </c>
+      <c r="W72">
+        <v>0.03762</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>6.843811581787171</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1419898348717458</v>
+      </c>
+      <c r="C73">
+        <v>135.4166704240842</v>
+      </c>
+      <c r="D73">
+        <v>233.0696704240842</v>
+      </c>
+      <c r="E73">
+        <v>0.5030000000000001</v>
+      </c>
+      <c r="F73">
+        <v>98.90300000000001</v>
+      </c>
+      <c r="G73">
+        <v>1.25</v>
+      </c>
+      <c r="H73">
+        <v>40.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K73">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L73">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M73">
+        <v>4.895698500000001</v>
+      </c>
+      <c r="N73">
+        <v>28.13763483333333</v>
+      </c>
+      <c r="O73">
+        <v>6.753032359999999</v>
+      </c>
+      <c r="P73">
+        <v>21.38460247333333</v>
+      </c>
+      <c r="Q73">
+        <v>27.18460247333333</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3975159823163648</v>
+      </c>
+      <c r="T73">
+        <v>1.619470806922779</v>
+      </c>
+      <c r="U73">
+        <v>0.0495</v>
+      </c>
+      <c r="V73">
+        <v>0.24</v>
+      </c>
+      <c r="W73">
+        <v>0.03762</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>6.747419869367635</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1416770870370156</v>
+      </c>
+      <c r="C74">
+        <v>134.732205598104</v>
+      </c>
+      <c r="D74">
+        <v>233.778205598104</v>
+      </c>
+      <c r="E74">
+        <v>1.896000000000001</v>
+      </c>
+      <c r="F74">
+        <v>100.296</v>
+      </c>
+      <c r="G74">
+        <v>1.25</v>
+      </c>
+      <c r="H74">
+        <v>40.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K74">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L74">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M74">
+        <v>4.964652000000001</v>
+      </c>
+      <c r="N74">
+        <v>28.06868133333333</v>
+      </c>
+      <c r="O74">
+        <v>6.736483519999999</v>
+      </c>
+      <c r="P74">
+        <v>21.33219781333333</v>
+      </c>
+      <c r="Q74">
+        <v>27.13219781333333</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.409252453703627</v>
+      </c>
+      <c r="T74">
+        <v>1.672456661261416</v>
+      </c>
+      <c r="U74">
+        <v>0.0495</v>
+      </c>
+      <c r="V74">
+        <v>0.24</v>
+      </c>
+      <c r="W74">
+        <v>0.03762</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>6.653705704515306</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1413643392022853</v>
+      </c>
+      <c r="C75">
+        <v>134.0520618225635</v>
+      </c>
+      <c r="D75">
+        <v>234.4910618225635</v>
+      </c>
+      <c r="E75">
+        <v>3.289000000000001</v>
+      </c>
+      <c r="F75">
+        <v>101.689</v>
+      </c>
+      <c r="G75">
+        <v>1.25</v>
+      </c>
+      <c r="H75">
+        <v>40.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K75">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L75">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M75">
+        <v>5.0336055</v>
+      </c>
+      <c r="N75">
+        <v>27.99972783333333</v>
+      </c>
+      <c r="O75">
+        <v>6.719934679999999</v>
+      </c>
+      <c r="P75">
+        <v>21.27979315333333</v>
+      </c>
+      <c r="Q75">
+        <v>27.07979315333333</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4218582933417975</v>
+      </c>
+      <c r="T75">
+        <v>1.72936739369921</v>
+      </c>
+      <c r="U75">
+        <v>0.0495</v>
+      </c>
+      <c r="V75">
+        <v>0.24</v>
+      </c>
+      <c r="W75">
+        <v>0.03762</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>6.562559051028797</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1410515913675551</v>
+      </c>
+      <c r="C76">
+        <v>133.376278746699</v>
+      </c>
+      <c r="D76">
+        <v>235.2082787466991</v>
+      </c>
+      <c r="E76">
+        <v>4.682000000000002</v>
+      </c>
+      <c r="F76">
+        <v>103.082</v>
+      </c>
+      <c r="G76">
+        <v>1.25</v>
+      </c>
+      <c r="H76">
+        <v>40.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K76">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L76">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M76">
+        <v>5.102559</v>
+      </c>
+      <c r="N76">
+        <v>27.93077433333333</v>
+      </c>
+      <c r="O76">
+        <v>6.703385839999999</v>
+      </c>
+      <c r="P76">
+        <v>21.22738849333333</v>
+      </c>
+      <c r="Q76">
+        <v>27.02738849333333</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.435433812952135</v>
+      </c>
+      <c r="T76">
+        <v>1.790655874786065</v>
+      </c>
+      <c r="U76">
+        <v>0.0495</v>
+      </c>
+      <c r="V76">
+        <v>0.24</v>
+      </c>
+      <c r="W76">
+        <v>0.03762</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>6.473875820609488</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1407388435328249</v>
+      </c>
+      <c r="C77">
+        <v>132.7048965063213</v>
+      </c>
+      <c r="D77">
+        <v>235.9298965063214</v>
+      </c>
+      <c r="E77">
+        <v>6.075000000000003</v>
+      </c>
+      <c r="F77">
+        <v>104.475</v>
+      </c>
+      <c r="G77">
+        <v>1.25</v>
+      </c>
+      <c r="H77">
+        <v>40.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K77">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L77">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M77">
+        <v>5.1715125</v>
+      </c>
+      <c r="N77">
+        <v>27.86182083333333</v>
+      </c>
+      <c r="O77">
+        <v>6.686837</v>
+      </c>
+      <c r="P77">
+        <v>21.17498383333333</v>
+      </c>
+      <c r="Q77">
+        <v>26.97498383333333</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.4500953741312996</v>
+      </c>
+      <c r="T77">
+        <v>1.85684743435987</v>
+      </c>
+      <c r="U77">
+        <v>0.0495</v>
+      </c>
+      <c r="V77">
+        <v>0.24</v>
+      </c>
+      <c r="W77">
+        <v>0.03762</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>6.387557476334695</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1404260956980947</v>
+      </c>
+      <c r="C78">
+        <v>132.037955731303</v>
+      </c>
+      <c r="D78">
+        <v>236.6559557313031</v>
+      </c>
+      <c r="E78">
+        <v>7.468000000000004</v>
+      </c>
+      <c r="F78">
+        <v>105.868</v>
+      </c>
+      <c r="G78">
+        <v>1.25</v>
+      </c>
+      <c r="H78">
+        <v>40.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K78">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L78">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M78">
+        <v>5.240466000000001</v>
+      </c>
+      <c r="N78">
+        <v>27.79286733333333</v>
+      </c>
+      <c r="O78">
+        <v>6.670288159999999</v>
+      </c>
+      <c r="P78">
+        <v>21.12257917333333</v>
+      </c>
+      <c r="Q78">
+        <v>26.92257917333333</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.4659787320753945</v>
+      </c>
+      <c r="T78">
+        <v>1.928554957231491</v>
+      </c>
+      <c r="U78">
+        <v>0.0495</v>
+      </c>
+      <c r="V78">
+        <v>0.24</v>
+      </c>
+      <c r="W78">
+        <v>0.03762</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>6.303510667435554</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1401133478633645</v>
+      </c>
+      <c r="C79">
+        <v>131.375497553204</v>
+      </c>
+      <c r="D79">
+        <v>237.386497553204</v>
+      </c>
+      <c r="E79">
+        <v>8.861000000000004</v>
+      </c>
+      <c r="F79">
+        <v>107.261</v>
+      </c>
+      <c r="G79">
+        <v>1.25</v>
+      </c>
+      <c r="H79">
+        <v>40.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K79">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L79">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M79">
+        <v>5.309419500000001</v>
+      </c>
+      <c r="N79">
+        <v>27.72391383333333</v>
+      </c>
+      <c r="O79">
+        <v>6.653739319999999</v>
+      </c>
+      <c r="P79">
+        <v>21.07017451333333</v>
+      </c>
+      <c r="Q79">
+        <v>26.87017451333333</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.4832432515798455</v>
+      </c>
+      <c r="T79">
+        <v>2.006497916874557</v>
+      </c>
+      <c r="U79">
+        <v>0.0495</v>
+      </c>
+      <c r="V79">
+        <v>0.24</v>
+      </c>
+      <c r="W79">
+        <v>0.03762</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>6.221646892533793</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1406305200286342</v>
+      </c>
+      <c r="C80">
+        <v>128.7768699190636</v>
+      </c>
+      <c r="D80">
+        <v>236.1808699190637</v>
+      </c>
+      <c r="E80">
+        <v>10.254</v>
+      </c>
+      <c r="F80">
+        <v>108.654</v>
+      </c>
+      <c r="G80">
+        <v>1.25</v>
+      </c>
+      <c r="H80">
+        <v>40.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K80">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L80">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M80">
+        <v>5.530488600000001</v>
+      </c>
+      <c r="N80">
+        <v>27.50284473333333</v>
+      </c>
+      <c r="O80">
+        <v>6.600682735999999</v>
+      </c>
+      <c r="P80">
+        <v>20.90216199733333</v>
+      </c>
+      <c r="Q80">
+        <v>26.70216199733333</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.5020772728574283</v>
+      </c>
+      <c r="T80">
+        <v>2.091526600121538</v>
+      </c>
+      <c r="U80">
+        <v>0.0509</v>
+      </c>
+      <c r="V80">
+        <v>0.24</v>
+      </c>
+      <c r="W80">
+        <v>0.038684</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.972950262176352</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.140328412193904</v>
+      </c>
+      <c r="C81">
+        <v>128.0866494629776</v>
+      </c>
+      <c r="D81">
+        <v>236.8836494629776</v>
+      </c>
+      <c r="E81">
+        <v>11.64700000000001</v>
+      </c>
+      <c r="F81">
+        <v>110.047</v>
+      </c>
+      <c r="G81">
+        <v>1.25</v>
+      </c>
+      <c r="H81">
+        <v>40.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K81">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L81">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M81">
+        <v>5.601392300000001</v>
+      </c>
+      <c r="N81">
+        <v>27.43194103333333</v>
+      </c>
+      <c r="O81">
+        <v>6.583665847999999</v>
+      </c>
+      <c r="P81">
+        <v>20.84827518533333</v>
+      </c>
+      <c r="Q81">
+        <v>26.64827518533333</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5227050104471621</v>
+      </c>
+      <c r="T81">
+        <v>2.184653253201566</v>
+      </c>
+      <c r="U81">
+        <v>0.0509</v>
+      </c>
+      <c r="V81">
+        <v>0.24</v>
+      </c>
+      <c r="W81">
+        <v>0.038684</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.897343296832348</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1400263043591738</v>
+      </c>
+      <c r="C82">
+        <v>127.4006238692379</v>
+      </c>
+      <c r="D82">
+        <v>237.5906238692379</v>
+      </c>
+      <c r="E82">
+        <v>13.04000000000001</v>
+      </c>
+      <c r="F82">
+        <v>111.44</v>
+      </c>
+      <c r="G82">
+        <v>1.25</v>
+      </c>
+      <c r="H82">
+        <v>40.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K82">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L82">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M82">
+        <v>5.672296000000001</v>
+      </c>
+      <c r="N82">
+        <v>27.36103733333333</v>
+      </c>
+      <c r="O82">
+        <v>6.566648959999998</v>
+      </c>
+      <c r="P82">
+        <v>20.79438837333333</v>
+      </c>
+      <c r="Q82">
+        <v>26.59438837333333</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.5453955217958693</v>
+      </c>
+      <c r="T82">
+        <v>2.287092571589596</v>
+      </c>
+      <c r="U82">
+        <v>0.0509</v>
+      </c>
+      <c r="V82">
+        <v>0.24</v>
+      </c>
+      <c r="W82">
+        <v>0.038684</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.823626505621943</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1397241965244436</v>
+      </c>
+      <c r="C83">
+        <v>126.718830808715</v>
+      </c>
+      <c r="D83">
+        <v>238.301830808715</v>
+      </c>
+      <c r="E83">
+        <v>14.43300000000001</v>
+      </c>
+      <c r="F83">
+        <v>112.833</v>
+      </c>
+      <c r="G83">
+        <v>1.25</v>
+      </c>
+      <c r="H83">
+        <v>40.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K83">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L83">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M83">
+        <v>5.743199700000001</v>
+      </c>
+      <c r="N83">
+        <v>27.29013363333333</v>
+      </c>
+      <c r="O83">
+        <v>6.549632071999999</v>
+      </c>
+      <c r="P83">
+        <v>20.74050156133333</v>
+      </c>
+      <c r="Q83">
+        <v>26.54050156133333</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.5704745080233875</v>
+      </c>
+      <c r="T83">
+        <v>2.400314976123735</v>
+      </c>
+      <c r="U83">
+        <v>0.0509</v>
+      </c>
+      <c r="V83">
+        <v>0.24</v>
+      </c>
+      <c r="W83">
+        <v>0.038684</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.751729882095747</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1394220886897134</v>
+      </c>
+      <c r="C84">
+        <v>126.0413084046917</v>
+      </c>
+      <c r="D84">
+        <v>239.0173084046917</v>
+      </c>
+      <c r="E84">
+        <v>15.82600000000001</v>
+      </c>
+      <c r="F84">
+        <v>114.226</v>
+      </c>
+      <c r="G84">
+        <v>1.25</v>
+      </c>
+      <c r="H84">
+        <v>40.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K84">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L84">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M84">
+        <v>5.8141034</v>
+      </c>
+      <c r="N84">
+        <v>27.21922993333333</v>
+      </c>
+      <c r="O84">
+        <v>6.532615183999999</v>
+      </c>
+      <c r="P84">
+        <v>20.68661474933333</v>
+      </c>
+      <c r="Q84">
+        <v>26.48661474933333</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.5983400482761856</v>
+      </c>
+      <c r="T84">
+        <v>2.526117647828333</v>
+      </c>
+      <c r="U84">
+        <v>0.0509</v>
+      </c>
+      <c r="V84">
+        <v>0.24</v>
+      </c>
+      <c r="W84">
+        <v>0.038684</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.681586834753116</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1391199808549832</v>
+      </c>
+      <c r="C85">
+        <v>125.3680952396749</v>
+      </c>
+      <c r="D85">
+        <v>239.7370952396749</v>
+      </c>
+      <c r="E85">
+        <v>17.21900000000001</v>
+      </c>
+      <c r="F85">
+        <v>115.619</v>
+      </c>
+      <c r="G85">
+        <v>1.25</v>
+      </c>
+      <c r="H85">
+        <v>40.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K85">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L85">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M85">
+        <v>5.885007100000001</v>
+      </c>
+      <c r="N85">
+        <v>27.14832623333333</v>
+      </c>
+      <c r="O85">
+        <v>6.515598295999999</v>
+      </c>
+      <c r="P85">
+        <v>20.63272793733333</v>
+      </c>
+      <c r="Q85">
+        <v>26.43272793733333</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.6294838873822541</v>
+      </c>
+      <c r="T85">
+        <v>2.666720633851119</v>
+      </c>
+      <c r="U85">
+        <v>0.0509</v>
+      </c>
+      <c r="V85">
+        <v>0.24</v>
+      </c>
+      <c r="W85">
+        <v>0.038684</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.613133981322354</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1388178730202529</v>
+      </c>
+      <c r="C86">
+        <v>124.6992303623315</v>
+      </c>
+      <c r="D86">
+        <v>240.4612303623315</v>
+      </c>
+      <c r="E86">
+        <v>18.61199999999999</v>
+      </c>
+      <c r="F86">
+        <v>117.012</v>
+      </c>
+      <c r="G86">
+        <v>1.25</v>
+      </c>
+      <c r="H86">
+        <v>40.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K86">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L86">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M86">
+        <v>5.9559108</v>
+      </c>
+      <c r="N86">
+        <v>27.07742253333333</v>
+      </c>
+      <c r="O86">
+        <v>6.498581408</v>
+      </c>
+      <c r="P86">
+        <v>20.57884112533333</v>
+      </c>
+      <c r="Q86">
+        <v>26.37884112533333</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.6645207063765808</v>
+      </c>
+      <c r="T86">
+        <v>2.824898993126753</v>
+      </c>
+      <c r="U86">
+        <v>0.0509</v>
+      </c>
+      <c r="V86">
+        <v>0.24</v>
+      </c>
+      <c r="W86">
+        <v>0.038684</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>5.546310957735185</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1385157651855227</v>
+      </c>
+      <c r="C87">
+        <v>124.0347532945496</v>
+      </c>
+      <c r="D87">
+        <v>241.1897532945496</v>
+      </c>
+      <c r="E87">
+        <v>20.005</v>
+      </c>
+      <c r="F87">
+        <v>118.405</v>
+      </c>
+      <c r="G87">
+        <v>1.25</v>
+      </c>
+      <c r="H87">
+        <v>40.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K87">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L87">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M87">
+        <v>6.0268145</v>
+      </c>
+      <c r="N87">
+        <v>27.00651883333333</v>
+      </c>
+      <c r="O87">
+        <v>6.481564519999999</v>
+      </c>
+      <c r="P87">
+        <v>20.52495431333333</v>
+      </c>
+      <c r="Q87">
+        <v>26.32495431333333</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.704229101236818</v>
+      </c>
+      <c r="T87">
+        <v>3.004167800305805</v>
+      </c>
+      <c r="U87">
+        <v>0.0509</v>
+      </c>
+      <c r="V87">
+        <v>0.24</v>
+      </c>
+      <c r="W87">
+        <v>0.038684</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>5.481060240585359</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1382136573507925</v>
+      </c>
+      <c r="C88">
+        <v>123.3747040386292</v>
+      </c>
+      <c r="D88">
+        <v>241.9227040386292</v>
+      </c>
+      <c r="E88">
+        <v>21.398</v>
+      </c>
+      <c r="F88">
+        <v>119.798</v>
+      </c>
+      <c r="G88">
+        <v>1.25</v>
+      </c>
+      <c r="H88">
+        <v>40.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K88">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L88">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M88">
+        <v>6.0977182</v>
+      </c>
+      <c r="N88">
+        <v>26.93561513333333</v>
+      </c>
+      <c r="O88">
+        <v>6.464547631999999</v>
+      </c>
+      <c r="P88">
+        <v>20.47106750133333</v>
+      </c>
+      <c r="Q88">
+        <v>26.27106750133333</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.7496101239342319</v>
+      </c>
+      <c r="T88">
+        <v>3.209046437081865</v>
+      </c>
+      <c r="U88">
+        <v>0.0509</v>
+      </c>
+      <c r="V88">
+        <v>0.24</v>
+      </c>
+      <c r="W88">
+        <v>0.038684</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>5.417326981973901</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1379115495160623</v>
+      </c>
+      <c r="C89">
+        <v>122.7191230846037</v>
+      </c>
+      <c r="D89">
+        <v>242.6601230846037</v>
+      </c>
+      <c r="E89">
+        <v>22.791</v>
+      </c>
+      <c r="F89">
+        <v>121.191</v>
+      </c>
+      <c r="G89">
+        <v>1.25</v>
+      </c>
+      <c r="H89">
+        <v>40.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K89">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L89">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M89">
+        <v>6.168621900000001</v>
+      </c>
+      <c r="N89">
+        <v>26.86471143333333</v>
+      </c>
+      <c r="O89">
+        <v>6.447530743999999</v>
+      </c>
+      <c r="P89">
+        <v>20.41718068933333</v>
+      </c>
+      <c r="Q89">
+        <v>26.21718068933333</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.8019728424312482</v>
+      </c>
+      <c r="T89">
+        <v>3.445444864131165</v>
+      </c>
+      <c r="U89">
+        <v>0.0509</v>
+      </c>
+      <c r="V89">
+        <v>0.24</v>
+      </c>
+      <c r="W89">
+        <v>0.038684</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>5.355058855744316</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1376094416813321</v>
+      </c>
+      <c r="C90">
+        <v>122.0680514176964</v>
+      </c>
+      <c r="D90">
+        <v>243.4020514176964</v>
+      </c>
+      <c r="E90">
+        <v>24.18400000000001</v>
+      </c>
+      <c r="F90">
+        <v>122.584</v>
+      </c>
+      <c r="G90">
+        <v>1.25</v>
+      </c>
+      <c r="H90">
+        <v>40.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K90">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L90">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M90">
+        <v>6.239525600000001</v>
+      </c>
+      <c r="N90">
+        <v>26.79380773333333</v>
+      </c>
+      <c r="O90">
+        <v>6.430513855999999</v>
+      </c>
+      <c r="P90">
+        <v>20.36329387733333</v>
+      </c>
+      <c r="Q90">
+        <v>26.16329387733333</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.8630626806777673</v>
+      </c>
+      <c r="T90">
+        <v>3.721243029022015</v>
+      </c>
+      <c r="U90">
+        <v>0.0509</v>
+      </c>
+      <c r="V90">
+        <v>0.24</v>
+      </c>
+      <c r="W90">
+        <v>0.038684</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>5.294205914201767</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1373073338466018</v>
+      </c>
+      <c r="C91">
+        <v>121.421530525914</v>
+      </c>
+      <c r="D91">
+        <v>244.148530525914</v>
+      </c>
+      <c r="E91">
+        <v>25.57700000000001</v>
+      </c>
+      <c r="F91">
+        <v>123.977</v>
+      </c>
+      <c r="G91">
+        <v>1.25</v>
+      </c>
+      <c r="H91">
+        <v>40.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K91">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L91">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M91">
+        <v>6.310429300000001</v>
+      </c>
+      <c r="N91">
+        <v>26.72290403333333</v>
+      </c>
+      <c r="O91">
+        <v>6.413496967999999</v>
+      </c>
+      <c r="P91">
+        <v>20.30940706533333</v>
+      </c>
+      <c r="Q91">
+        <v>26.10940706533333</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.9352597622418348</v>
+      </c>
+      <c r="T91">
+        <v>4.047186314802111</v>
+      </c>
+      <c r="U91">
+        <v>0.0509</v>
+      </c>
+      <c r="V91">
+        <v>0.24</v>
+      </c>
+      <c r="W91">
+        <v>0.038684</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>5.234720454491634</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1370052260118716</v>
+      </c>
+      <c r="C92">
+        <v>120.7796024077793</v>
+      </c>
+      <c r="D92">
+        <v>244.8996024077793</v>
+      </c>
+      <c r="E92">
+        <v>26.97000000000001</v>
+      </c>
+      <c r="F92">
+        <v>125.37</v>
+      </c>
+      <c r="G92">
+        <v>1.25</v>
+      </c>
+      <c r="H92">
+        <v>40.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K92">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L92">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M92">
+        <v>6.381333000000001</v>
+      </c>
+      <c r="N92">
+        <v>26.65200033333333</v>
+      </c>
+      <c r="O92">
+        <v>6.396480079999999</v>
+      </c>
+      <c r="P92">
+        <v>20.25552025333333</v>
+      </c>
+      <c r="Q92">
+        <v>26.05552025333333</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.021896260118716</v>
+      </c>
+      <c r="T92">
+        <v>4.438318257738226</v>
+      </c>
+      <c r="U92">
+        <v>0.0509</v>
+      </c>
+      <c r="V92">
+        <v>0.24</v>
+      </c>
+      <c r="W92">
+        <v>0.038684</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>5.176556893886171</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1367031181771414</v>
+      </c>
+      <c r="C93">
+        <v>120.1423095802091</v>
+      </c>
+      <c r="D93">
+        <v>245.6553095802091</v>
+      </c>
+      <c r="E93">
+        <v>28.36300000000001</v>
+      </c>
+      <c r="F93">
+        <v>126.763</v>
+      </c>
+      <c r="G93">
+        <v>1.25</v>
+      </c>
+      <c r="H93">
+        <v>40.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K93">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L93">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M93">
+        <v>6.452236700000001</v>
+      </c>
+      <c r="N93">
+        <v>26.58109663333333</v>
+      </c>
+      <c r="O93">
+        <v>6.379463191999999</v>
+      </c>
+      <c r="P93">
+        <v>20.20163344133333</v>
+      </c>
+      <c r="Q93">
+        <v>26.00163344133333</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.127785313079349</v>
+      </c>
+      <c r="T93">
+        <v>4.916368410215699</v>
+      </c>
+      <c r="U93">
+        <v>0.0509</v>
+      </c>
+      <c r="V93">
+        <v>0.24</v>
+      </c>
+      <c r="W93">
+        <v>0.038684</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>5.119671653294016</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1364010103424112</v>
+      </c>
+      <c r="C94">
+        <v>119.5096950865362</v>
+      </c>
+      <c r="D94">
+        <v>246.4156950865362</v>
+      </c>
+      <c r="E94">
+        <v>29.756</v>
+      </c>
+      <c r="F94">
+        <v>128.156</v>
+      </c>
+      <c r="G94">
+        <v>1.25</v>
+      </c>
+      <c r="H94">
+        <v>40.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K94">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L94">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M94">
+        <v>6.523140400000001</v>
+      </c>
+      <c r="N94">
+        <v>26.51019293333333</v>
+      </c>
+      <c r="O94">
+        <v>6.362446303999999</v>
+      </c>
+      <c r="P94">
+        <v>20.14774662933333</v>
+      </c>
+      <c r="Q94">
+        <v>25.94774662933333</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.26014662928014</v>
+      </c>
+      <c r="T94">
+        <v>5.513931100812543</v>
+      </c>
+      <c r="U94">
+        <v>0.0509</v>
+      </c>
+      <c r="V94">
+        <v>0.24</v>
+      </c>
+      <c r="W94">
+        <v>0.038684</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>5.064023048366907</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.136098902507681</v>
+      </c>
+      <c r="C95">
+        <v>118.8818025046827</v>
+      </c>
+      <c r="D95">
+        <v>247.1808025046827</v>
+      </c>
+      <c r="E95">
+        <v>31.149</v>
+      </c>
+      <c r="F95">
+        <v>129.549</v>
+      </c>
+      <c r="G95">
+        <v>1.25</v>
+      </c>
+      <c r="H95">
+        <v>40.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K95">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L95">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M95">
+        <v>6.594044100000001</v>
+      </c>
+      <c r="N95">
+        <v>26.43928923333333</v>
+      </c>
+      <c r="O95">
+        <v>6.345429415999999</v>
+      </c>
+      <c r="P95">
+        <v>20.09385981733333</v>
+      </c>
+      <c r="Q95">
+        <v>25.89385981733333</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.430325464395443</v>
+      </c>
+      <c r="T95">
+        <v>6.282225988722769</v>
+      </c>
+      <c r="U95">
+        <v>0.0509</v>
+      </c>
+      <c r="V95">
+        <v>0.24</v>
+      </c>
+      <c r="W95">
+        <v>0.038684</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>5.00957118763178</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1357967946729507</v>
+      </c>
+      <c r="C96">
+        <v>118.2586759554844</v>
+      </c>
+      <c r="D96">
+        <v>247.9506759554844</v>
+      </c>
+      <c r="E96">
+        <v>32.542</v>
+      </c>
+      <c r="F96">
+        <v>130.942</v>
+      </c>
+      <c r="G96">
+        <v>1.25</v>
+      </c>
+      <c r="H96">
+        <v>40.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K96">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L96">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M96">
+        <v>6.6649478</v>
+      </c>
+      <c r="N96">
+        <v>26.36838553333333</v>
+      </c>
+      <c r="O96">
+        <v>6.328412527999999</v>
+      </c>
+      <c r="P96">
+        <v>20.03997300533333</v>
+      </c>
+      <c r="Q96">
+        <v>25.83997300533333</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.657230577882514</v>
+      </c>
+      <c r="T96">
+        <v>7.306619172603071</v>
+      </c>
+      <c r="U96">
+        <v>0.0509</v>
+      </c>
+      <c r="V96">
+        <v>0.24</v>
+      </c>
+      <c r="W96">
+        <v>0.038684</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.956277877125059</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1354946868382205</v>
+      </c>
+      <c r="C97">
+        <v>117.6403601111726</v>
+      </c>
+      <c r="D97">
+        <v>248.7253601111726</v>
+      </c>
+      <c r="E97">
+        <v>33.935</v>
+      </c>
+      <c r="F97">
+        <v>132.335</v>
+      </c>
+      <c r="G97">
+        <v>1.25</v>
+      </c>
+      <c r="H97">
+        <v>40.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K97">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L97">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M97">
+        <v>6.735851500000001</v>
+      </c>
+      <c r="N97">
+        <v>26.29748183333333</v>
+      </c>
+      <c r="O97">
+        <v>6.311395639999999</v>
+      </c>
+      <c r="P97">
+        <v>19.98608619333333</v>
+      </c>
+      <c r="Q97">
+        <v>25.78608619333333</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.974897736764413</v>
+      </c>
+      <c r="T97">
+        <v>8.740769630035496</v>
+      </c>
+      <c r="U97">
+        <v>0.0509</v>
+      </c>
+      <c r="V97">
+        <v>0.24</v>
+      </c>
+      <c r="W97">
+        <v>0.038684</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.904106531050058</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1351925790034903</v>
+      </c>
+      <c r="C98">
+        <v>117.0269002040149</v>
+      </c>
+      <c r="D98">
+        <v>249.5049002040149</v>
+      </c>
+      <c r="E98">
+        <v>35.328</v>
+      </c>
+      <c r="F98">
+        <v>133.728</v>
+      </c>
+      <c r="G98">
+        <v>1.25</v>
+      </c>
+      <c r="H98">
+        <v>40.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K98">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L98">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M98">
+        <v>6.8067552</v>
+      </c>
+      <c r="N98">
+        <v>26.22657813333333</v>
+      </c>
+      <c r="O98">
+        <v>6.294378751999999</v>
+      </c>
+      <c r="P98">
+        <v>19.93219938133333</v>
+      </c>
+      <c r="Q98">
+        <v>25.73219938133333</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.451398475087256</v>
+      </c>
+      <c r="T98">
+        <v>10.8919953161841</v>
+      </c>
+      <c r="U98">
+        <v>0.0509</v>
+      </c>
+      <c r="V98">
+        <v>0.24</v>
+      </c>
+      <c r="W98">
+        <v>0.038684</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.853022088018286</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1348904711687601</v>
+      </c>
+      <c r="C99">
+        <v>116.4183420351182</v>
+      </c>
+      <c r="D99">
+        <v>250.2893420351182</v>
+      </c>
+      <c r="E99">
+        <v>36.721</v>
+      </c>
+      <c r="F99">
+        <v>135.121</v>
+      </c>
+      <c r="G99">
+        <v>1.25</v>
+      </c>
+      <c r="H99">
+        <v>40.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K99">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L99">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M99">
+        <v>6.877658900000001</v>
+      </c>
+      <c r="N99">
+        <v>26.15567443333333</v>
+      </c>
+      <c r="O99">
+        <v>6.277361864</v>
+      </c>
+      <c r="P99">
+        <v>19.87831256933333</v>
+      </c>
+      <c r="Q99">
+        <v>25.67831256933333</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.245566372292</v>
+      </c>
+      <c r="T99">
+        <v>14.47737145976515</v>
+      </c>
+      <c r="U99">
+        <v>0.0509</v>
+      </c>
+      <c r="V99">
+        <v>0.24</v>
+      </c>
+      <c r="W99">
+        <v>0.038684</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.802990932471706</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1345883633340299</v>
+      </c>
+      <c r="C100">
+        <v>115.8147319834004</v>
+      </c>
+      <c r="D100">
+        <v>251.0787319834004</v>
+      </c>
+      <c r="E100">
+        <v>38.114</v>
+      </c>
+      <c r="F100">
+        <v>136.514</v>
+      </c>
+      <c r="G100">
+        <v>1.25</v>
+      </c>
+      <c r="H100">
+        <v>40.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K100">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L100">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M100">
+        <v>6.948562600000001</v>
+      </c>
+      <c r="N100">
+        <v>26.08477073333333</v>
+      </c>
+      <c r="O100">
+        <v>6.260344975999999</v>
+      </c>
+      <c r="P100">
+        <v>19.82442575733333</v>
+      </c>
+      <c r="Q100">
+        <v>25.62442575733333</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.833902166701489</v>
+      </c>
+      <c r="T100">
+        <v>21.64812374692724</v>
+      </c>
+      <c r="U100">
+        <v>0.0509</v>
+      </c>
+      <c r="V100">
+        <v>0.24</v>
+      </c>
+      <c r="W100">
+        <v>0.038684</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>4.753980820915872</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1342862554992997</v>
+      </c>
+      <c r="C101">
+        <v>115.2161170147296</v>
+      </c>
+      <c r="D101">
+        <v>251.8731170147296</v>
+      </c>
+      <c r="E101">
+        <v>39.50700000000001</v>
+      </c>
+      <c r="F101">
+        <v>137.907</v>
+      </c>
+      <c r="G101">
+        <v>1.25</v>
+      </c>
+      <c r="H101">
+        <v>40.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>38.83333333333334</v>
+      </c>
+      <c r="K101">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="L101">
+        <v>33.03333333333333</v>
+      </c>
+      <c r="M101">
+        <v>7.0194663</v>
+      </c>
+      <c r="N101">
+        <v>26.01386703333333</v>
+      </c>
+      <c r="O101">
+        <v>6.243328087999999</v>
+      </c>
+      <c r="P101">
+        <v>19.77053894533333</v>
+      </c>
+      <c r="Q101">
+        <v>25.57053894533333</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>9.598909549929957</v>
+      </c>
+      <c r="T101">
+        <v>43.16038060841352</v>
+      </c>
+      <c r="U101">
+        <v>0.0509</v>
+      </c>
+      <c r="V101">
+        <v>0.24</v>
+      </c>
+      <c r="W101">
+        <v>0.038684</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>4.705960812623793</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_oil_gas_distribution.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1610186322011557</v>
+        <v>0.160666387483873</v>
       </c>
       <c r="C2">
-        <v>200.6664147132117</v>
+        <v>199.81970383749</v>
       </c>
       <c r="D2">
-        <v>199.6664147132117</v>
+        <v>200.27870383749</v>
       </c>
       <c r="E2">
-        <v>-104.5</v>
+        <v>-103.041</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.459</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1439,28 +1439,28 @@
         <v>17.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0733877</v>
       </c>
       <c r="N2">
-        <v>17.1</v>
+        <v>17.0266123</v>
       </c>
       <c r="O2">
-        <v>4.104</v>
+        <v>4.086386952</v>
       </c>
       <c r="P2">
-        <v>12.996</v>
+        <v>12.940225348</v>
       </c>
       <c r="Q2">
-        <v>19.096</v>
+        <v>19.040225348</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1610186322011557</v>
+        <v>0.1619031388725989</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5704579331477598</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>233.0090737276138</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.160666387483873</v>
+        <v>0.1603141427665902</v>
       </c>
       <c r="C3">
-        <v>199.81970383749</v>
+        <v>198.9767597560572</v>
       </c>
       <c r="D3">
-        <v>200.27870383749</v>
+        <v>200.8947597560572</v>
       </c>
       <c r="E3">
-        <v>-103.041</v>
+        <v>-101.582</v>
       </c>
       <c r="F3">
-        <v>1.459</v>
+        <v>2.918</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -1521,28 +1521,28 @@
         <v>17.1</v>
       </c>
       <c r="M3">
-        <v>0.0733877</v>
+        <v>0.1467754</v>
       </c>
       <c r="N3">
-        <v>17.0266123</v>
+        <v>16.9532246</v>
       </c>
       <c r="O3">
-        <v>4.086386952</v>
+        <v>4.068773904</v>
       </c>
       <c r="P3">
-        <v>12.940225348</v>
+        <v>12.884450696</v>
       </c>
       <c r="Q3">
-        <v>19.040225348</v>
+        <v>18.984450696</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1619031388725989</v>
+        <v>0.1628056967006022</v>
       </c>
       <c r="T3">
-        <v>0.5704579331477598</v>
+        <v>0.5748925356753801</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>233.0090737276138</v>
+        <v>116.5045368638069</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1603141427665902</v>
+        <v>0.1599618980493074</v>
       </c>
       <c r="C4">
-        <v>198.9767597560572</v>
+        <v>198.1376173360643</v>
       </c>
       <c r="D4">
-        <v>200.8947597560572</v>
+        <v>201.5146173360643</v>
       </c>
       <c r="E4">
-        <v>-101.582</v>
+        <v>-100.123</v>
       </c>
       <c r="F4">
-        <v>2.918</v>
+        <v>4.377</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1603,28 +1603,28 @@
         <v>17.1</v>
       </c>
       <c r="M4">
-        <v>0.1467754</v>
+        <v>0.2201631</v>
       </c>
       <c r="N4">
-        <v>16.9532246</v>
+        <v>16.8798369</v>
       </c>
       <c r="O4">
-        <v>4.068773904</v>
+        <v>4.051160856</v>
       </c>
       <c r="P4">
-        <v>12.884450696</v>
+        <v>12.828676044</v>
       </c>
       <c r="Q4">
-        <v>18.984450696</v>
+        <v>18.928676044</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1628056967006022</v>
+        <v>0.1637268639683581</v>
       </c>
       <c r="T4">
-        <v>0.5748925356753801</v>
+        <v>0.5794185733066628</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>116.5045368638069</v>
+        <v>77.66969124253794</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1599618980493074</v>
+        <v>0.1596096533320246</v>
       </c>
       <c r="C5">
-        <v>198.1376173360643</v>
+        <v>197.3023118763227</v>
       </c>
       <c r="D5">
-        <v>201.5146173360643</v>
+        <v>202.1383118763227</v>
       </c>
       <c r="E5">
-        <v>-100.123</v>
+        <v>-98.664</v>
       </c>
       <c r="F5">
-        <v>4.377</v>
+        <v>5.836</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1685,28 +1685,28 @@
         <v>17.1</v>
       </c>
       <c r="M5">
-        <v>0.2201631</v>
+        <v>0.2935508</v>
       </c>
       <c r="N5">
-        <v>16.8798369</v>
+        <v>16.8064492</v>
       </c>
       <c r="O5">
-        <v>4.051160856</v>
+        <v>4.033547808000001</v>
       </c>
       <c r="P5">
-        <v>12.828676044</v>
+        <v>12.772901392</v>
       </c>
       <c r="Q5">
-        <v>18.928676044</v>
+        <v>18.872901392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1637268639683581</v>
+        <v>0.164667222220859</v>
       </c>
       <c r="T5">
-        <v>0.5794185733066628</v>
+        <v>0.5840389033885971</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>77.66969124253794</v>
+        <v>58.25226843190345</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1596096533320246</v>
+        <v>0.1592574086147419</v>
       </c>
       <c r="C6">
-        <v>197.3023118763227</v>
+        <v>196.4708791140046</v>
       </c>
       <c r="D6">
-        <v>202.1383118763227</v>
+        <v>202.7658791140045</v>
       </c>
       <c r="E6">
-        <v>-98.664</v>
+        <v>-97.205</v>
       </c>
       <c r="F6">
-        <v>5.836</v>
+        <v>7.295000000000001</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1767,28 +1767,28 @@
         <v>17.1</v>
       </c>
       <c r="M6">
-        <v>0.2935508</v>
+        <v>0.3669385</v>
       </c>
       <c r="N6">
-        <v>16.8064492</v>
+        <v>16.7330615</v>
       </c>
       <c r="O6">
-        <v>4.033547808000001</v>
+        <v>4.01593476</v>
       </c>
       <c r="P6">
-        <v>12.772901392</v>
+        <v>12.71712674</v>
       </c>
       <c r="Q6">
-        <v>18.872901392</v>
+        <v>18.81712674</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.164667222220859</v>
+        <v>0.1656273774892019</v>
       </c>
       <c r="T6">
-        <v>0.5840389033885971</v>
+        <v>0.5887565035775195</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>58.25226843190345</v>
+        <v>46.60181474552275</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1592574086147419</v>
+        <v>0.1589051638974591</v>
       </c>
       <c r="C7">
-        <v>196.4708791140046</v>
+        <v>195.6433552314687</v>
       </c>
       <c r="D7">
-        <v>202.7658791140045</v>
+        <v>203.3973552314687</v>
       </c>
       <c r="E7">
-        <v>-97.205</v>
+        <v>-95.746</v>
       </c>
       <c r="F7">
-        <v>7.295000000000001</v>
+        <v>8.754000000000001</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1849,28 +1849,28 @@
         <v>17.1</v>
       </c>
       <c r="M7">
-        <v>0.3669385</v>
+        <v>0.4403262000000001</v>
       </c>
       <c r="N7">
-        <v>16.7330615</v>
+        <v>16.6596738</v>
       </c>
       <c r="O7">
-        <v>4.01593476</v>
+        <v>3.998321712</v>
       </c>
       <c r="P7">
-        <v>12.71712674</v>
+        <v>12.661352088</v>
       </c>
       <c r="Q7">
-        <v>18.81712674</v>
+        <v>18.761352088</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1656273774892019</v>
+        <v>0.1666079615930416</v>
       </c>
       <c r="T7">
-        <v>0.5887565035775195</v>
+        <v>0.5935744782385467</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.60181474552275</v>
+        <v>38.83484562126895</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1589051638974591</v>
+        <v>0.1585529191801763</v>
       </c>
       <c r="C8">
-        <v>195.6433552314687</v>
+        <v>194.8197768632145</v>
       </c>
       <c r="D8">
-        <v>203.3973552314687</v>
+        <v>204.0327768632145</v>
       </c>
       <c r="E8">
-        <v>-95.746</v>
+        <v>-94.28700000000001</v>
       </c>
       <c r="F8">
-        <v>8.754</v>
+        <v>10.213</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1931,28 +1931,28 @@
         <v>17.1</v>
       </c>
       <c r="M8">
-        <v>0.4403261999999999</v>
+        <v>0.5137138999999999</v>
       </c>
       <c r="N8">
-        <v>16.6596738</v>
+        <v>16.5862861</v>
       </c>
       <c r="O8">
-        <v>3.998321712</v>
+        <v>3.980708664</v>
       </c>
       <c r="P8">
-        <v>12.661352088</v>
+        <v>12.605577436</v>
       </c>
       <c r="Q8">
-        <v>18.761352088</v>
+        <v>18.705577436</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1666079615930416</v>
+        <v>0.1676096335270713</v>
       </c>
       <c r="T8">
-        <v>0.5935744782385467</v>
+        <v>0.5984960652578755</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.83484562126896</v>
+        <v>33.28701053251626</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1585529191801763</v>
+        <v>0.1582006744628935</v>
       </c>
       <c r="C9">
-        <v>194.8197768632145</v>
+        <v>194.0001811029668</v>
       </c>
       <c r="D9">
-        <v>204.0327768632145</v>
+        <v>204.6721811029668</v>
       </c>
       <c r="E9">
-        <v>-94.28700000000001</v>
+        <v>-92.828</v>
       </c>
       <c r="F9">
-        <v>10.213</v>
+        <v>11.672</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2013,28 +2013,28 @@
         <v>17.1</v>
       </c>
       <c r="M9">
-        <v>0.5137139000000001</v>
+        <v>0.5871016</v>
       </c>
       <c r="N9">
-        <v>16.5862861</v>
+        <v>16.5128984</v>
       </c>
       <c r="O9">
-        <v>3.980708664</v>
+        <v>3.963095616</v>
       </c>
       <c r="P9">
-        <v>12.605577436</v>
+        <v>12.549802784</v>
       </c>
       <c r="Q9">
-        <v>18.705577436</v>
+        <v>18.649802784</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1676096335270713</v>
+        <v>0.1686330809379278</v>
       </c>
       <c r="T9">
-        <v>0.5984960652578755</v>
+        <v>0.6035246432993636</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>33.28701053251625</v>
+        <v>29.12613421595172</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1582006744628935</v>
+        <v>0.1578484297456108</v>
       </c>
       <c r="C10">
-        <v>194.0001811029668</v>
+        <v>193.1846055108942</v>
       </c>
       <c r="D10">
-        <v>204.6721811029668</v>
+        <v>205.3156055108942</v>
       </c>
       <c r="E10">
-        <v>-92.828</v>
+        <v>-91.369</v>
       </c>
       <c r="F10">
-        <v>11.672</v>
+        <v>13.131</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2095,28 +2095,28 @@
         <v>17.1</v>
       </c>
       <c r="M10">
-        <v>0.5871016</v>
+        <v>0.6604892999999999</v>
       </c>
       <c r="N10">
-        <v>16.5128984</v>
+        <v>16.4395107</v>
       </c>
       <c r="O10">
-        <v>3.963095616</v>
+        <v>3.945482568000001</v>
       </c>
       <c r="P10">
-        <v>12.549802784</v>
+        <v>12.494028132</v>
       </c>
       <c r="Q10">
-        <v>18.649802784</v>
+        <v>18.594028132</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1686330809379278</v>
+        <v>0.1696790216984733</v>
       </c>
       <c r="T10">
-        <v>0.6035246432993636</v>
+        <v>0.6086637395395658</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>29.12613421595172</v>
+        <v>25.88989708084598</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1578484297456108</v>
+        <v>0.157496185028328</v>
       </c>
       <c r="C11">
-        <v>193.1846055108942</v>
+        <v>192.3730881209635</v>
       </c>
       <c r="D11">
-        <v>205.3156055108942</v>
+        <v>205.9630881209635</v>
       </c>
       <c r="E11">
-        <v>-91.369</v>
+        <v>-89.91</v>
       </c>
       <c r="F11">
-        <v>13.131</v>
+        <v>14.59</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2177,28 +2177,28 @@
         <v>17.1</v>
       </c>
       <c r="M11">
-        <v>0.6604892999999999</v>
+        <v>0.733877</v>
       </c>
       <c r="N11">
-        <v>16.4395107</v>
+        <v>16.366123</v>
       </c>
       <c r="O11">
-        <v>3.945482568000001</v>
+        <v>3.92786952</v>
       </c>
       <c r="P11">
-        <v>12.494028132</v>
+        <v>12.43825348</v>
       </c>
       <c r="Q11">
-        <v>18.594028132</v>
+        <v>18.53825348</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1696790216984733</v>
+        <v>0.1707482055870311</v>
       </c>
       <c r="T11">
-        <v>0.6086637395395658</v>
+        <v>0.6139170379184392</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.88989708084598</v>
+        <v>23.30090737276138</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.157496185028328</v>
+        <v>0.1571439403110452</v>
       </c>
       <c r="C12">
-        <v>192.3730881209635</v>
+        <v>191.5656674484347</v>
       </c>
       <c r="D12">
-        <v>205.9630881209635</v>
+        <v>206.6146674484347</v>
       </c>
       <c r="E12">
-        <v>-89.91</v>
+        <v>-88.45099999999999</v>
       </c>
       <c r="F12">
-        <v>14.59</v>
+        <v>16.049</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -2259,28 +2259,28 @@
         <v>17.1</v>
       </c>
       <c r="M12">
-        <v>0.733877</v>
+        <v>0.8072646999999999</v>
       </c>
       <c r="N12">
-        <v>16.366123</v>
+        <v>16.2927353</v>
       </c>
       <c r="O12">
-        <v>3.92786952</v>
+        <v>3.910256472</v>
       </c>
       <c r="P12">
-        <v>12.43825348</v>
+        <v>12.382478828</v>
       </c>
       <c r="Q12">
-        <v>18.53825348</v>
+        <v>18.482478828</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1707482055870311</v>
+        <v>0.1718414160798261</v>
       </c>
       <c r="T12">
-        <v>0.6139170379184392</v>
+        <v>0.6192883879462759</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.30090737276138</v>
+        <v>21.18264306614671</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1571439403110452</v>
+        <v>0.1567916955937624</v>
       </c>
       <c r="C13">
-        <v>191.5656674484347</v>
+        <v>190.7623824974977</v>
       </c>
       <c r="D13">
-        <v>206.6146674484347</v>
+        <v>207.2703824974977</v>
       </c>
       <c r="E13">
-        <v>-88.45099999999999</v>
+        <v>-86.992</v>
       </c>
       <c r="F13">
-        <v>16.049</v>
+        <v>17.508</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -2341,28 +2341,28 @@
         <v>17.1</v>
       </c>
       <c r="M13">
-        <v>0.8072646999999999</v>
+        <v>0.8806523999999999</v>
       </c>
       <c r="N13">
-        <v>16.2927353</v>
+        <v>16.2193476</v>
       </c>
       <c r="O13">
-        <v>3.910256472</v>
+        <v>3.892643424000001</v>
       </c>
       <c r="P13">
-        <v>12.382478828</v>
+        <v>12.326704176</v>
       </c>
       <c r="Q13">
-        <v>18.482478828</v>
+        <v>18.426704176</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1718414160798261</v>
+        <v>0.1729594722656391</v>
       </c>
       <c r="T13">
-        <v>0.6192883879462759</v>
+        <v>0.6247818141111089</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>21.18264306614671</v>
+        <v>19.41742281063448</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1567916955937624</v>
+        <v>0.1564394508764797</v>
       </c>
       <c r="C14">
-        <v>190.7623824974977</v>
+        <v>189.9632727690558</v>
       </c>
       <c r="D14">
-        <v>207.2703824974977</v>
+        <v>207.9302727690558</v>
       </c>
       <c r="E14">
-        <v>-86.992</v>
+        <v>-85.533</v>
       </c>
       <c r="F14">
-        <v>17.508</v>
+        <v>18.967</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2423,28 +2423,28 @@
         <v>17.1</v>
       </c>
       <c r="M14">
-        <v>0.8806523999999999</v>
+        <v>0.9540401000000001</v>
       </c>
       <c r="N14">
-        <v>16.2193476</v>
+        <v>16.1459599</v>
       </c>
       <c r="O14">
-        <v>3.892643424000001</v>
+        <v>3.875030376</v>
       </c>
       <c r="P14">
-        <v>12.326704176</v>
+        <v>12.270929524</v>
       </c>
       <c r="Q14">
-        <v>18.426704176</v>
+        <v>18.370929524</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1729594722656391</v>
+        <v>0.1741032308925054</v>
       </c>
       <c r="T14">
-        <v>0.6247818141111089</v>
+        <v>0.6304015259349037</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.41742281063448</v>
+        <v>17.92377490212413</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1564394508764797</v>
+        <v>0.1560872061591969</v>
       </c>
       <c r="C15">
-        <v>189.9632727690558</v>
+        <v>189.1683782686579</v>
       </c>
       <c r="D15">
-        <v>207.9302727690558</v>
+        <v>208.5943782686579</v>
       </c>
       <c r="E15">
-        <v>-85.533</v>
+        <v>-84.074</v>
       </c>
       <c r="F15">
-        <v>18.967</v>
+        <v>20.426</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -2505,28 +2505,28 @@
         <v>17.1</v>
       </c>
       <c r="M15">
-        <v>0.9540401000000001</v>
+        <v>1.0274278</v>
       </c>
       <c r="N15">
-        <v>16.1459599</v>
+        <v>16.0725722</v>
       </c>
       <c r="O15">
-        <v>3.875030376</v>
+        <v>3.857417328</v>
       </c>
       <c r="P15">
-        <v>12.270929524</v>
+        <v>12.215154872</v>
       </c>
       <c r="Q15">
-        <v>18.370929524</v>
+        <v>18.315154872</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1741032308925054</v>
+        <v>0.1752735885572057</v>
       </c>
       <c r="T15">
-        <v>0.6304015259349037</v>
+        <v>0.6361519287313449</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.92377490212413</v>
+        <v>16.64350526625812</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1560872061591969</v>
+        <v>0.1557349614419141</v>
       </c>
       <c r="C16">
-        <v>189.1683782686579</v>
+        <v>188.3777395145826</v>
       </c>
       <c r="D16">
-        <v>208.5943782686579</v>
+        <v>209.2627395145826</v>
       </c>
       <c r="E16">
-        <v>-84.074</v>
+        <v>-82.61499999999999</v>
       </c>
       <c r="F16">
-        <v>20.426</v>
+        <v>21.88500000000001</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2587,28 +2587,28 @@
         <v>17.1</v>
       </c>
       <c r="M16">
-        <v>1.0274278</v>
+        <v>1.1008155</v>
       </c>
       <c r="N16">
-        <v>16.0725722</v>
+        <v>15.9991845</v>
       </c>
       <c r="O16">
-        <v>3.857417328</v>
+        <v>3.839804280000001</v>
       </c>
       <c r="P16">
-        <v>12.215154872</v>
+        <v>12.15938022</v>
       </c>
       <c r="Q16">
-        <v>18.315154872</v>
+        <v>18.25938022</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1752735885572057</v>
+        <v>0.1764714840493108</v>
       </c>
       <c r="T16">
-        <v>0.6361519287313449</v>
+        <v>0.6420376351229965</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.64350526625812</v>
+        <v>15.53393824850758</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1557349614419141</v>
+        <v>0.1553827167246313</v>
       </c>
       <c r="C17">
-        <v>188.3777395145827</v>
+        <v>187.5913975460802</v>
       </c>
       <c r="D17">
-        <v>209.2627395145827</v>
+        <v>209.9353975460802</v>
       </c>
       <c r="E17">
-        <v>-82.61499999999999</v>
+        <v>-81.15600000000001</v>
       </c>
       <c r="F17">
-        <v>21.885</v>
+        <v>23.344</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2669,28 +2669,28 @@
         <v>17.1</v>
       </c>
       <c r="M17">
-        <v>1.1008155</v>
+        <v>1.1742032</v>
       </c>
       <c r="N17">
-        <v>15.9991845</v>
+        <v>15.9257968</v>
       </c>
       <c r="O17">
-        <v>3.839804280000001</v>
+        <v>3.822191232</v>
       </c>
       <c r="P17">
-        <v>12.15938022</v>
+        <v>12.103605568</v>
       </c>
       <c r="Q17">
-        <v>18.25938022</v>
+        <v>18.203605568</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1764714840493107</v>
+        <v>0.1776979008626564</v>
       </c>
       <c r="T17">
-        <v>0.6420376351229964</v>
+        <v>0.6480634773811158</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.53393824850759</v>
+        <v>14.56306710797586</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1553827167246313</v>
+        <v>0.1550304720073486</v>
       </c>
       <c r="C18">
-        <v>187.5913975460802</v>
+        <v>186.8093939317709</v>
       </c>
       <c r="D18">
-        <v>209.9353975460802</v>
+        <v>210.6123939317709</v>
       </c>
       <c r="E18">
-        <v>-81.15600000000001</v>
+        <v>-79.697</v>
       </c>
       <c r="F18">
-        <v>23.344</v>
+        <v>24.803</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2751,28 +2751,28 @@
         <v>17.1</v>
       </c>
       <c r="M18">
-        <v>1.1742032</v>
+        <v>1.2475909</v>
       </c>
       <c r="N18">
-        <v>15.9257968</v>
+        <v>15.8524091</v>
       </c>
       <c r="O18">
-        <v>3.822191232</v>
+        <v>3.804578184</v>
       </c>
       <c r="P18">
-        <v>12.103605568</v>
+        <v>12.047830916</v>
       </c>
       <c r="Q18">
-        <v>18.203605568</v>
+        <v>18.147830916</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1776979008626564</v>
+        <v>0.1789538698883718</v>
       </c>
       <c r="T18">
-        <v>0.6480634773811158</v>
+        <v>0.6542345206575032</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.56306710797586</v>
+        <v>13.70641610162434</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1550304720073486</v>
+        <v>0.1546782272900658</v>
       </c>
       <c r="C19">
-        <v>186.8093939317709</v>
+        <v>186.0317707782096</v>
       </c>
       <c r="D19">
-        <v>210.6123939317709</v>
+        <v>211.2937707782096</v>
       </c>
       <c r="E19">
-        <v>-79.697</v>
+        <v>-78.238</v>
       </c>
       <c r="F19">
-        <v>24.803</v>
+        <v>26.262</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2833,28 +2833,28 @@
         <v>17.1</v>
       </c>
       <c r="M19">
-        <v>1.2475909</v>
+        <v>1.3209786</v>
       </c>
       <c r="N19">
-        <v>15.8524091</v>
+        <v>15.7790214</v>
       </c>
       <c r="O19">
-        <v>3.804578184</v>
+        <v>3.786965136</v>
       </c>
       <c r="P19">
-        <v>12.047830916</v>
+        <v>11.992056264</v>
       </c>
       <c r="Q19">
-        <v>18.147830916</v>
+        <v>18.092056264</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1789538698883718</v>
+        <v>0.1802404723049583</v>
       </c>
       <c r="T19">
-        <v>0.6542345206575032</v>
+        <v>0.6605560771845341</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>13.70641610162434</v>
+        <v>12.94494854042299</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1546782272900658</v>
+        <v>0.154542582572783</v>
       </c>
       <c r="C20">
-        <v>186.0317707782096</v>
+        <v>184.836337111864</v>
       </c>
       <c r="D20">
-        <v>211.2937707782096</v>
+        <v>211.557337111864</v>
       </c>
       <c r="E20">
-        <v>-78.238</v>
+        <v>-76.779</v>
       </c>
       <c r="F20">
-        <v>26.262</v>
+        <v>27.721</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2915,45 +2915,45 @@
         <v>17.1</v>
       </c>
       <c r="M20">
-        <v>1.3209786</v>
+        <v>1.4359478</v>
       </c>
       <c r="N20">
-        <v>15.7790214</v>
+        <v>15.6640522</v>
       </c>
       <c r="O20">
-        <v>3.786965136</v>
+        <v>3.759372528000001</v>
       </c>
       <c r="P20">
-        <v>11.992056264</v>
+        <v>11.904679672</v>
       </c>
       <c r="Q20">
-        <v>18.092056264</v>
+        <v>18.004679672</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1802404723049583</v>
+        <v>0.1815588426824482</v>
       </c>
       <c r="T20">
-        <v>0.660556077184534</v>
+        <v>0.6670337215270472</v>
       </c>
       <c r="U20">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>12.94494854042299</v>
+        <v>11.90851088040944</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.154542582572783</v>
+        <v>0.1542017378555003</v>
       </c>
       <c r="C21">
-        <v>184.836337111864</v>
+        <v>184.0425312515844</v>
       </c>
       <c r="D21">
-        <v>211.557337111864</v>
+        <v>212.2225312515844</v>
       </c>
       <c r="E21">
-        <v>-76.779</v>
+        <v>-75.31999999999999</v>
       </c>
       <c r="F21">
-        <v>27.721</v>
+        <v>29.18</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2997,28 +2997,28 @@
         <v>17.1</v>
       </c>
       <c r="M21">
-        <v>1.4359478</v>
+        <v>1.511524</v>
       </c>
       <c r="N21">
-        <v>15.6640522</v>
+        <v>15.588476</v>
       </c>
       <c r="O21">
-        <v>3.759372528000001</v>
+        <v>3.74123424</v>
       </c>
       <c r="P21">
-        <v>11.904679672</v>
+        <v>11.84724176</v>
       </c>
       <c r="Q21">
-        <v>18.004679672</v>
+        <v>17.94724176</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1815588426824482</v>
+        <v>0.1829101723193753</v>
       </c>
       <c r="T21">
-        <v>0.6670337215270472</v>
+        <v>0.6736733069781232</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.90851088040944</v>
+        <v>11.31308533638897</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1542017378555003</v>
+        <v>0.1538608931382175</v>
       </c>
       <c r="C22">
-        <v>184.0425312515844</v>
+        <v>183.2529216902972</v>
       </c>
       <c r="D22">
-        <v>212.2225312515844</v>
+        <v>212.8919216902972</v>
       </c>
       <c r="E22">
-        <v>-75.31999999999999</v>
+        <v>-73.86099999999999</v>
       </c>
       <c r="F22">
-        <v>29.18</v>
+        <v>30.639</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3079,28 +3079,28 @@
         <v>17.1</v>
       </c>
       <c r="M22">
-        <v>1.511524</v>
+        <v>1.5871002</v>
       </c>
       <c r="N22">
-        <v>15.588476</v>
+        <v>15.5128998</v>
       </c>
       <c r="O22">
-        <v>3.74123424</v>
+        <v>3.723095952</v>
       </c>
       <c r="P22">
-        <v>11.84724176</v>
+        <v>11.789803848</v>
       </c>
       <c r="Q22">
-        <v>17.94724176</v>
+        <v>17.889803848</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1829101723193753</v>
+        <v>0.1842957128331867</v>
       </c>
       <c r="T22">
-        <v>0.6736733069781232</v>
+        <v>0.6804809832001126</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.31308533638897</v>
+        <v>10.77436698703711</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1538608931382175</v>
+        <v>0.1535200484209347</v>
       </c>
       <c r="C23">
-        <v>183.2529216902972</v>
+        <v>182.4675482614324</v>
       </c>
       <c r="D23">
-        <v>212.8919216902972</v>
+        <v>213.5655482614324</v>
       </c>
       <c r="E23">
-        <v>-73.861</v>
+        <v>-72.402</v>
       </c>
       <c r="F23">
-        <v>30.639</v>
+        <v>32.098</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3161,28 +3161,28 @@
         <v>17.1</v>
       </c>
       <c r="M23">
-        <v>1.5871002</v>
+        <v>1.6626764</v>
       </c>
       <c r="N23">
-        <v>15.5128998</v>
+        <v>15.4373236</v>
       </c>
       <c r="O23">
-        <v>3.723095952</v>
+        <v>3.704957664</v>
       </c>
       <c r="P23">
-        <v>11.789803848</v>
+        <v>11.732365936</v>
       </c>
       <c r="Q23">
-        <v>17.889803848</v>
+        <v>17.832365936</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1842957128331867</v>
+        <v>0.1857167800268394</v>
       </c>
       <c r="T23">
-        <v>0.6804809832001126</v>
+        <v>0.6874632152226658</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.77436698703712</v>
+        <v>10.28462303308088</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1535200484209347</v>
+        <v>0.1531792037036519</v>
       </c>
       <c r="C24">
-        <v>182.4675482614324</v>
+        <v>181.6864513041799</v>
       </c>
       <c r="D24">
-        <v>213.5655482614324</v>
+        <v>214.2434513041799</v>
       </c>
       <c r="E24">
-        <v>-72.402</v>
+        <v>-70.943</v>
       </c>
       <c r="F24">
-        <v>32.098</v>
+        <v>33.557</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3243,28 +3243,28 @@
         <v>17.1</v>
       </c>
       <c r="M24">
-        <v>1.6626764</v>
+        <v>1.7382526</v>
       </c>
       <c r="N24">
-        <v>15.4373236</v>
+        <v>15.3617474</v>
       </c>
       <c r="O24">
-        <v>3.704957664</v>
+        <v>3.686819376</v>
       </c>
       <c r="P24">
-        <v>11.732365936</v>
+        <v>11.674928024</v>
       </c>
       <c r="Q24">
-        <v>17.832365936</v>
+        <v>17.774928024</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1857167800268394</v>
+        <v>0.1871747580566908</v>
       </c>
       <c r="T24">
-        <v>0.6874632152226658</v>
+        <v>0.6946268039211294</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>10.28462303308088</v>
+        <v>9.837465509903453</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1531792037036519</v>
+        <v>0.1531484389863692</v>
       </c>
       <c r="C25">
-        <v>181.6864513041799</v>
+        <v>180.2888507923448</v>
       </c>
       <c r="D25">
-        <v>214.2434513041799</v>
+        <v>214.3048507923448</v>
       </c>
       <c r="E25">
-        <v>-70.943</v>
+        <v>-69.48399999999999</v>
       </c>
       <c r="F25">
-        <v>33.557</v>
+        <v>35.01600000000001</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3325,45 +3325,45 @@
         <v>17.1</v>
       </c>
       <c r="M25">
-        <v>1.7382526</v>
+        <v>1.873356</v>
       </c>
       <c r="N25">
-        <v>15.3617474</v>
+        <v>15.226644</v>
       </c>
       <c r="O25">
-        <v>3.686819376</v>
+        <v>3.65439456</v>
       </c>
       <c r="P25">
-        <v>11.674928024</v>
+        <v>11.57224944</v>
       </c>
       <c r="Q25">
-        <v>17.774928024</v>
+        <v>17.67224944</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1871747580566908</v>
+        <v>0.1886711039294331</v>
       </c>
       <c r="T25">
-        <v>0.6946268039211294</v>
+        <v>0.7019789081116579</v>
       </c>
       <c r="U25">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>9.837465509903453</v>
+        <v>9.128003433410413</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1531484389863692</v>
+        <v>0.1528205142690864</v>
       </c>
       <c r="C26">
-        <v>180.2888507923448</v>
+        <v>179.486508612468</v>
       </c>
       <c r="D26">
-        <v>214.3048507923448</v>
+        <v>214.961508612468</v>
       </c>
       <c r="E26">
-        <v>-69.48400000000001</v>
+        <v>-68.02500000000001</v>
       </c>
       <c r="F26">
-        <v>35.016</v>
+        <v>36.475</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3407,28 +3407,28 @@
         <v>17.1</v>
       </c>
       <c r="M26">
-        <v>1.873356</v>
+        <v>1.9514125</v>
       </c>
       <c r="N26">
-        <v>15.226644</v>
+        <v>15.1485875</v>
       </c>
       <c r="O26">
-        <v>3.654394560000001</v>
+        <v>3.635661</v>
       </c>
       <c r="P26">
-        <v>11.57224944</v>
+        <v>11.5129265</v>
       </c>
       <c r="Q26">
-        <v>17.67224944</v>
+        <v>17.6129265</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1886711039294331</v>
+        <v>0.1902073523587818</v>
       </c>
       <c r="T26">
-        <v>0.7019789081116579</v>
+        <v>0.7095270684139338</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.128003433410417</v>
+        <v>8.762883296073998</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1528205142690864</v>
+        <v>0.1524925895518036</v>
       </c>
       <c r="C27">
-        <v>179.486508612468</v>
+        <v>178.6882029702912</v>
       </c>
       <c r="D27">
-        <v>214.961508612468</v>
+        <v>215.6222029702912</v>
       </c>
       <c r="E27">
-        <v>-68.02500000000001</v>
+        <v>-66.566</v>
       </c>
       <c r="F27">
-        <v>36.475</v>
+        <v>37.934</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3489,28 +3489,28 @@
         <v>17.1</v>
       </c>
       <c r="M27">
-        <v>1.9514125</v>
+        <v>2.029469</v>
       </c>
       <c r="N27">
-        <v>15.1485875</v>
+        <v>15.070531</v>
       </c>
       <c r="O27">
-        <v>3.635661</v>
+        <v>3.61692744</v>
       </c>
       <c r="P27">
-        <v>11.5129265</v>
+        <v>11.45360356</v>
       </c>
       <c r="Q27">
-        <v>17.6129265</v>
+        <v>17.55360356</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1902073523587818</v>
+        <v>0.1917851210159508</v>
       </c>
       <c r="T27">
-        <v>0.7095270684139338</v>
+        <v>0.7172792330487036</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.762883296073998</v>
+        <v>8.425849323148075</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1524925895518036</v>
+        <v>0.1521646648345208</v>
       </c>
       <c r="C28">
-        <v>178.6882029702912</v>
+        <v>177.8939712000311</v>
       </c>
       <c r="D28">
-        <v>215.6222029702912</v>
+        <v>216.2869712000311</v>
       </c>
       <c r="E28">
-        <v>-66.566</v>
+        <v>-65.107</v>
       </c>
       <c r="F28">
-        <v>37.934</v>
+        <v>39.393</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3571,28 +3571,28 @@
         <v>17.1</v>
       </c>
       <c r="M28">
-        <v>2.029469</v>
+        <v>2.1075255</v>
       </c>
       <c r="N28">
-        <v>15.070531</v>
+        <v>14.9924745</v>
       </c>
       <c r="O28">
-        <v>3.61692744</v>
+        <v>3.59819388</v>
       </c>
       <c r="P28">
-        <v>11.45360356</v>
+        <v>11.39428062</v>
       </c>
       <c r="Q28">
-        <v>17.55360356</v>
+        <v>17.49428062</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1917851210159508</v>
+        <v>0.1934061162116724</v>
       </c>
       <c r="T28">
-        <v>0.7172792330487036</v>
+        <v>0.7252437857556588</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.425849323148075</v>
+        <v>8.113780829698147</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1521646648345208</v>
+        <v>0.1518367401172381</v>
       </c>
       <c r="C29">
-        <v>177.8939712000311</v>
+        <v>177.1038510977373</v>
       </c>
       <c r="D29">
-        <v>216.2869712000311</v>
+        <v>216.9558510977373</v>
       </c>
       <c r="E29">
-        <v>-65.107</v>
+        <v>-63.648</v>
       </c>
       <c r="F29">
-        <v>39.393</v>
+        <v>40.852</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3653,28 +3653,28 @@
         <v>17.1</v>
       </c>
       <c r="M29">
-        <v>2.1075255</v>
+        <v>2.185582</v>
       </c>
       <c r="N29">
-        <v>14.9924745</v>
+        <v>14.914418</v>
       </c>
       <c r="O29">
-        <v>3.59819388</v>
+        <v>3.57946032</v>
       </c>
       <c r="P29">
-        <v>11.39428062</v>
+        <v>11.33495768</v>
       </c>
       <c r="Q29">
-        <v>17.49428062</v>
+        <v>17.43495768</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1934061162116724</v>
+        <v>0.1950721390517195</v>
       </c>
       <c r="T29">
-        <v>0.7252437857556588</v>
+        <v>0.7334295760378075</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.113780829698147</v>
+        <v>7.824002942923213</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1518367401172381</v>
+        <v>0.1516851353999553</v>
       </c>
       <c r="C30">
-        <v>177.1038510977373</v>
+        <v>175.9554851668564</v>
       </c>
       <c r="D30">
-        <v>216.9558510977373</v>
+        <v>217.2664851668565</v>
       </c>
       <c r="E30">
-        <v>-63.648</v>
+        <v>-62.18899999999999</v>
       </c>
       <c r="F30">
-        <v>40.852</v>
+        <v>42.31100000000001</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -3735,45 +3735,45 @@
         <v>17.1</v>
       </c>
       <c r="M30">
-        <v>2.185582</v>
+        <v>2.2974873</v>
       </c>
       <c r="N30">
-        <v>14.914418</v>
+        <v>14.8025127</v>
       </c>
       <c r="O30">
-        <v>3.57946032</v>
+        <v>3.552603048</v>
       </c>
       <c r="P30">
-        <v>11.33495768</v>
+        <v>11.249909652</v>
       </c>
       <c r="Q30">
-        <v>17.43495768</v>
+        <v>17.349909652</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1950721390517195</v>
+        <v>0.1967850921126131</v>
       </c>
       <c r="T30">
-        <v>0.7334295760378075</v>
+        <v>0.7418459519617067</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.824002942923213</v>
+        <v>7.442913830252729</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1516851353999553</v>
+        <v>0.1513632906826725</v>
       </c>
       <c r="C31">
-        <v>175.9554851668564</v>
+        <v>175.1588941353656</v>
       </c>
       <c r="D31">
-        <v>217.2664851668565</v>
+        <v>217.9288941353656</v>
       </c>
       <c r="E31">
-        <v>-62.189</v>
+        <v>-60.73</v>
       </c>
       <c r="F31">
-        <v>42.311</v>
+        <v>43.77</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -3817,28 +3817,28 @@
         <v>17.1</v>
       </c>
       <c r="M31">
-        <v>2.2974873</v>
+        <v>2.376711</v>
       </c>
       <c r="N31">
-        <v>14.8025127</v>
+        <v>14.723289</v>
       </c>
       <c r="O31">
-        <v>3.552603048</v>
+        <v>3.53358936</v>
       </c>
       <c r="P31">
-        <v>11.249909652</v>
+        <v>11.18969964</v>
       </c>
       <c r="Q31">
-        <v>17.349909652</v>
+        <v>17.28969964</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1967850921126131</v>
+        <v>0.1985469866895322</v>
       </c>
       <c r="T31">
-        <v>0.7418459519617067</v>
+        <v>0.7505027957691457</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.442913830252729</v>
+        <v>7.194816702577637</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1513632906826725</v>
+        <v>0.1510414459653898</v>
       </c>
       <c r="C32">
-        <v>175.1588941353656</v>
+        <v>174.3663546032673</v>
       </c>
       <c r="D32">
-        <v>217.9288941353656</v>
+        <v>218.5953546032673</v>
       </c>
       <c r="E32">
-        <v>-60.73</v>
+        <v>-59.271</v>
       </c>
       <c r="F32">
-        <v>43.77</v>
+        <v>45.229</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -3899,28 +3899,28 @@
         <v>17.1</v>
       </c>
       <c r="M32">
-        <v>2.376711</v>
+        <v>2.4559347</v>
       </c>
       <c r="N32">
-        <v>14.723289</v>
+        <v>14.6440653</v>
       </c>
       <c r="O32">
-        <v>3.53358936</v>
+        <v>3.514575672</v>
       </c>
       <c r="P32">
-        <v>11.18969964</v>
+        <v>11.129489628</v>
       </c>
       <c r="Q32">
-        <v>17.28969964</v>
+        <v>17.229489628</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1985469866895322</v>
+        <v>0.2003599506744779</v>
       </c>
       <c r="T32">
-        <v>0.7505027957691457</v>
+        <v>0.7594105625854962</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.194816702577637</v>
+        <v>6.962725841204167</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1510414459653898</v>
+        <v>0.150719601248107</v>
       </c>
       <c r="C33">
-        <v>174.3663546032673</v>
+        <v>173.5779038549296</v>
       </c>
       <c r="D33">
-        <v>218.5953546032673</v>
+        <v>219.2659038549296</v>
       </c>
       <c r="E33">
-        <v>-59.271</v>
+        <v>-57.812</v>
       </c>
       <c r="F33">
-        <v>45.229</v>
+        <v>46.688</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3981,28 +3981,28 @@
         <v>17.1</v>
       </c>
       <c r="M33">
-        <v>2.4559347</v>
+        <v>2.5351584</v>
       </c>
       <c r="N33">
-        <v>14.6440653</v>
+        <v>14.5648416</v>
       </c>
       <c r="O33">
-        <v>3.514575672</v>
+        <v>3.495561984</v>
       </c>
       <c r="P33">
-        <v>11.129489628</v>
+        <v>11.069279616</v>
       </c>
       <c r="Q33">
-        <v>17.229489628</v>
+        <v>17.169279616</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2003599506744779</v>
+        <v>0.2022262371295691</v>
       </c>
       <c r="T33">
-        <v>0.7594105625854962</v>
+        <v>0.7685803225435039</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.962725841204167</v>
+        <v>6.745140658666536</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.150719601248107</v>
+        <v>0.1503977565308242</v>
       </c>
       <c r="C34">
-        <v>173.5779038549296</v>
+        <v>172.7935796336128</v>
       </c>
       <c r="D34">
-        <v>219.2659038549296</v>
+        <v>219.9405796336128</v>
       </c>
       <c r="E34">
-        <v>-57.812</v>
+        <v>-56.35299999999999</v>
       </c>
       <c r="F34">
-        <v>46.688</v>
+        <v>48.14700000000001</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -4063,28 +4063,28 @@
         <v>17.1</v>
       </c>
       <c r="M34">
-        <v>2.5351584</v>
+        <v>2.6143821</v>
       </c>
       <c r="N34">
-        <v>14.5648416</v>
+        <v>14.4856179</v>
       </c>
       <c r="O34">
-        <v>3.495561984</v>
+        <v>3.476548296</v>
       </c>
       <c r="P34">
-        <v>11.069279616</v>
+        <v>11.009069604</v>
       </c>
       <c r="Q34">
-        <v>17.169279616</v>
+        <v>17.109069604</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2022262371295691</v>
+        <v>0.2041482336280958</v>
       </c>
       <c r="T34">
-        <v>0.7685803225435039</v>
+        <v>0.7780238066793627</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.745140658666536</v>
+        <v>6.540742456888761</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1503977565308242</v>
+        <v>0.1500759118135414</v>
       </c>
       <c r="C35">
-        <v>172.7935796336128</v>
+        <v>172.0134201485512</v>
       </c>
       <c r="D35">
-        <v>219.9405796336128</v>
+        <v>220.6194201485512</v>
       </c>
       <c r="E35">
-        <v>-56.35299999999999</v>
+        <v>-54.89399999999999</v>
       </c>
       <c r="F35">
-        <v>48.14700000000001</v>
+        <v>49.60600000000001</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -4145,28 +4145,28 @@
         <v>17.1</v>
       </c>
       <c r="M35">
-        <v>2.6143821</v>
+        <v>2.693605800000001</v>
       </c>
       <c r="N35">
-        <v>14.4856179</v>
+        <v>14.4063942</v>
       </c>
       <c r="O35">
-        <v>3.476548296</v>
+        <v>3.457534608</v>
       </c>
       <c r="P35">
-        <v>11.009069604</v>
+        <v>10.948859592</v>
       </c>
       <c r="Q35">
-        <v>17.109069604</v>
+        <v>17.048859592</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2041482336280958</v>
+        <v>0.2061284724447597</v>
       </c>
       <c r="T35">
-        <v>0.7780238066793627</v>
+        <v>0.7877534570011566</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.540742456888761</v>
+        <v>6.348367678744974</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1500759118135414</v>
+        <v>0.1497540670962586</v>
       </c>
       <c r="C36">
-        <v>172.0134201485512</v>
+        <v>171.2374640821671</v>
       </c>
       <c r="D36">
-        <v>220.6194201485512</v>
+        <v>221.3024640821671</v>
       </c>
       <c r="E36">
-        <v>-54.89399999999999</v>
+        <v>-53.435</v>
       </c>
       <c r="F36">
-        <v>49.60600000000001</v>
+        <v>51.065</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -4227,28 +4227,28 @@
         <v>17.1</v>
       </c>
       <c r="M36">
-        <v>2.693605800000001</v>
+        <v>2.7728295</v>
       </c>
       <c r="N36">
-        <v>14.4063942</v>
+        <v>14.3271705</v>
       </c>
       <c r="O36">
-        <v>3.457534608</v>
+        <v>3.43852092</v>
       </c>
       <c r="P36">
-        <v>10.948859592</v>
+        <v>10.88864958</v>
       </c>
       <c r="Q36">
-        <v>17.048859592</v>
+        <v>16.98864958</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2061284724447597</v>
+        <v>0.2081696416865518</v>
       </c>
       <c r="T36">
-        <v>0.7877534570011566</v>
+        <v>0.7977824811790057</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.348367678744974</v>
+        <v>6.166985745066547</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1497540670962586</v>
+        <v>0.1497058223789759</v>
       </c>
       <c r="C37">
-        <v>171.2374640821671</v>
+        <v>169.8812174656559</v>
       </c>
       <c r="D37">
-        <v>221.3024640821671</v>
+        <v>221.4052174656559</v>
       </c>
       <c r="E37">
-        <v>-53.435</v>
+        <v>-51.97599999999999</v>
       </c>
       <c r="F37">
-        <v>51.065</v>
+        <v>52.52400000000001</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4309,45 +4309,45 @@
         <v>17.1</v>
       </c>
       <c r="M37">
-        <v>2.7728295</v>
+        <v>2.904577200000001</v>
       </c>
       <c r="N37">
-        <v>14.3271705</v>
+        <v>14.1954228</v>
       </c>
       <c r="O37">
-        <v>3.43852092</v>
+        <v>3.406901472</v>
       </c>
       <c r="P37">
-        <v>10.88864958</v>
+        <v>10.788521328</v>
       </c>
       <c r="Q37">
-        <v>16.98864958</v>
+        <v>16.888521328</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2081696416865518</v>
+        <v>0.2102745974671498</v>
       </c>
       <c r="T37">
-        <v>0.7977824811790057</v>
+        <v>0.8081249123624127</v>
       </c>
       <c r="U37">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V37">
         <v>0.24</v>
       </c>
       <c r="W37">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y37">
-        <v>6.166985745066547</v>
+        <v>5.887259598402135</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1497058223789759</v>
+        <v>0.1493915776616931</v>
       </c>
       <c r="C38">
-        <v>169.8812174656559</v>
+        <v>169.0938494799364</v>
       </c>
       <c r="D38">
-        <v>221.4052174656559</v>
+        <v>222.0768494799364</v>
       </c>
       <c r="E38">
-        <v>-51.976</v>
+        <v>-50.517</v>
       </c>
       <c r="F38">
-        <v>52.524</v>
+        <v>53.983</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -4391,28 +4391,28 @@
         <v>17.1</v>
       </c>
       <c r="M38">
-        <v>2.9045772</v>
+        <v>2.9852599</v>
       </c>
       <c r="N38">
-        <v>14.1954228</v>
+        <v>14.1147401</v>
       </c>
       <c r="O38">
-        <v>3.406901472</v>
+        <v>3.387537624</v>
       </c>
       <c r="P38">
-        <v>10.788521328</v>
+        <v>10.727202476</v>
       </c>
       <c r="Q38">
-        <v>16.888521328</v>
+        <v>16.827202476</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2102745974671498</v>
+        <v>0.2124463772407827</v>
       </c>
       <c r="T38">
-        <v>0.8081249123624126</v>
+        <v>0.818795674694499</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.887259598402136</v>
+        <v>5.728144474120996</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1493915776616931</v>
+        <v>0.1490773329444103</v>
       </c>
       <c r="C39">
-        <v>169.0938494799364</v>
+        <v>168.3105686797868</v>
       </c>
       <c r="D39">
-        <v>222.0768494799364</v>
+        <v>222.7525686797868</v>
       </c>
       <c r="E39">
-        <v>-50.517</v>
+        <v>-49.058</v>
       </c>
       <c r="F39">
-        <v>53.983</v>
+        <v>55.442</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4473,28 +4473,28 @@
         <v>17.1</v>
       </c>
       <c r="M39">
-        <v>2.9852599</v>
+        <v>3.0659426</v>
       </c>
       <c r="N39">
-        <v>14.1147401</v>
+        <v>14.0340574</v>
       </c>
       <c r="O39">
-        <v>3.387537624</v>
+        <v>3.368173776</v>
       </c>
       <c r="P39">
-        <v>10.727202476</v>
+        <v>10.665883624</v>
       </c>
       <c r="Q39">
-        <v>16.827202476</v>
+        <v>16.765883624</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2124463772407827</v>
+        <v>0.2146882144264683</v>
       </c>
       <c r="T39">
-        <v>0.818795674694499</v>
+        <v>0.8298106551663302</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.728144474120996</v>
+        <v>5.577403830065181</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1490773329444103</v>
+        <v>0.1487630882271276</v>
       </c>
       <c r="C40">
-        <v>168.3105686797868</v>
+        <v>167.5314124876413</v>
       </c>
       <c r="D40">
-        <v>222.7525686797868</v>
+        <v>223.4324124876413</v>
       </c>
       <c r="E40">
-        <v>-49.058</v>
+        <v>-47.599</v>
       </c>
       <c r="F40">
-        <v>55.442</v>
+        <v>56.901</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4555,28 +4555,28 @@
         <v>17.1</v>
       </c>
       <c r="M40">
-        <v>3.0659426</v>
+        <v>3.1466253</v>
       </c>
       <c r="N40">
-        <v>14.0340574</v>
+        <v>13.9533747</v>
       </c>
       <c r="O40">
-        <v>3.368173776</v>
+        <v>3.348809928</v>
       </c>
       <c r="P40">
-        <v>10.665883624</v>
+        <v>10.604564772</v>
       </c>
       <c r="Q40">
-        <v>16.765883624</v>
+        <v>16.704564772</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2146882144264683</v>
+        <v>0.2170035544707009</v>
       </c>
       <c r="T40">
-        <v>0.8298106551663302</v>
+        <v>0.8411867825388772</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.577403830065181</v>
+        <v>5.434393475448125</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1487630882271276</v>
+        <v>0.1484488435098448</v>
       </c>
       <c r="C41">
-        <v>167.5314124876413</v>
+        <v>166.7564187841882</v>
       </c>
       <c r="D41">
-        <v>223.4324124876413</v>
+        <v>224.1164187841882</v>
       </c>
       <c r="E41">
-        <v>-47.599</v>
+        <v>-46.13999999999999</v>
       </c>
       <c r="F41">
-        <v>56.901</v>
+        <v>58.36000000000001</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -4637,28 +4637,28 @@
         <v>17.1</v>
       </c>
       <c r="M41">
-        <v>3.1466253</v>
+        <v>3.227308</v>
       </c>
       <c r="N41">
-        <v>13.9533747</v>
+        <v>13.872692</v>
       </c>
       <c r="O41">
-        <v>3.348809928</v>
+        <v>3.32944608</v>
       </c>
       <c r="P41">
-        <v>10.604564772</v>
+        <v>10.54324592</v>
       </c>
       <c r="Q41">
-        <v>16.704564772</v>
+        <v>16.64324592</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2170035544707009</v>
+        <v>0.219396072516408</v>
       </c>
       <c r="T41">
-        <v>0.8411867825388772</v>
+        <v>0.8529421141571758</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.434393475448125</v>
+        <v>5.298533638561922</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1484488435098448</v>
+        <v>0.148134598792562</v>
       </c>
       <c r="C42">
-        <v>166.7564187841882</v>
+        <v>165.9856259154052</v>
       </c>
       <c r="D42">
-        <v>224.1164187841882</v>
+        <v>224.8046259154052</v>
       </c>
       <c r="E42">
-        <v>-46.13999999999999</v>
+        <v>-44.68099999999999</v>
       </c>
       <c r="F42">
-        <v>58.36000000000001</v>
+        <v>59.81900000000001</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -4719,28 +4719,28 @@
         <v>17.1</v>
       </c>
       <c r="M42">
-        <v>3.227308</v>
+        <v>3.307990700000001</v>
       </c>
       <c r="N42">
-        <v>13.872692</v>
+        <v>13.7920093</v>
       </c>
       <c r="O42">
-        <v>3.32944608</v>
+        <v>3.310082232</v>
       </c>
       <c r="P42">
-        <v>10.54324592</v>
+        <v>10.481927068</v>
       </c>
       <c r="Q42">
-        <v>16.64324592</v>
+        <v>16.581927068</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.219396072516408</v>
+        <v>0.2218696928687491</v>
       </c>
       <c r="T42">
-        <v>0.8529421141571758</v>
+        <v>0.8650959315930435</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.298533638561922</v>
+        <v>5.169301110792119</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.148134598792562</v>
+        <v>0.1478203540752792</v>
       </c>
       <c r="C43">
-        <v>165.9856259154052</v>
+        <v>165.2190726997254</v>
       </c>
       <c r="D43">
-        <v>224.8046259154052</v>
+        <v>225.4970726997254</v>
       </c>
       <c r="E43">
-        <v>-44.68099999999999</v>
+        <v>-43.22199999999999</v>
       </c>
       <c r="F43">
-        <v>59.81900000000001</v>
+        <v>61.27800000000001</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4801,28 +4801,28 @@
         <v>17.1</v>
       </c>
       <c r="M43">
-        <v>3.307990700000001</v>
+        <v>3.388673400000001</v>
       </c>
       <c r="N43">
-        <v>13.7920093</v>
+        <v>13.7113266</v>
       </c>
       <c r="O43">
-        <v>3.310082232</v>
+        <v>3.290718384</v>
       </c>
       <c r="P43">
-        <v>10.481927068</v>
+        <v>10.420608216</v>
       </c>
       <c r="Q43">
-        <v>16.581927068</v>
+        <v>16.520608216</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2218696928687491</v>
+        <v>0.2244286104746194</v>
       </c>
       <c r="T43">
-        <v>0.8650959315930435</v>
+        <v>0.8776688461818727</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.169301110792119</v>
+        <v>5.046222512916116</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1478203540752792</v>
+        <v>0.1475061093579965</v>
       </c>
       <c r="C44">
-        <v>165.2190726997254</v>
+        <v>164.4567984353367</v>
       </c>
       <c r="D44">
-        <v>225.4970726997254</v>
+        <v>226.1937984353367</v>
       </c>
       <c r="E44">
-        <v>-43.222</v>
+        <v>-41.763</v>
       </c>
       <c r="F44">
-        <v>61.278</v>
+        <v>62.737</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -4883,28 +4883,28 @@
         <v>17.1</v>
       </c>
       <c r="M44">
-        <v>3.3886734</v>
+        <v>3.4693561</v>
       </c>
       <c r="N44">
-        <v>13.7113266</v>
+        <v>13.6306439</v>
       </c>
       <c r="O44">
-        <v>3.290718384</v>
+        <v>3.271354536</v>
       </c>
       <c r="P44">
-        <v>10.420608216</v>
+        <v>10.359289364</v>
       </c>
       <c r="Q44">
-        <v>16.520608216</v>
+        <v>16.459289364</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2244286104746193</v>
+        <v>0.2270773146631516</v>
       </c>
       <c r="T44">
-        <v>0.8776688461818726</v>
+        <v>0.8906829156685551</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.046222512916117</v>
+        <v>4.928868500987835</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1475061093579965</v>
+        <v>0.1471918646407137</v>
       </c>
       <c r="C45">
-        <v>164.4567984353367</v>
+        <v>163.6988429076157</v>
       </c>
       <c r="D45">
-        <v>226.1937984353367</v>
+        <v>226.8948429076157</v>
       </c>
       <c r="E45">
-        <v>-41.763</v>
+        <v>-40.304</v>
       </c>
       <c r="F45">
-        <v>62.737</v>
+        <v>64.196</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -4965,28 +4965,28 @@
         <v>17.1</v>
       </c>
       <c r="M45">
-        <v>3.4693561</v>
+        <v>3.5500388</v>
       </c>
       <c r="N45">
-        <v>13.6306439</v>
+        <v>13.5499612</v>
       </c>
       <c r="O45">
-        <v>3.271354536</v>
+        <v>3.251990688</v>
       </c>
       <c r="P45">
-        <v>10.359289364</v>
+        <v>10.297970512</v>
       </c>
       <c r="Q45">
-        <v>16.459289364</v>
+        <v>16.397970512</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2270773146631516</v>
+        <v>0.2298206154298458</v>
       </c>
       <c r="T45">
-        <v>0.8906829156685551</v>
+        <v>0.9041617733511905</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.928868500987835</v>
+        <v>4.816848762329021</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1471918646407137</v>
+        <v>0.1468776199234309</v>
       </c>
       <c r="C46">
-        <v>163.6988429076157</v>
+        <v>162.945246396701</v>
       </c>
       <c r="D46">
-        <v>226.8948429076157</v>
+        <v>227.600246396701</v>
       </c>
       <c r="E46">
-        <v>-40.304</v>
+        <v>-38.845</v>
       </c>
       <c r="F46">
-        <v>64.196</v>
+        <v>65.655</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5047,28 +5047,28 @@
         <v>17.1</v>
       </c>
       <c r="M46">
-        <v>3.5500388</v>
+        <v>3.6307215</v>
       </c>
       <c r="N46">
-        <v>13.5499612</v>
+        <v>13.4692785</v>
       </c>
       <c r="O46">
-        <v>3.251990688</v>
+        <v>3.23262684</v>
       </c>
       <c r="P46">
-        <v>10.297970512</v>
+        <v>10.23665166</v>
       </c>
       <c r="Q46">
-        <v>16.397970512</v>
+        <v>16.33665166</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2298206154298458</v>
+        <v>0.2326636725880562</v>
       </c>
       <c r="T46">
-        <v>0.9041617733511905</v>
+        <v>0.9181307713131948</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.816848762329021</v>
+        <v>4.709807678721709</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1468776199234309</v>
+        <v>0.1465633752061481</v>
       </c>
       <c r="C47">
-        <v>162.945246396701</v>
+        <v>162.1960496852083</v>
       </c>
       <c r="D47">
-        <v>227.600246396701</v>
+        <v>228.3100496852083</v>
       </c>
       <c r="E47">
-        <v>-38.845</v>
+        <v>-37.386</v>
       </c>
       <c r="F47">
-        <v>65.655</v>
+        <v>67.114</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -5129,28 +5129,28 @@
         <v>17.1</v>
       </c>
       <c r="M47">
-        <v>3.6307215</v>
+        <v>3.7114042</v>
       </c>
       <c r="N47">
-        <v>13.4692785</v>
+        <v>13.3885958</v>
       </c>
       <c r="O47">
-        <v>3.23262684</v>
+        <v>3.213262992</v>
       </c>
       <c r="P47">
-        <v>10.23665166</v>
+        <v>10.175332808</v>
       </c>
       <c r="Q47">
-        <v>16.33665166</v>
+        <v>16.275332808</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2326636725880562</v>
+        <v>0.2356120281595336</v>
       </c>
       <c r="T47">
-        <v>0.9181307713131948</v>
+        <v>0.9326171395700878</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.709807678721709</v>
+        <v>4.607420555271236</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1465633752061481</v>
+        <v>0.1462491304888653</v>
       </c>
       <c r="C48">
-        <v>162.1960496852083</v>
+        <v>161.4512940660902</v>
       </c>
       <c r="D48">
-        <v>228.3100496852083</v>
+        <v>229.0242940660902</v>
       </c>
       <c r="E48">
-        <v>-37.386</v>
+        <v>-35.92699999999999</v>
       </c>
       <c r="F48">
-        <v>67.114</v>
+        <v>68.57300000000001</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -5211,28 +5211,28 @@
         <v>17.1</v>
       </c>
       <c r="M48">
-        <v>3.7114042</v>
+        <v>3.792086900000001</v>
       </c>
       <c r="N48">
-        <v>13.3885958</v>
+        <v>13.3079131</v>
       </c>
       <c r="O48">
-        <v>3.213262992</v>
+        <v>3.193899144</v>
       </c>
       <c r="P48">
-        <v>10.175332808</v>
+        <v>10.114013956</v>
       </c>
       <c r="Q48">
-        <v>16.275332808</v>
+        <v>16.214013956</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2356120281595336</v>
+        <v>0.2386716424318214</v>
       </c>
       <c r="T48">
-        <v>0.9326171395700878</v>
+        <v>0.9476501632329014</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.607420555271236</v>
+        <v>4.509390330690997</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1462491304888653</v>
+        <v>0.1468468857715826</v>
       </c>
       <c r="C49">
-        <v>161.4512940660902</v>
+        <v>158.6374726819056</v>
       </c>
       <c r="D49">
-        <v>229.0242940660902</v>
+        <v>227.6694726819056</v>
       </c>
       <c r="E49">
-        <v>-35.92699999999999</v>
+        <v>-34.46799999999999</v>
       </c>
       <c r="F49">
-        <v>68.57300000000001</v>
+        <v>70.03200000000001</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -5293,45 +5293,45 @@
         <v>17.1</v>
       </c>
       <c r="M49">
-        <v>3.792086900000001</v>
+        <v>4.047849600000001</v>
       </c>
       <c r="N49">
-        <v>13.3079131</v>
+        <v>13.0521504</v>
       </c>
       <c r="O49">
-        <v>3.193899144</v>
+        <v>3.132516096</v>
       </c>
       <c r="P49">
-        <v>10.114013956</v>
+        <v>9.919634304000001</v>
       </c>
       <c r="Q49">
-        <v>16.214013956</v>
+        <v>16.019634304</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2386716424318214</v>
+        <v>0.2418489341761204</v>
       </c>
       <c r="T49">
-        <v>0.9476501632329014</v>
+        <v>0.9632613801135156</v>
       </c>
       <c r="U49">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V49">
         <v>0.24</v>
       </c>
       <c r="W49">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.509390330690997</v>
+        <v>4.224465256811913</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1468468857715826</v>
+        <v>0.1465516410542998</v>
       </c>
       <c r="C50">
-        <v>158.6374726819056</v>
+        <v>157.8456400688832</v>
       </c>
       <c r="D50">
-        <v>227.6694726819056</v>
+        <v>228.3366400688832</v>
       </c>
       <c r="E50">
-        <v>-34.468</v>
+        <v>-33.009</v>
       </c>
       <c r="F50">
-        <v>70.032</v>
+        <v>71.491</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -5375,28 +5375,28 @@
         <v>17.1</v>
       </c>
       <c r="M50">
-        <v>4.0478496</v>
+        <v>4.1321798</v>
       </c>
       <c r="N50">
-        <v>13.0521504</v>
+        <v>12.9678202</v>
       </c>
       <c r="O50">
-        <v>3.132516096</v>
+        <v>3.112276848</v>
       </c>
       <c r="P50">
-        <v>9.919634304000002</v>
+        <v>9.855543352000002</v>
       </c>
       <c r="Q50">
-        <v>16.019634304</v>
+        <v>15.955543352</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2418489341761204</v>
+        <v>0.2451508255966663</v>
       </c>
       <c r="T50">
-        <v>0.9632613801135156</v>
+        <v>0.9794848015776831</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.224465256811913</v>
+        <v>4.138251680142282</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1465516410542998</v>
+        <v>0.146256396337017</v>
       </c>
       <c r="C51">
-        <v>157.8456400688832</v>
+        <v>157.0577291105034</v>
       </c>
       <c r="D51">
-        <v>228.3366400688832</v>
+        <v>229.0077291105034</v>
       </c>
       <c r="E51">
-        <v>-33.009</v>
+        <v>-31.55</v>
       </c>
       <c r="F51">
-        <v>71.491</v>
+        <v>72.95</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5457,28 +5457,28 @@
         <v>17.1</v>
       </c>
       <c r="M51">
-        <v>4.1321798</v>
+        <v>4.21651</v>
       </c>
       <c r="N51">
-        <v>12.9678202</v>
+        <v>12.88349</v>
       </c>
       <c r="O51">
-        <v>3.112276848</v>
+        <v>3.0920376</v>
       </c>
       <c r="P51">
-        <v>9.855543352000002</v>
+        <v>9.791452400000001</v>
       </c>
       <c r="Q51">
-        <v>15.955543352</v>
+        <v>15.8914524</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2451508255966663</v>
+        <v>0.2485847926740341</v>
       </c>
       <c r="T51">
-        <v>0.9794848015776831</v>
+        <v>0.9963571599004176</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.138251680142282</v>
+        <v>4.055486646539437</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.146256396337017</v>
+        <v>0.1473177516197343</v>
       </c>
       <c r="C52">
-        <v>157.0577291105034</v>
+        <v>153.2044822010076</v>
       </c>
       <c r="D52">
-        <v>229.0077291105034</v>
+        <v>226.6134822010077</v>
       </c>
       <c r="E52">
-        <v>-31.55</v>
+        <v>-30.09099999999999</v>
       </c>
       <c r="F52">
-        <v>72.95</v>
+        <v>74.40900000000001</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5539,45 +5539,45 @@
         <v>17.1</v>
       </c>
       <c r="M52">
-        <v>4.21651</v>
+        <v>4.561271700000001</v>
       </c>
       <c r="N52">
-        <v>12.88349</v>
+        <v>12.5387283</v>
       </c>
       <c r="O52">
-        <v>3.0920376</v>
+        <v>3.009294792</v>
       </c>
       <c r="P52">
-        <v>9.791452400000001</v>
+        <v>9.529433508</v>
       </c>
       <c r="Q52">
-        <v>15.8914524</v>
+        <v>15.629433508</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2485847926740341</v>
+        <v>0.2521589216729271</v>
       </c>
       <c r="T52">
-        <v>0.9963571599004176</v>
+        <v>1.013918185909794</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.24</v>
       </c>
       <c r="W52">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.055486646539437</v>
+        <v>3.748954485653639</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1473177516197343</v>
+        <v>0.1470491069024515</v>
       </c>
       <c r="C53">
-        <v>153.2044822010076</v>
+        <v>152.346756787232</v>
       </c>
       <c r="D53">
-        <v>226.6134822010077</v>
+        <v>227.214756787232</v>
       </c>
       <c r="E53">
-        <v>-30.09099999999999</v>
+        <v>-28.63199999999999</v>
       </c>
       <c r="F53">
-        <v>74.40900000000001</v>
+        <v>75.86800000000001</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5621,28 +5621,28 @@
         <v>17.1</v>
       </c>
       <c r="M53">
-        <v>4.561271700000001</v>
+        <v>4.650708400000001</v>
       </c>
       <c r="N53">
-        <v>12.5387283</v>
+        <v>12.4492916</v>
       </c>
       <c r="O53">
-        <v>3.009294792</v>
+        <v>2.987829984</v>
       </c>
       <c r="P53">
-        <v>9.529433508</v>
+        <v>9.461461616000001</v>
       </c>
       <c r="Q53">
-        <v>15.629433508</v>
+        <v>15.561461616</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2521589216729271</v>
+        <v>0.2558819727134406</v>
       </c>
       <c r="T53">
-        <v>1.013918185909794</v>
+        <v>1.032210921336228</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.748954485653639</v>
+        <v>3.676859207083377</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1470491069024515</v>
+        <v>0.1467804621851687</v>
       </c>
       <c r="C54">
-        <v>152.346756787232</v>
+        <v>151.492230591161</v>
       </c>
       <c r="D54">
-        <v>227.214756787232</v>
+        <v>227.819230591161</v>
       </c>
       <c r="E54">
-        <v>-28.63199999999999</v>
+        <v>-27.17299999999999</v>
       </c>
       <c r="F54">
-        <v>75.86800000000001</v>
+        <v>77.32700000000001</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5703,28 +5703,28 @@
         <v>17.1</v>
       </c>
       <c r="M54">
-        <v>4.650708400000001</v>
+        <v>4.740145100000001</v>
       </c>
       <c r="N54">
-        <v>12.4492916</v>
+        <v>12.3598549</v>
       </c>
       <c r="O54">
-        <v>2.987829984</v>
+        <v>2.966365176</v>
       </c>
       <c r="P54">
-        <v>9.461461616000001</v>
+        <v>9.393489724</v>
       </c>
       <c r="Q54">
-        <v>15.561461616</v>
+        <v>15.493489724</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2558819727134406</v>
+        <v>0.2597634514578058</v>
       </c>
       <c r="T54">
-        <v>1.032210921336228</v>
+        <v>1.051282071036127</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.676859207083377</v>
+        <v>3.607484505062935</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1467804621851687</v>
+        <v>0.1465118174678859</v>
       </c>
       <c r="C55">
-        <v>151.492230591161</v>
+        <v>150.640929214148</v>
       </c>
       <c r="D55">
-        <v>227.819230591161</v>
+        <v>228.426929214148</v>
       </c>
       <c r="E55">
-        <v>-27.17299999999999</v>
+        <v>-25.714</v>
       </c>
       <c r="F55">
-        <v>77.32700000000001</v>
+        <v>78.786</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5785,28 +5785,28 @@
         <v>17.1</v>
       </c>
       <c r="M55">
-        <v>4.740145100000001</v>
+        <v>4.8295818</v>
       </c>
       <c r="N55">
-        <v>12.3598549</v>
+        <v>12.2704182</v>
       </c>
       <c r="O55">
-        <v>2.966365176</v>
+        <v>2.944900368</v>
       </c>
       <c r="P55">
-        <v>9.393489724</v>
+        <v>9.325517832000001</v>
       </c>
       <c r="Q55">
-        <v>15.493489724</v>
+        <v>15.425517832</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2597634514578058</v>
+        <v>0.2638136901475781</v>
       </c>
       <c r="T55">
-        <v>1.051282071036127</v>
+        <v>1.071182401157761</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.607484505062935</v>
+        <v>3.54067923645066</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1465118174678859</v>
+        <v>0.1474135727506032</v>
       </c>
       <c r="C56">
-        <v>150.640929214148</v>
+        <v>147.1547867315261</v>
       </c>
       <c r="D56">
-        <v>228.426929214148</v>
+        <v>226.3997867315261</v>
       </c>
       <c r="E56">
-        <v>-25.714</v>
+        <v>-24.255</v>
       </c>
       <c r="F56">
-        <v>78.786</v>
+        <v>80.245</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -5867,45 +5867,45 @@
         <v>17.1</v>
       </c>
       <c r="M56">
-        <v>4.8295818</v>
+        <v>5.143704500000001</v>
       </c>
       <c r="N56">
-        <v>12.2704182</v>
+        <v>11.9562955</v>
       </c>
       <c r="O56">
-        <v>2.944900368</v>
+        <v>2.86951092</v>
       </c>
       <c r="P56">
-        <v>9.325517832000001</v>
+        <v>9.08678458</v>
       </c>
       <c r="Q56">
-        <v>15.425517832</v>
+        <v>15.18678458</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2638136901475781</v>
+        <v>0.2680439394457848</v>
       </c>
       <c r="T56">
-        <v>1.071182401157761</v>
+        <v>1.091967190395912</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.24</v>
       </c>
       <c r="W56">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.54067923645066</v>
+        <v>3.324452250318811</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1474135727506032</v>
+        <v>0.1471662080333204</v>
       </c>
       <c r="C57">
-        <v>147.1547867315261</v>
+        <v>146.2482718281307</v>
       </c>
       <c r="D57">
-        <v>226.3997867315261</v>
+        <v>226.9522718281307</v>
       </c>
       <c r="E57">
-        <v>-24.255</v>
+        <v>-22.79599999999999</v>
       </c>
       <c r="F57">
-        <v>80.245</v>
+        <v>81.70400000000001</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -5949,28 +5949,28 @@
         <v>17.1</v>
       </c>
       <c r="M57">
-        <v>5.143704500000001</v>
+        <v>5.237226400000001</v>
       </c>
       <c r="N57">
-        <v>11.9562955</v>
+        <v>11.8627736</v>
       </c>
       <c r="O57">
-        <v>2.86951092</v>
+        <v>2.847065664</v>
       </c>
       <c r="P57">
-        <v>9.08678458</v>
+        <v>9.015707936</v>
       </c>
       <c r="Q57">
-        <v>15.18678458</v>
+        <v>15.115707936</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2680439394457848</v>
+        <v>0.2724664728030008</v>
       </c>
       <c r="T57">
-        <v>1.091967190395912</v>
+        <v>1.113696742781252</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.324452250318811</v>
+        <v>3.265087031563119</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1471662080333204</v>
+        <v>0.1469188433160376</v>
       </c>
       <c r="C58">
-        <v>146.2482718281307</v>
+        <v>145.344459988086</v>
       </c>
       <c r="D58">
-        <v>226.9522718281307</v>
+        <v>227.5074599880861</v>
       </c>
       <c r="E58">
-        <v>-22.79599999999999</v>
+        <v>-21.33699999999999</v>
       </c>
       <c r="F58">
-        <v>81.70400000000001</v>
+        <v>83.16300000000001</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -6031,28 +6031,28 @@
         <v>17.1</v>
       </c>
       <c r="M58">
-        <v>5.237226400000001</v>
+        <v>5.330748300000001</v>
       </c>
       <c r="N58">
-        <v>11.8627736</v>
+        <v>11.7692517</v>
       </c>
       <c r="O58">
-        <v>2.847065664</v>
+        <v>2.824620408</v>
       </c>
       <c r="P58">
-        <v>9.015707936</v>
+        <v>8.944631292</v>
       </c>
       <c r="Q58">
-        <v>15.115707936</v>
+        <v>15.044631292</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2724664728030008</v>
+        <v>0.277094705386134</v>
       </c>
       <c r="T58">
-        <v>1.113696742781252</v>
+        <v>1.136436972021724</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.265087031563119</v>
+        <v>3.207804802939205</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1469188433160376</v>
+        <v>0.1466714785987548</v>
       </c>
       <c r="C59">
-        <v>145.344459988086</v>
+        <v>144.4433710973653</v>
       </c>
       <c r="D59">
-        <v>227.5074599880861</v>
+        <v>228.0653710973654</v>
       </c>
       <c r="E59">
-        <v>-21.33699999999999</v>
+        <v>-19.87799999999999</v>
       </c>
       <c r="F59">
-        <v>83.16300000000001</v>
+        <v>84.62200000000001</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -6113,28 +6113,28 @@
         <v>17.1</v>
       </c>
       <c r="M59">
-        <v>5.330748300000001</v>
+        <v>5.424270200000001</v>
       </c>
       <c r="N59">
-        <v>11.7692517</v>
+        <v>11.6757298</v>
       </c>
       <c r="O59">
-        <v>2.824620408</v>
+        <v>2.802175152</v>
       </c>
       <c r="P59">
-        <v>8.944631292</v>
+        <v>8.873554647999999</v>
       </c>
       <c r="Q59">
-        <v>15.044631292</v>
+        <v>14.973554648</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.277094705386134</v>
+        <v>0.2819433299970353</v>
       </c>
       <c r="T59">
-        <v>1.136436972021724</v>
+        <v>1.160260069321265</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.207804802939205</v>
+        <v>3.152497823578183</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1466714785987548</v>
+        <v>0.1464241138814721</v>
       </c>
       <c r="C60">
-        <v>144.4433710973653</v>
+        <v>143.5450252374847</v>
       </c>
       <c r="D60">
-        <v>228.0653710973653</v>
+        <v>228.6260252374847</v>
       </c>
       <c r="E60">
-        <v>-19.878</v>
+        <v>-18.419</v>
       </c>
       <c r="F60">
-        <v>84.622</v>
+        <v>86.081</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -6195,28 +6195,28 @@
         <v>17.1</v>
       </c>
       <c r="M60">
-        <v>5.4242702</v>
+        <v>5.5177921</v>
       </c>
       <c r="N60">
-        <v>11.6757298</v>
+        <v>11.5822079</v>
       </c>
       <c r="O60">
-        <v>2.802175152</v>
+        <v>2.779729896</v>
       </c>
       <c r="P60">
-        <v>8.873554648000001</v>
+        <v>8.802478004000001</v>
       </c>
       <c r="Q60">
-        <v>14.973554648</v>
+        <v>14.902478004</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2819433299970353</v>
+        <v>0.2870284728816392</v>
       </c>
       <c r="T60">
-        <v>1.160260069321265</v>
+        <v>1.185245268928102</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.152497823578184</v>
+        <v>3.099065657076859</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1464241138814721</v>
+        <v>0.1461767491641893</v>
       </c>
       <c r="C61">
-        <v>143.5450252374847</v>
+        <v>142.6494426879129</v>
       </c>
       <c r="D61">
-        <v>228.6260252374847</v>
+        <v>229.1894426879129</v>
       </c>
       <c r="E61">
-        <v>-18.419</v>
+        <v>-16.95999999999999</v>
       </c>
       <c r="F61">
-        <v>86.081</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -6277,28 +6277,28 @@
         <v>17.1</v>
       </c>
       <c r="M61">
-        <v>5.5177921</v>
+        <v>5.611314000000001</v>
       </c>
       <c r="N61">
-        <v>11.5822079</v>
+        <v>11.488686</v>
       </c>
       <c r="O61">
-        <v>2.779729896</v>
+        <v>2.75728464</v>
       </c>
       <c r="P61">
-        <v>8.802478004000001</v>
+        <v>8.731401360000001</v>
       </c>
       <c r="Q61">
-        <v>14.902478004</v>
+        <v>14.83140136</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2870284728816392</v>
+        <v>0.2923678729104732</v>
       </c>
       <c r="T61">
-        <v>1.185245268928102</v>
+        <v>1.21147972851528</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.099065657076859</v>
+        <v>3.047414562792244</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1461767491641893</v>
+        <v>0.1495454644469065</v>
       </c>
       <c r="C62">
-        <v>142.6494426879129</v>
+        <v>133.7484404535372</v>
       </c>
       <c r="D62">
-        <v>229.1894426879129</v>
+        <v>221.7474404535372</v>
       </c>
       <c r="E62">
-        <v>-16.95999999999999</v>
+        <v>-15.501</v>
       </c>
       <c r="F62">
-        <v>87.54000000000001</v>
+        <v>88.999</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -6359,45 +6359,45 @@
         <v>17.1</v>
       </c>
       <c r="M62">
-        <v>5.611314000000001</v>
+        <v>6.3990281</v>
       </c>
       <c r="N62">
-        <v>11.488686</v>
+        <v>10.7009719</v>
       </c>
       <c r="O62">
-        <v>2.75728464</v>
+        <v>2.568233256000001</v>
       </c>
       <c r="P62">
-        <v>8.731401360000001</v>
+        <v>8.132738644000002</v>
       </c>
       <c r="Q62">
-        <v>14.83140136</v>
+        <v>14.232738644</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2923678729104732</v>
+        <v>0.2979810883254014</v>
       </c>
       <c r="T62">
-        <v>1.21147972851528</v>
+        <v>1.239059545004366</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.24</v>
       </c>
       <c r="W62">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.047414562792244</v>
+        <v>2.672280810893767</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1495454644469065</v>
+        <v>0.1493573797296238</v>
       </c>
       <c r="C63">
-        <v>133.7484404535372</v>
+        <v>132.6921863008614</v>
       </c>
       <c r="D63">
-        <v>221.7474404535372</v>
+        <v>222.1501863008614</v>
       </c>
       <c r="E63">
-        <v>-15.501</v>
+        <v>-14.042</v>
       </c>
       <c r="F63">
-        <v>88.999</v>
+        <v>90.458</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6441,28 +6441,28 @@
         <v>17.1</v>
       </c>
       <c r="M63">
-        <v>6.3990281</v>
+        <v>6.5039302</v>
       </c>
       <c r="N63">
-        <v>10.7009719</v>
+        <v>10.5960698</v>
       </c>
       <c r="O63">
-        <v>2.568233256000001</v>
+        <v>2.543056752</v>
       </c>
       <c r="P63">
-        <v>8.132738644000002</v>
+        <v>8.053013048000002</v>
       </c>
       <c r="Q63">
-        <v>14.232738644</v>
+        <v>14.153013048</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2979810883254014</v>
+        <v>0.3038897361305888</v>
       </c>
       <c r="T63">
-        <v>1.239059545004366</v>
+        <v>1.26809093078235</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.672280810893767</v>
+        <v>2.629179507492255</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1493573797296238</v>
+        <v>0.149169295012341</v>
       </c>
       <c r="C64">
-        <v>132.6921863008614</v>
+        <v>131.6373977737144</v>
       </c>
       <c r="D64">
-        <v>222.1501863008614</v>
+        <v>222.5543977737144</v>
       </c>
       <c r="E64">
-        <v>-14.042</v>
+        <v>-12.583</v>
       </c>
       <c r="F64">
-        <v>90.458</v>
+        <v>91.917</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6523,28 +6523,28 @@
         <v>17.1</v>
       </c>
       <c r="M64">
-        <v>6.5039302</v>
+        <v>6.6088323</v>
       </c>
       <c r="N64">
-        <v>10.5960698</v>
+        <v>10.4911677</v>
       </c>
       <c r="O64">
-        <v>2.543056752</v>
+        <v>2.517880248</v>
       </c>
       <c r="P64">
-        <v>8.053013048000002</v>
+        <v>7.973287452000001</v>
       </c>
       <c r="Q64">
-        <v>14.153013048</v>
+        <v>14.073287452</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3038897361305888</v>
+        <v>0.3101177703036243</v>
       </c>
       <c r="T64">
-        <v>1.26809093078235</v>
+        <v>1.298691580656441</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.629179507492255</v>
+        <v>2.587446499436822</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.149169295012341</v>
+        <v>0.1489812102950582</v>
       </c>
       <c r="C65">
-        <v>131.6373977737144</v>
+        <v>130.5840828869789</v>
       </c>
       <c r="D65">
-        <v>222.5543977737144</v>
+        <v>222.9600828869789</v>
       </c>
       <c r="E65">
-        <v>-12.583</v>
+        <v>-11.124</v>
       </c>
       <c r="F65">
-        <v>91.917</v>
+        <v>93.376</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6605,28 +6605,28 @@
         <v>17.1</v>
       </c>
       <c r="M65">
-        <v>6.6088323</v>
+        <v>6.713734400000001</v>
       </c>
       <c r="N65">
-        <v>10.4911677</v>
+        <v>10.3862656</v>
       </c>
       <c r="O65">
-        <v>2.517880248</v>
+        <v>2.492703744</v>
       </c>
       <c r="P65">
-        <v>7.973287452000001</v>
+        <v>7.893561856000002</v>
       </c>
       <c r="Q65">
-        <v>14.073287452</v>
+        <v>13.993561856</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3101177703036243</v>
+        <v>0.3166918063751616</v>
       </c>
       <c r="T65">
-        <v>1.298691580656441</v>
+        <v>1.330992266634649</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.587446499436822</v>
+        <v>2.547017647883122</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1489812102950582</v>
+        <v>0.1487931255777754</v>
       </c>
       <c r="C66">
-        <v>130.5840828869789</v>
+        <v>129.5322497140839</v>
       </c>
       <c r="D66">
-        <v>222.9600828869789</v>
+        <v>223.3672497140839</v>
       </c>
       <c r="E66">
-        <v>-11.124</v>
+        <v>-9.664999999999992</v>
       </c>
       <c r="F66">
-        <v>93.376</v>
+        <v>94.83500000000001</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6687,28 +6687,28 @@
         <v>17.1</v>
       </c>
       <c r="M66">
-        <v>6.713734400000001</v>
+        <v>6.818636500000001</v>
       </c>
       <c r="N66">
-        <v>10.3862656</v>
+        <v>10.2813635</v>
       </c>
       <c r="O66">
-        <v>2.492703744</v>
+        <v>2.46752724</v>
       </c>
       <c r="P66">
-        <v>7.893561856000002</v>
+        <v>7.81383626</v>
       </c>
       <c r="Q66">
-        <v>13.993561856</v>
+        <v>13.91383626</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3166918063751616</v>
+        <v>0.323641501650787</v>
       </c>
       <c r="T66">
-        <v>1.330992266634649</v>
+        <v>1.365138706097326</v>
       </c>
       <c r="U66">
         <v>0.07190000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.547017647883122</v>
+        <v>2.507832760992612</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1487931255777754</v>
+        <v>0.1505612808604926</v>
       </c>
       <c r="C67">
-        <v>129.5322497140839</v>
+        <v>124.3032692468356</v>
       </c>
       <c r="D67">
-        <v>223.3672497140839</v>
+        <v>219.5972692468356</v>
       </c>
       <c r="E67">
-        <v>-9.664999999999992</v>
+        <v>-8.205999999999989</v>
       </c>
       <c r="F67">
-        <v>94.83500000000001</v>
+        <v>96.29400000000001</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6769,45 +6769,45 @@
         <v>17.1</v>
       </c>
       <c r="M67">
-        <v>6.818636500000001</v>
+        <v>7.299085200000001</v>
       </c>
       <c r="N67">
-        <v>10.2813635</v>
+        <v>9.800914800000001</v>
       </c>
       <c r="O67">
-        <v>2.46752724</v>
+        <v>2.352219552</v>
       </c>
       <c r="P67">
-        <v>7.81383626</v>
+        <v>7.448695248000001</v>
       </c>
       <c r="Q67">
-        <v>13.91383626</v>
+        <v>13.548695248</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.323641501650787</v>
+        <v>0.3310000025308608</v>
       </c>
       <c r="T67">
-        <v>1.365138706097326</v>
+        <v>1.401293759646042</v>
       </c>
       <c r="U67">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V67">
         <v>0.24</v>
       </c>
       <c r="W67">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.507832760992612</v>
+        <v>2.34275933647137</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1505612808604926</v>
+        <v>0.1504028361432099</v>
       </c>
       <c r="C68">
-        <v>124.3032692468356</v>
+        <v>123.1768991116152</v>
       </c>
       <c r="D68">
-        <v>219.5972692468356</v>
+        <v>219.9298991116152</v>
       </c>
       <c r="E68">
-        <v>-8.205999999999989</v>
+        <v>-6.746999999999986</v>
       </c>
       <c r="F68">
-        <v>96.29400000000001</v>
+        <v>97.75300000000001</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6851,28 +6851,28 @@
         <v>17.1</v>
       </c>
       <c r="M68">
-        <v>7.299085200000001</v>
+        <v>7.409677400000001</v>
       </c>
       <c r="N68">
-        <v>9.800914800000001</v>
+        <v>9.6903226</v>
       </c>
       <c r="O68">
-        <v>2.352219552</v>
+        <v>2.325677424</v>
       </c>
       <c r="P68">
-        <v>7.448695248000001</v>
+        <v>7.364645176</v>
       </c>
       <c r="Q68">
-        <v>13.548695248</v>
+        <v>13.464645176</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3310000025308608</v>
+        <v>0.3388044731612421</v>
       </c>
       <c r="T68">
-        <v>1.401293759646042</v>
+        <v>1.439640028561348</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.34275933647137</v>
+        <v>2.307792779210604</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1504028361432099</v>
+        <v>0.1502443914259271</v>
       </c>
       <c r="C69">
-        <v>123.1768991116152</v>
+        <v>122.0515381918092</v>
       </c>
       <c r="D69">
-        <v>219.9298991116152</v>
+        <v>220.2635381918092</v>
       </c>
       <c r="E69">
-        <v>-6.746999999999986</v>
+        <v>-5.287999999999982</v>
       </c>
       <c r="F69">
-        <v>97.75300000000001</v>
+        <v>99.21200000000002</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6933,28 +6933,28 @@
         <v>17.1</v>
       </c>
       <c r="M69">
-        <v>7.409677400000001</v>
+        <v>7.520269600000002</v>
       </c>
       <c r="N69">
-        <v>9.6903226</v>
+        <v>9.579730399999999</v>
       </c>
       <c r="O69">
-        <v>2.325677424</v>
+        <v>2.299135296</v>
       </c>
       <c r="P69">
-        <v>7.364645176</v>
+        <v>7.280595104</v>
       </c>
       <c r="Q69">
-        <v>13.464645176</v>
+        <v>13.380595104</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3388044731612421</v>
+        <v>0.3470967232060223</v>
       </c>
       <c r="T69">
-        <v>1.439640028561348</v>
+        <v>1.480382939283859</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.307792779210604</v>
+        <v>2.273854650104565</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1502443914259271</v>
+        <v>0.1500859467086443</v>
       </c>
       <c r="C70">
-        <v>122.0515381918092</v>
+        <v>120.9271910874099</v>
       </c>
       <c r="D70">
-        <v>220.2635381918092</v>
+        <v>220.5981910874099</v>
       </c>
       <c r="E70">
-        <v>-5.287999999999982</v>
+        <v>-3.828999999999994</v>
       </c>
       <c r="F70">
-        <v>99.21200000000002</v>
+        <v>100.671</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -7015,28 +7015,28 @@
         <v>17.1</v>
       </c>
       <c r="M70">
-        <v>7.520269600000002</v>
+        <v>7.630861800000001</v>
       </c>
       <c r="N70">
-        <v>9.579730399999999</v>
+        <v>9.4691382</v>
       </c>
       <c r="O70">
-        <v>2.299135296</v>
+        <v>2.272593168</v>
       </c>
       <c r="P70">
-        <v>7.280595104</v>
+        <v>7.196545032</v>
       </c>
       <c r="Q70">
-        <v>13.380595104</v>
+        <v>13.296545032</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3470967232060223</v>
+        <v>0.3559239571246592</v>
       </c>
       <c r="T70">
-        <v>1.480382939283859</v>
+        <v>1.523754424891695</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.273854650104565</v>
+        <v>2.240900234885658</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1500859467086443</v>
+        <v>0.1499275019913616</v>
       </c>
       <c r="C71">
-        <v>120.9271910874099</v>
+        <v>119.8038624264076</v>
       </c>
       <c r="D71">
-        <v>220.5981910874099</v>
+        <v>220.9338624264076</v>
       </c>
       <c r="E71">
-        <v>-3.828999999999994</v>
+        <v>-2.36999999999999</v>
       </c>
       <c r="F71">
-        <v>100.671</v>
+        <v>102.13</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -7097,28 +7097,28 @@
         <v>17.1</v>
       </c>
       <c r="M71">
-        <v>7.630861800000001</v>
+        <v>7.741454000000001</v>
       </c>
       <c r="N71">
-        <v>9.4691382</v>
+        <v>9.358546</v>
       </c>
       <c r="O71">
-        <v>2.272593168</v>
+        <v>2.24605104</v>
       </c>
       <c r="P71">
-        <v>7.196545032</v>
+        <v>7.11249496</v>
       </c>
       <c r="Q71">
-        <v>13.296545032</v>
+        <v>13.21249496</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3559239571246592</v>
+        <v>0.3653396733045386</v>
       </c>
       <c r="T71">
-        <v>1.523754424891695</v>
+        <v>1.570017342873386</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.240900234885658</v>
+        <v>2.208887374387292</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1499275019913616</v>
+        <v>0.1497690572740788</v>
       </c>
       <c r="C72">
-        <v>119.8038624264076</v>
+        <v>118.6815568650045</v>
       </c>
       <c r="D72">
-        <v>220.9338624264076</v>
+        <v>221.2705568650046</v>
       </c>
       <c r="E72">
-        <v>-2.36999999999999</v>
+        <v>-0.9109999999999872</v>
       </c>
       <c r="F72">
-        <v>102.13</v>
+        <v>103.589</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -7179,28 +7179,28 @@
         <v>17.1</v>
       </c>
       <c r="M72">
-        <v>7.741454000000001</v>
+        <v>7.852046200000002</v>
       </c>
       <c r="N72">
-        <v>9.358546</v>
+        <v>9.247953799999999</v>
       </c>
       <c r="O72">
-        <v>2.24605104</v>
+        <v>2.219508912</v>
       </c>
       <c r="P72">
-        <v>7.11249496</v>
+        <v>7.028444887999999</v>
       </c>
       <c r="Q72">
-        <v>13.21249496</v>
+        <v>13.128444888</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3653396733045386</v>
+        <v>0.3754047492209615</v>
       </c>
       <c r="T72">
-        <v>1.570017342873386</v>
+        <v>1.61947080692278</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.208887374387292</v>
+        <v>2.177776284607189</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1497690572740788</v>
+        <v>0.149610612556796</v>
       </c>
       <c r="C73">
-        <v>118.6815568650046</v>
+        <v>117.5602790878293</v>
       </c>
       <c r="D73">
-        <v>221.2705568650046</v>
+        <v>221.6082790878293</v>
       </c>
       <c r="E73">
-        <v>-0.9110000000000014</v>
+        <v>0.5480000000000018</v>
       </c>
       <c r="F73">
-        <v>103.589</v>
+        <v>105.048</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7261,28 +7261,28 @@
         <v>17.1</v>
       </c>
       <c r="M73">
-        <v>7.8520462</v>
+        <v>7.962638400000001</v>
       </c>
       <c r="N73">
-        <v>9.247953800000001</v>
+        <v>9.1373616</v>
       </c>
       <c r="O73">
-        <v>2.219508912</v>
+        <v>2.192966784</v>
       </c>
       <c r="P73">
-        <v>7.028444888000001</v>
+        <v>6.944394816000001</v>
       </c>
       <c r="Q73">
-        <v>13.128444888</v>
+        <v>13.044394816</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3754047492209613</v>
+        <v>0.3861887591314143</v>
       </c>
       <c r="T73">
-        <v>1.619470806922779</v>
+        <v>1.672456661261415</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.17777628460719</v>
+        <v>2.147529391765423</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.149610612556796</v>
+        <v>0.1494521678395132</v>
       </c>
       <c r="C74">
-        <v>117.5602790878293</v>
+        <v>116.4400338081547</v>
       </c>
       <c r="D74">
-        <v>221.6082790878293</v>
+        <v>221.9470338081547</v>
       </c>
       <c r="E74">
-        <v>0.5480000000000018</v>
+        <v>2.007000000000005</v>
       </c>
       <c r="F74">
-        <v>105.048</v>
+        <v>106.507</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7343,28 +7343,28 @@
         <v>17.1</v>
       </c>
       <c r="M74">
-        <v>7.962638400000001</v>
+        <v>8.0732306</v>
       </c>
       <c r="N74">
-        <v>9.1373616</v>
+        <v>9.026769400000001</v>
       </c>
       <c r="O74">
-        <v>2.192966784</v>
+        <v>2.166424656</v>
       </c>
       <c r="P74">
-        <v>6.944394816000001</v>
+        <v>6.860344744000001</v>
       </c>
       <c r="Q74">
-        <v>13.044394816</v>
+        <v>12.960344744</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3861887591314143</v>
+        <v>0.3977715845907898</v>
       </c>
       <c r="T74">
-        <v>1.672456661261415</v>
+        <v>1.72936739369921</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.147529391765423</v>
+        <v>2.118111180919321</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1494521678395132</v>
+        <v>0.1492937231222305</v>
       </c>
       <c r="C75">
-        <v>116.4400338081547</v>
+        <v>115.3208257681168</v>
       </c>
       <c r="D75">
-        <v>221.9470338081547</v>
+        <v>222.2868257681168</v>
       </c>
       <c r="E75">
-        <v>2.007000000000005</v>
+        <v>3.466000000000008</v>
       </c>
       <c r="F75">
-        <v>106.507</v>
+        <v>107.966</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -7425,28 +7425,28 @@
         <v>17.1</v>
       </c>
       <c r="M75">
-        <v>8.0732306</v>
+        <v>8.183822800000002</v>
       </c>
       <c r="N75">
-        <v>9.026769400000001</v>
+        <v>8.9161772</v>
       </c>
       <c r="O75">
-        <v>2.166424656</v>
+        <v>2.139882528</v>
       </c>
       <c r="P75">
-        <v>6.860344744000001</v>
+        <v>6.776294672000001</v>
       </c>
       <c r="Q75">
-        <v>12.960344744</v>
+        <v>12.876294672</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3977715845907898</v>
+        <v>0.4102453966239633</v>
       </c>
       <c r="T75">
-        <v>1.72936739369921</v>
+        <v>1.790655874786065</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.118111180919321</v>
+        <v>2.089488056852844</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1492937231222305</v>
+        <v>0.1491352784049477</v>
       </c>
       <c r="C76">
-        <v>115.3208257681168</v>
+        <v>114.2026597389364</v>
       </c>
       <c r="D76">
-        <v>222.2868257681168</v>
+        <v>222.6276597389364</v>
       </c>
       <c r="E76">
-        <v>3.466000000000008</v>
+        <v>4.925000000000011</v>
       </c>
       <c r="F76">
-        <v>107.966</v>
+        <v>109.425</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7507,28 +7507,28 @@
         <v>17.1</v>
       </c>
       <c r="M76">
-        <v>8.183822800000002</v>
+        <v>8.294415000000001</v>
       </c>
       <c r="N76">
-        <v>8.9161772</v>
+        <v>8.805585000000001</v>
       </c>
       <c r="O76">
-        <v>2.139882528</v>
+        <v>2.1133404</v>
       </c>
       <c r="P76">
-        <v>6.776294672000001</v>
+        <v>6.6922446</v>
       </c>
       <c r="Q76">
-        <v>12.876294672</v>
+        <v>12.7922446</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4102453966239633</v>
+        <v>0.4237171136197908</v>
       </c>
       <c r="T76">
-        <v>1.790655874786065</v>
+        <v>1.856847434359869</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.089488056852844</v>
+        <v>2.061628216094806</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1491352784049477</v>
+        <v>0.1489768336876649</v>
       </c>
       <c r="C77">
-        <v>114.2026597389364</v>
+        <v>113.0855405211423</v>
       </c>
       <c r="D77">
-        <v>222.6276597389364</v>
+        <v>222.9695405211423</v>
       </c>
       <c r="E77">
-        <v>4.925000000000011</v>
+        <v>6.384</v>
       </c>
       <c r="F77">
-        <v>109.425</v>
+        <v>110.884</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -7589,28 +7589,28 @@
         <v>17.1</v>
       </c>
       <c r="M77">
-        <v>8.294415000000001</v>
+        <v>8.4050072</v>
       </c>
       <c r="N77">
-        <v>8.805585000000001</v>
+        <v>8.694992800000001</v>
       </c>
       <c r="O77">
-        <v>2.1133404</v>
+        <v>2.086798272</v>
       </c>
       <c r="P77">
-        <v>6.6922446</v>
+        <v>6.608194528000001</v>
       </c>
       <c r="Q77">
-        <v>12.7922446</v>
+        <v>12.708194528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4237171136197908</v>
+        <v>0.4383114736986038</v>
       </c>
       <c r="T77">
-        <v>1.856847434359869</v>
+        <v>1.92855495723149</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.061628216094806</v>
+        <v>2.034501529040927</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1489768336876649</v>
+        <v>0.1488183889703821</v>
       </c>
       <c r="C78">
-        <v>113.0855405211423</v>
+        <v>111.9694729447963</v>
       </c>
       <c r="D78">
-        <v>222.9695405211423</v>
+        <v>223.3124729447963</v>
       </c>
       <c r="E78">
-        <v>6.384</v>
+        <v>7.843000000000004</v>
       </c>
       <c r="F78">
-        <v>110.884</v>
+        <v>112.343</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7671,28 +7671,28 @@
         <v>17.1</v>
       </c>
       <c r="M78">
-        <v>8.4050072</v>
+        <v>8.515599400000001</v>
       </c>
       <c r="N78">
-        <v>8.694992800000001</v>
+        <v>8.5844006</v>
       </c>
       <c r="O78">
-        <v>2.086798272</v>
+        <v>2.060256144</v>
       </c>
       <c r="P78">
-        <v>6.608194528000001</v>
+        <v>6.524144456</v>
       </c>
       <c r="Q78">
-        <v>12.708194528</v>
+        <v>12.624144456</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4383114736986038</v>
+        <v>0.4541749085668789</v>
       </c>
       <c r="T78">
-        <v>1.92855495723149</v>
+        <v>2.006497916874557</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.034501529040927</v>
+        <v>2.008079431261175</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1488183889703821</v>
+        <v>0.1570777042530994</v>
       </c>
       <c r="C79">
-        <v>111.9694729447963</v>
+        <v>93.93565112407244</v>
       </c>
       <c r="D79">
-        <v>223.3124729447963</v>
+        <v>206.7376511240724</v>
       </c>
       <c r="E79">
-        <v>7.843000000000004</v>
+        <v>9.302000000000007</v>
       </c>
       <c r="F79">
-        <v>112.343</v>
+        <v>113.802</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7753,45 +7753,45 @@
         <v>17.1</v>
       </c>
       <c r="M79">
-        <v>8.515599400000001</v>
+        <v>10.24218</v>
       </c>
       <c r="N79">
-        <v>8.5844006</v>
+        <v>6.857820000000002</v>
       </c>
       <c r="O79">
-        <v>2.060256144</v>
+        <v>1.6458768</v>
       </c>
       <c r="P79">
-        <v>6.524144456</v>
+        <v>5.211943200000002</v>
       </c>
       <c r="Q79">
-        <v>12.624144456</v>
+        <v>11.3119432</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4541749085668789</v>
+        <v>0.4714804738777244</v>
       </c>
       <c r="T79">
-        <v>2.006497916874557</v>
+        <v>2.091526600121538</v>
       </c>
       <c r="U79">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V79">
         <v>0.24</v>
       </c>
       <c r="W79">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.008079431261175</v>
+        <v>1.669566439957119</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1570777042530994</v>
+        <v>0.1570271795358166</v>
       </c>
       <c r="C80">
-        <v>93.93565112407244</v>
+        <v>92.57056127641413</v>
       </c>
       <c r="D80">
-        <v>206.7376511240724</v>
+        <v>206.8315612764141</v>
       </c>
       <c r="E80">
-        <v>9.302000000000007</v>
+        <v>10.76100000000001</v>
       </c>
       <c r="F80">
-        <v>113.802</v>
+        <v>115.261</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7835,28 +7835,28 @@
         <v>17.1</v>
       </c>
       <c r="M80">
-        <v>10.24218</v>
+        <v>10.37349</v>
       </c>
       <c r="N80">
-        <v>6.857820000000002</v>
+        <v>6.726510000000001</v>
       </c>
       <c r="O80">
-        <v>1.6458768</v>
+        <v>1.6143624</v>
       </c>
       <c r="P80">
-        <v>5.211943200000002</v>
+        <v>5.112147600000001</v>
       </c>
       <c r="Q80">
-        <v>11.3119432</v>
+        <v>11.2121476</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4714804738777244</v>
+        <v>0.4904341882657934</v>
       </c>
       <c r="T80">
-        <v>2.091526600121538</v>
+        <v>2.184653253201565</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.669566439957119</v>
+        <v>1.648432687552598</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1570271795358166</v>
+        <v>0.1569766548185338</v>
       </c>
       <c r="C81">
-        <v>92.57056127641413</v>
+        <v>91.20555678451522</v>
       </c>
       <c r="D81">
-        <v>206.8315612764141</v>
+        <v>206.9255567845152</v>
       </c>
       <c r="E81">
-        <v>10.76100000000001</v>
+        <v>12.22000000000001</v>
       </c>
       <c r="F81">
-        <v>115.261</v>
+        <v>116.72</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7917,28 +7917,28 @@
         <v>17.1</v>
       </c>
       <c r="M81">
-        <v>10.37349</v>
+        <v>10.5048</v>
       </c>
       <c r="N81">
-        <v>6.726510000000001</v>
+        <v>6.5952</v>
       </c>
       <c r="O81">
-        <v>1.6143624</v>
+        <v>1.582848</v>
       </c>
       <c r="P81">
-        <v>5.112147600000001</v>
+        <v>5.012352</v>
       </c>
       <c r="Q81">
-        <v>11.2121476</v>
+        <v>11.112352</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4904341882657934</v>
+        <v>0.5112832740926692</v>
       </c>
       <c r="T81">
-        <v>2.184653253201565</v>
+        <v>2.287092571589596</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.648432687552598</v>
+        <v>1.62782727895819</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1569766548185338</v>
+        <v>0.1569261301012511</v>
       </c>
       <c r="C82">
-        <v>91.20555678451522</v>
+        <v>89.84063776479941</v>
       </c>
       <c r="D82">
-        <v>206.9255567845152</v>
+        <v>207.0196377647994</v>
       </c>
       <c r="E82">
-        <v>12.22000000000001</v>
+        <v>13.67900000000002</v>
       </c>
       <c r="F82">
-        <v>116.72</v>
+        <v>118.179</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -7999,28 +7999,28 @@
         <v>17.1</v>
       </c>
       <c r="M82">
-        <v>10.5048</v>
+        <v>10.63611</v>
       </c>
       <c r="N82">
-        <v>6.5952</v>
+        <v>6.463890000000001</v>
       </c>
       <c r="O82">
-        <v>1.582848</v>
+        <v>1.5513336</v>
       </c>
       <c r="P82">
-        <v>5.012352</v>
+        <v>4.912556400000001</v>
       </c>
       <c r="Q82">
-        <v>11.112352</v>
+        <v>11.0125564</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5112832740926692</v>
+        <v>0.5343270005329004</v>
       </c>
       <c r="T82">
-        <v>2.287092571589596</v>
+        <v>2.400314976123734</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.62782727895819</v>
+        <v>1.607730645884633</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1569261301012511</v>
+        <v>0.1568756053839682</v>
       </c>
       <c r="C83">
-        <v>89.84063776479941</v>
+        <v>88.4758043339025</v>
       </c>
       <c r="D83">
-        <v>207.0196377647994</v>
+        <v>207.1138043339025</v>
       </c>
       <c r="E83">
-        <v>13.67900000000002</v>
+        <v>15.13800000000002</v>
       </c>
       <c r="F83">
-        <v>118.179</v>
+        <v>119.638</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -8081,28 +8081,28 @@
         <v>17.1</v>
       </c>
       <c r="M83">
-        <v>10.63611</v>
+        <v>10.76742</v>
       </c>
       <c r="N83">
-        <v>6.463890000000001</v>
+        <v>6.33258</v>
       </c>
       <c r="O83">
-        <v>1.5513336</v>
+        <v>1.5198192</v>
       </c>
       <c r="P83">
-        <v>4.912556400000001</v>
+        <v>4.8127608</v>
       </c>
       <c r="Q83">
-        <v>11.0125564</v>
+        <v>10.9127608</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5343270005329004</v>
+        <v>0.559931141022046</v>
       </c>
       <c r="T83">
-        <v>2.400314976123734</v>
+        <v>2.526117647828332</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.607730645884633</v>
+        <v>1.588124174593357</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1568756053839682</v>
+        <v>0.1568250806666855</v>
       </c>
       <c r="C84">
-        <v>88.4758043339025</v>
+        <v>87.11105660867216</v>
       </c>
       <c r="D84">
-        <v>207.1138043339025</v>
+        <v>207.2080566086722</v>
       </c>
       <c r="E84">
-        <v>15.13800000000002</v>
+        <v>16.59700000000001</v>
       </c>
       <c r="F84">
-        <v>119.638</v>
+        <v>121.097</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -8163,28 +8163,28 @@
         <v>17.1</v>
       </c>
       <c r="M84">
-        <v>10.76742</v>
+        <v>10.89873</v>
       </c>
       <c r="N84">
-        <v>6.33258</v>
+        <v>6.201270000000001</v>
       </c>
       <c r="O84">
-        <v>1.5198192</v>
+        <v>1.4883048</v>
       </c>
       <c r="P84">
-        <v>4.8127608</v>
+        <v>4.712965200000001</v>
       </c>
       <c r="Q84">
-        <v>10.9127608</v>
+        <v>10.8129652</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.559931141022046</v>
+        <v>0.5885475333334443</v>
       </c>
       <c r="T84">
-        <v>2.526117647828332</v>
+        <v>2.666720633851119</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.588124174593357</v>
+        <v>1.568990148393437</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1568250806666855</v>
+        <v>0.1567745559494027</v>
       </c>
       <c r="C85">
-        <v>87.11105660867216</v>
+        <v>85.74639470616941</v>
       </c>
       <c r="D85">
-        <v>207.2080566086722</v>
+        <v>207.3023947061694</v>
       </c>
       <c r="E85">
-        <v>16.59700000000001</v>
+        <v>18.05600000000001</v>
       </c>
       <c r="F85">
-        <v>121.097</v>
+        <v>122.556</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -8245,28 +8245,28 @@
         <v>17.1</v>
       </c>
       <c r="M85">
-        <v>10.89873</v>
+        <v>11.03004</v>
       </c>
       <c r="N85">
-        <v>6.201270000000001</v>
+        <v>6.06996</v>
       </c>
       <c r="O85">
-        <v>1.4883048</v>
+        <v>1.4567904</v>
       </c>
       <c r="P85">
-        <v>4.712965200000001</v>
+        <v>4.6131696</v>
       </c>
       <c r="Q85">
-        <v>10.8129652</v>
+        <v>10.7131696</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5885475333334443</v>
+        <v>0.6207409746837673</v>
       </c>
       <c r="T85">
-        <v>2.666720633851119</v>
+        <v>2.824898993126754</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.568990148393437</v>
+        <v>1.550311694245896</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1567745559494027</v>
+        <v>0.1567240312321199</v>
       </c>
       <c r="C86">
-        <v>85.74639470616943</v>
+        <v>84.38181874366815</v>
       </c>
       <c r="D86">
-        <v>207.3023947061694</v>
+        <v>207.3968187436681</v>
       </c>
       <c r="E86">
-        <v>18.056</v>
+        <v>19.515</v>
       </c>
       <c r="F86">
-        <v>122.556</v>
+        <v>124.015</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -8327,28 +8327,28 @@
         <v>17.1</v>
       </c>
       <c r="M86">
-        <v>11.03004</v>
+        <v>11.16135</v>
       </c>
       <c r="N86">
-        <v>6.069960000000002</v>
+        <v>5.938650000000003</v>
       </c>
       <c r="O86">
-        <v>1.4567904</v>
+        <v>1.425276000000001</v>
       </c>
       <c r="P86">
-        <v>4.613169600000001</v>
+        <v>4.513374000000002</v>
       </c>
       <c r="Q86">
-        <v>10.7131696</v>
+        <v>10.613374</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6207409746837669</v>
+        <v>0.6572268748807996</v>
       </c>
       <c r="T86">
-        <v>2.824898993126752</v>
+        <v>3.004167800305805</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.550311694245896</v>
+        <v>1.532072733137121</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1567240312321199</v>
+        <v>0.1566735065148372</v>
       </c>
       <c r="C87">
-        <v>84.38181874366815</v>
+        <v>83.01732883865613</v>
       </c>
       <c r="D87">
-        <v>207.3968187436681</v>
+        <v>207.4913288386561</v>
       </c>
       <c r="E87">
-        <v>19.515</v>
+        <v>20.974</v>
       </c>
       <c r="F87">
-        <v>124.015</v>
+        <v>125.474</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -8409,28 +8409,28 @@
         <v>17.1</v>
       </c>
       <c r="M87">
-        <v>11.16135</v>
+        <v>11.29266</v>
       </c>
       <c r="N87">
-        <v>5.938650000000003</v>
+        <v>5.807340000000002</v>
       </c>
       <c r="O87">
-        <v>1.425276000000001</v>
+        <v>1.3937616</v>
       </c>
       <c r="P87">
-        <v>4.513374000000002</v>
+        <v>4.413578400000001</v>
       </c>
       <c r="Q87">
-        <v>10.613374</v>
+        <v>10.5135784</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6572268748807996</v>
+        <v>0.6989250465345512</v>
       </c>
       <c r="T87">
-        <v>3.004167800305805</v>
+        <v>3.209046437081864</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.532072733137121</v>
+        <v>1.514257933914596</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1566735065148372</v>
+        <v>0.198682336478023</v>
       </c>
       <c r="C88">
-        <v>83.01732883865613</v>
+        <v>24.54410369779701</v>
       </c>
       <c r="D88">
-        <v>207.4913288386561</v>
+        <v>150.477103697797</v>
       </c>
       <c r="E88">
-        <v>20.974</v>
+        <v>22.43300000000001</v>
       </c>
       <c r="F88">
-        <v>125.474</v>
+        <v>126.933</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -8491,45 +8491,45 @@
         <v>17.1</v>
       </c>
       <c r="M88">
-        <v>11.29266</v>
+        <v>18.6337644</v>
       </c>
       <c r="N88">
-        <v>5.807340000000002</v>
+        <v>-1.533764400000003</v>
       </c>
       <c r="O88">
-        <v>1.3937616</v>
+        <v>-0.3681034560000006</v>
       </c>
       <c r="P88">
-        <v>4.413578400000001</v>
+        <v>-1.165660944000002</v>
       </c>
       <c r="Q88">
-        <v>10.5135784</v>
+        <v>4.934339055999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.6989250465345512</v>
+        <v>0.7622707066032349</v>
       </c>
       <c r="T88">
-        <v>3.209046437081864</v>
+        <v>3.52028724131468</v>
       </c>
       <c r="U88">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.24</v>
+        <v>0.2202453520341815</v>
       </c>
       <c r="W88">
-        <v>0.0684</v>
+        <v>0.1144679823213822</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y88">
-        <v>1.514257933914596</v>
+        <v>0.9176889668090897</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.198682336478023</v>
+        <v>0.199692336478023</v>
       </c>
       <c r="C89">
-        <v>24.54410369779701</v>
+        <v>22.09751797252292</v>
       </c>
       <c r="D89">
-        <v>150.477103697797</v>
+        <v>149.4895179725229</v>
       </c>
       <c r="E89">
-        <v>22.43300000000001</v>
+        <v>23.892</v>
       </c>
       <c r="F89">
-        <v>126.933</v>
+        <v>128.392</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -8573,37 +8573,37 @@
         <v>17.1</v>
       </c>
       <c r="M89">
-        <v>18.6337644</v>
+        <v>18.8479456</v>
       </c>
       <c r="N89">
-        <v>-1.533764400000003</v>
+        <v>-1.747945600000001</v>
       </c>
       <c r="O89">
-        <v>-0.3681034560000006</v>
+        <v>-0.4195069440000003</v>
       </c>
       <c r="P89">
-        <v>-1.165660944000002</v>
+        <v>-1.328438656000001</v>
       </c>
       <c r="Q89">
-        <v>4.934339055999997</v>
+        <v>4.771561343999998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7622707066032349</v>
+        <v>0.8219765988201713</v>
       </c>
       <c r="T89">
-        <v>3.52028724131468</v>
+        <v>3.813644511424236</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2202453520341815</v>
+        <v>0.217742563942884</v>
       </c>
       <c r="W89">
-        <v>0.1144679823213822</v>
+        <v>0.1148353916131846</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9176889668090897</v>
+        <v>0.9072606830953501</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.199692336478023</v>
+        <v>0.200702336478023</v>
       </c>
       <c r="C90">
-        <v>22.09751797252292</v>
+        <v>19.66381083391454</v>
       </c>
       <c r="D90">
-        <v>149.4895179725229</v>
+        <v>148.5148108339145</v>
       </c>
       <c r="E90">
-        <v>23.892</v>
+        <v>25.351</v>
       </c>
       <c r="F90">
-        <v>128.392</v>
+        <v>129.851</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -8655,37 +8655,37 @@
         <v>17.1</v>
       </c>
       <c r="M90">
-        <v>18.8479456</v>
+        <v>19.0621268</v>
       </c>
       <c r="N90">
-        <v>-1.747945600000001</v>
+        <v>-1.9621268</v>
       </c>
       <c r="O90">
-        <v>-0.4195069440000003</v>
+        <v>-0.470910432</v>
       </c>
       <c r="P90">
-        <v>-1.328438656000001</v>
+        <v>-1.491216368</v>
       </c>
       <c r="Q90">
-        <v>4.771561343999998</v>
+        <v>4.608783632</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8219765988201713</v>
+        <v>0.892538107803823</v>
       </c>
       <c r="T90">
-        <v>3.813644511424236</v>
+        <v>4.160339467008257</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.217742563942884</v>
+        <v>0.2152960182806044</v>
       </c>
       <c r="W90">
-        <v>0.1148353916131846</v>
+        <v>0.1151945445164073</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9072606830953501</v>
+        <v>0.8970667428358519</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.200702336478023</v>
+        <v>0.2017123364780231</v>
       </c>
       <c r="C91">
-        <v>19.66381083391454</v>
+        <v>17.24273199954723</v>
       </c>
       <c r="D91">
-        <v>148.5148108339145</v>
+        <v>147.5527319995472</v>
       </c>
       <c r="E91">
-        <v>25.351</v>
+        <v>26.81</v>
       </c>
       <c r="F91">
-        <v>129.851</v>
+        <v>131.31</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -8737,37 +8737,37 @@
         <v>17.1</v>
       </c>
       <c r="M91">
-        <v>19.0621268</v>
+        <v>19.276308</v>
       </c>
       <c r="N91">
-        <v>-1.9621268</v>
+        <v>-2.176308000000002</v>
       </c>
       <c r="O91">
-        <v>-0.470910432</v>
+        <v>-0.5223139200000005</v>
       </c>
       <c r="P91">
-        <v>-1.491216368</v>
+        <v>-1.653994080000002</v>
       </c>
       <c r="Q91">
-        <v>4.608783632</v>
+        <v>4.446005919999998</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.892538107803823</v>
+        <v>0.9772119185842058</v>
       </c>
       <c r="T91">
-        <v>4.160339467008257</v>
+        <v>4.576373413709085</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2152960182806044</v>
+        <v>0.2129038402997088</v>
       </c>
       <c r="W91">
-        <v>0.1151945445164073</v>
+        <v>0.1155457162440028</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8970667428358519</v>
+        <v>0.8870993345821201</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2017123364780231</v>
+        <v>0.202722336478023</v>
       </c>
       <c r="C92">
-        <v>17.24273199954723</v>
+        <v>14.83403763057248</v>
       </c>
       <c r="D92">
-        <v>147.5527319995472</v>
+        <v>146.6030376305725</v>
       </c>
       <c r="E92">
-        <v>26.81</v>
+        <v>28.26900000000001</v>
       </c>
       <c r="F92">
-        <v>131.31</v>
+        <v>132.769</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -8819,37 +8819,37 @@
         <v>17.1</v>
       </c>
       <c r="M92">
-        <v>19.276308</v>
+        <v>19.4904892</v>
       </c>
       <c r="N92">
-        <v>-2.176308000000002</v>
+        <v>-2.390489200000001</v>
       </c>
       <c r="O92">
-        <v>-0.5223139200000005</v>
+        <v>-0.5737174080000003</v>
       </c>
       <c r="P92">
-        <v>-1.653994080000002</v>
+        <v>-1.816771792000001</v>
       </c>
       <c r="Q92">
-        <v>4.446005919999998</v>
+        <v>4.283228207999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9772119185842058</v>
+        <v>1.080702131760229</v>
       </c>
       <c r="T92">
-        <v>4.576373413709085</v>
+        <v>5.084859348565649</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2129038402997088</v>
+        <v>0.2105642376590527</v>
       </c>
       <c r="W92">
-        <v>0.1155457162440028</v>
+        <v>0.1158891699116511</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8870993345821201</v>
+        <v>0.8773509902460529</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.202722336478023</v>
+        <v>0.2037323364780231</v>
       </c>
       <c r="C93">
-        <v>14.83403763057248</v>
+        <v>12.43749012567955</v>
       </c>
       <c r="D93">
-        <v>146.6030376305725</v>
+        <v>145.6654901256796</v>
       </c>
       <c r="E93">
-        <v>28.26900000000001</v>
+        <v>29.72800000000001</v>
       </c>
       <c r="F93">
-        <v>132.769</v>
+        <v>134.228</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -8901,37 +8901,37 @@
         <v>17.1</v>
       </c>
       <c r="M93">
-        <v>19.4904892</v>
+        <v>19.7046704</v>
       </c>
       <c r="N93">
-        <v>-2.390489200000001</v>
+        <v>-2.604670400000003</v>
       </c>
       <c r="O93">
-        <v>-0.5737174080000003</v>
+        <v>-0.6251208960000008</v>
       </c>
       <c r="P93">
-        <v>-1.816771792000001</v>
+        <v>-1.979549504000003</v>
       </c>
       <c r="Q93">
-        <v>4.283228207999999</v>
+        <v>4.120450495999997</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.080702131760229</v>
+        <v>1.210064898230258</v>
       </c>
       <c r="T93">
-        <v>5.084859348565649</v>
+        <v>5.720466767136358</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2105642376590527</v>
+        <v>0.2082754959453673</v>
       </c>
       <c r="W93">
-        <v>0.1158891699116511</v>
+        <v>0.1162251571952201</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8773509902460529</v>
+        <v>0.8678145664390304</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2037323364780231</v>
+        <v>0.204742336478023</v>
       </c>
       <c r="C94">
-        <v>12.43749012567955</v>
+        <v>10.05285792291349</v>
       </c>
       <c r="D94">
-        <v>145.6654901256796</v>
+        <v>144.7398579229135</v>
       </c>
       <c r="E94">
-        <v>29.72800000000001</v>
+        <v>31.18700000000001</v>
       </c>
       <c r="F94">
-        <v>134.228</v>
+        <v>135.687</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -8983,37 +8983,37 @@
         <v>17.1</v>
       </c>
       <c r="M94">
-        <v>19.7046704</v>
+        <v>19.9188516</v>
       </c>
       <c r="N94">
-        <v>-2.604670400000003</v>
+        <v>-2.818851600000002</v>
       </c>
       <c r="O94">
-        <v>-0.6251208960000008</v>
+        <v>-0.6765243840000005</v>
       </c>
       <c r="P94">
-        <v>-1.979549504000003</v>
+        <v>-2.142327216000002</v>
       </c>
       <c r="Q94">
-        <v>4.120450495999997</v>
+        <v>3.957672783999998</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.210064898230258</v>
+        <v>1.376388455120295</v>
       </c>
       <c r="T94">
-        <v>5.720466767136358</v>
+        <v>6.537676305298695</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2082754959453673</v>
+        <v>0.2060359744835892</v>
       </c>
       <c r="W94">
-        <v>0.1162251571952201</v>
+        <v>0.1165539189458091</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8678145664390304</v>
+        <v>0.8584832270149549</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.204742336478023</v>
+        <v>0.205752336478023</v>
       </c>
       <c r="C95">
-        <v>10.05285792291349</v>
+        <v>7.679915309000933</v>
       </c>
       <c r="D95">
-        <v>144.7398579229135</v>
+        <v>143.8259153090009</v>
       </c>
       <c r="E95">
-        <v>31.18700000000001</v>
+        <v>32.64600000000002</v>
       </c>
       <c r="F95">
-        <v>135.687</v>
+        <v>137.146</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -9065,37 +9065,37 @@
         <v>17.1</v>
       </c>
       <c r="M95">
-        <v>19.9188516</v>
+        <v>20.13303280000001</v>
       </c>
       <c r="N95">
-        <v>-2.818851600000002</v>
+        <v>-3.033032800000004</v>
       </c>
       <c r="O95">
-        <v>-0.6765243840000005</v>
+        <v>-0.7279278720000011</v>
       </c>
       <c r="P95">
-        <v>-2.142327216000002</v>
+        <v>-2.305104928000003</v>
       </c>
       <c r="Q95">
-        <v>3.957672783999998</v>
+        <v>3.794895071999997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.376388455120295</v>
+        <v>1.598153197640344</v>
       </c>
       <c r="T95">
-        <v>6.537676305298695</v>
+        <v>7.627289022848479</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2060359744835892</v>
+        <v>0.2038441024146148</v>
       </c>
       <c r="W95">
-        <v>0.1165539189458091</v>
+        <v>0.1168756857655346</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8584832270149549</v>
+        <v>0.8493504267275617</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.205752336478023</v>
+        <v>0.206762336478023</v>
       </c>
       <c r="C96">
-        <v>7.679915309000933</v>
+        <v>5.318442235854889</v>
       </c>
       <c r="D96">
-        <v>143.8259153090009</v>
+        <v>142.9234422358549</v>
       </c>
       <c r="E96">
-        <v>32.64600000000002</v>
+        <v>34.10500000000002</v>
       </c>
       <c r="F96">
-        <v>137.146</v>
+        <v>138.605</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -9147,37 +9147,37 @@
         <v>17.1</v>
       </c>
       <c r="M96">
-        <v>20.13303280000001</v>
+        <v>20.347214</v>
       </c>
       <c r="N96">
-        <v>-3.033032800000004</v>
+        <v>-3.247214000000003</v>
       </c>
       <c r="O96">
-        <v>-0.7279278720000011</v>
+        <v>-0.7793313600000007</v>
       </c>
       <c r="P96">
-        <v>-2.305104928000003</v>
+        <v>-2.467882640000003</v>
       </c>
       <c r="Q96">
-        <v>3.794895071999997</v>
+        <v>3.632117359999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.598153197640344</v>
+        <v>1.908623837168413</v>
       </c>
       <c r="T96">
-        <v>7.627289022848479</v>
+        <v>9.152746827418179</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2038441024146148</v>
+        <v>0.2016983750207768</v>
       </c>
       <c r="W96">
-        <v>0.1168756857655346</v>
+        <v>0.11719067854695</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8493504267275617</v>
+        <v>0.8404098959199032</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.206762336478023</v>
+        <v>0.207772336478023</v>
       </c>
       <c r="C97">
-        <v>5.318442235854889</v>
+        <v>2.968224143944497</v>
       </c>
       <c r="D97">
-        <v>142.9234422358549</v>
+        <v>142.0322241439445</v>
       </c>
       <c r="E97">
-        <v>34.10500000000002</v>
+        <v>35.56400000000002</v>
       </c>
       <c r="F97">
-        <v>138.605</v>
+        <v>140.064</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -9229,37 +9229,37 @@
         <v>17.1</v>
       </c>
       <c r="M97">
-        <v>20.347214</v>
+        <v>20.5613952</v>
       </c>
       <c r="N97">
-        <v>-3.247214000000003</v>
+        <v>-3.461395200000002</v>
       </c>
       <c r="O97">
-        <v>-0.7793313600000007</v>
+        <v>-0.8307348480000004</v>
       </c>
       <c r="P97">
-        <v>-2.467882640000003</v>
+        <v>-2.630660352000001</v>
       </c>
       <c r="Q97">
-        <v>3.632117359999997</v>
+        <v>3.469339647999998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.908623837168413</v>
+        <v>2.374329796460518</v>
       </c>
       <c r="T97">
-        <v>9.152746827418179</v>
+        <v>11.44093353427273</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2016983750207768</v>
+        <v>0.199597350280977</v>
       </c>
       <c r="W97">
-        <v>0.11719067854695</v>
+        <v>0.1174991089787526</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8404098959199032</v>
+        <v>0.8316556261707376</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.207772336478023</v>
+        <v>0.208782336478023</v>
       </c>
       <c r="C98">
-        <v>2.968224143944525</v>
+        <v>0.6290517922325023</v>
       </c>
       <c r="D98">
-        <v>142.0322241439445</v>
+        <v>141.1520517922325</v>
       </c>
       <c r="E98">
-        <v>35.56399999999999</v>
+        <v>37.023</v>
       </c>
       <c r="F98">
-        <v>140.064</v>
+        <v>141.523</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -9311,37 +9311,37 @@
         <v>17.1</v>
       </c>
       <c r="M98">
-        <v>20.5613952</v>
+        <v>20.7755764</v>
       </c>
       <c r="N98">
-        <v>-3.461395199999998</v>
+        <v>-3.675576400000001</v>
       </c>
       <c r="O98">
-        <v>-0.8307348479999995</v>
+        <v>-0.8821383360000001</v>
       </c>
       <c r="P98">
-        <v>-2.630660351999999</v>
+        <v>-2.793438064</v>
       </c>
       <c r="Q98">
-        <v>3.469339648000001</v>
+        <v>3.306561935999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.374329796460512</v>
+        <v>3.150506395280682</v>
       </c>
       <c r="T98">
-        <v>11.4409335342727</v>
+        <v>15.25457804569693</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1995973502809771</v>
+        <v>0.1975396456389051</v>
       </c>
       <c r="W98">
-        <v>0.1174991089787526</v>
+        <v>0.1178011800202087</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8316556261707377</v>
+        <v>0.8230818568287713</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.208782336478023</v>
+        <v>0.209792336478023</v>
       </c>
       <c r="C99">
-        <v>0.6290517922325023</v>
+        <v>-1.699278905603279</v>
       </c>
       <c r="D99">
-        <v>141.1520517922325</v>
+        <v>140.2827210943967</v>
       </c>
       <c r="E99">
-        <v>37.023</v>
+        <v>38.482</v>
       </c>
       <c r="F99">
-        <v>141.523</v>
+        <v>142.982</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -9393,37 +9393,37 @@
         <v>17.1</v>
       </c>
       <c r="M99">
-        <v>20.7755764</v>
+        <v>20.9897576</v>
       </c>
       <c r="N99">
-        <v>-3.675576400000001</v>
+        <v>-3.889757599999999</v>
       </c>
       <c r="O99">
-        <v>-0.8821383360000001</v>
+        <v>-0.9335418239999999</v>
       </c>
       <c r="P99">
-        <v>-2.793438064</v>
+        <v>-2.956215776</v>
       </c>
       <c r="Q99">
-        <v>3.306561935999999</v>
+        <v>3.143784224</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.150506395280682</v>
+        <v>4.702859592921024</v>
       </c>
       <c r="T99">
-        <v>15.25457804569693</v>
+        <v>22.8818670685454</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1975396456389051</v>
+        <v>0.1955239349691204</v>
       </c>
       <c r="W99">
-        <v>0.1178011800202087</v>
+        <v>0.1180970863465331</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8230818568287713</v>
+        <v>0.8146830623713349</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.209792336478023</v>
+        <v>0.210802336478023</v>
       </c>
       <c r="C100">
-        <v>-1.699278905603279</v>
+        <v>-4.016967038932904</v>
       </c>
       <c r="D100">
-        <v>140.2827210943967</v>
+        <v>139.4240329610671</v>
       </c>
       <c r="E100">
-        <v>38.482</v>
+        <v>39.941</v>
       </c>
       <c r="F100">
-        <v>142.982</v>
+        <v>144.441</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -9475,37 +9475,37 @@
         <v>17.1</v>
       </c>
       <c r="M100">
-        <v>20.9897576</v>
+        <v>21.2039388</v>
       </c>
       <c r="N100">
-        <v>-3.889757599999999</v>
+        <v>-4.103938800000002</v>
       </c>
       <c r="O100">
-        <v>-0.9335418239999999</v>
+        <v>-0.9849453120000004</v>
       </c>
       <c r="P100">
-        <v>-2.956215776</v>
+        <v>-3.118993488000001</v>
       </c>
       <c r="Q100">
-        <v>3.143784224</v>
+        <v>2.981006511999998</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.702859592921024</v>
+        <v>9.359919185842047</v>
       </c>
       <c r="T100">
-        <v>22.8818670685454</v>
+        <v>45.76373413709079</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1955239349691204</v>
+        <v>0.193548945727008</v>
       </c>
       <c r="W100">
-        <v>0.1180970863465331</v>
+        <v>0.1183870147672752</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8146830623713349</v>
+        <v>0.8064539405292002</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.210802336478023</v>
-      </c>
-      <c r="C101">
-        <v>-4.016967038932904</v>
-      </c>
-      <c r="D101">
-        <v>139.4240329610671</v>
-      </c>
-      <c r="E101">
-        <v>39.941</v>
-      </c>
-      <c r="F101">
-        <v>144.441</v>
-      </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-      <c r="H101">
-        <v>41.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23.2</v>
-      </c>
-      <c r="K101">
-        <v>6.1</v>
-      </c>
-      <c r="L101">
-        <v>17.1</v>
-      </c>
-      <c r="M101">
-        <v>21.2039388</v>
-      </c>
-      <c r="N101">
-        <v>-4.103938800000002</v>
-      </c>
-      <c r="O101">
-        <v>-0.9849453120000004</v>
-      </c>
-      <c r="P101">
-        <v>-3.118993488000001</v>
-      </c>
-      <c r="Q101">
-        <v>2.981006511999998</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.359919185842047</v>
-      </c>
-      <c r="T101">
-        <v>45.76373413709079</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.193548945727008</v>
-      </c>
-      <c r="W101">
-        <v>0.1183870147672752</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8064539405292002</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
